--- a/pmu-admissions-audit/email_package_v2/02_Admission_Pages_Comments_Register.xlsx
+++ b/pmu-admissions-audit/email_package_v2/02_Admission_Pages_Comments_Register.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D. Previous requests" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A. Key findings'!$A$4:$J$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'A. Key findings'!$A$4:$L$75</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'A. Key findings'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'B. Page-by-page notes'!$A$4:$I$215</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'B. Page-by-page notes'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C. Decisions'!$A$4:$E$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C. Decisions'!$A$4:$H$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'C. Decisions'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'D. Previous requests'!$A$4:$C$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'D. Previous requests'!$4:$4</definedName>
@@ -202,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -269,6 +269,16 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -669,7 +679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:F30"/>
+  <dimension ref="B2:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -678,6 +688,12 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -690,7 +706,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Revisit of the Admissions Office webpages – published content as of 10 October 2026</t>
+          <t>Revisit of the Admissions Office webpages – published content as of 10 October 2026 (key facts re-checked 11 October 2026)</t>
         </is>
       </c>
     </row>
@@ -707,6 +723,11 @@
           <t>Coverage</t>
         </is>
       </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Key findings by area</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
@@ -719,6 +740,36 @@
           <t>Count</t>
         </is>
       </c>
+      <c r="H7" s="30" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="I7" s="30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J7" s="30" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="K7" s="30" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="L7" s="30" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="M7" s="30" t="inlineStr">
+        <is>
+          <t>Needs decision</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="inlineStr">
@@ -729,6 +780,26 @@
       <c r="C8" s="29" t="n">
         <v>39</v>
       </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>Fees &amp; VAT</t>
+        </is>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="M8" s="32" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="inlineStr">
@@ -739,6 +810,26 @@
       <c r="C9" s="29" t="n">
         <v>1248</v>
       </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>Eligibility &amp; admission criteria</t>
+        </is>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="M9" s="32" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
@@ -749,6 +840,26 @@
       <c r="C10" s="29" t="n">
         <v>257</v>
       </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>Admission cycle, calendar &amp; application route</t>
+        </is>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" s="32" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
@@ -759,6 +870,26 @@
       <c r="C11" s="29" t="n">
         <v>136</v>
       </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>Graduate programmes &amp; catalogue</t>
+        </is>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="M11" s="32" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
@@ -769,6 +900,48 @@
       <c r="C12" s="29" t="n">
         <v>3</v>
       </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>English language tests</t>
+        </is>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" s="32" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>Contact &amp; privacy</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" s="32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -776,6 +949,26 @@
           <t>Findings and notes by priority</t>
         </is>
       </c>
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>Wording, accessibility &amp; web quality</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="L14" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="M14" s="32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
@@ -802,6 +995,31 @@
         <is>
           <t>Total</t>
         </is>
+      </c>
+      <c r="H15" s="33" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="I15" s="9">
+        <f>SUM(I8:I14)</f>
+        <v/>
+      </c>
+      <c r="J15" s="9">
+        <f>SUM(J8:J14)</f>
+        <v/>
+      </c>
+      <c r="K15" s="9">
+        <f>SUM(K8:K14)</f>
+        <v/>
+      </c>
+      <c r="L15" s="9">
+        <f>SUM(L8:L14)</f>
+        <v/>
+      </c>
+      <c r="M15" s="9">
+        <f>SUM(M8:M14)</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -941,19 +1159,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -966,7 +1186,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Independent findings, verified line by line against the published pages (10 October 2026)</t>
+          <t>Verified line by line against the published pages (10 Oct 2026; key facts re-checked 11 Oct 2026). "Decision needed" links to sheet C.</t>
         </is>
       </c>
     </row>
@@ -981,6 +1201,8 @@
       <c r="H3" s="18" t="n"/>
       <c r="I3" s="18" t="n"/>
       <c r="J3" s="18" t="n"/>
+      <c r="K3" s="18" t="n"/>
+      <c r="L3" s="18" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
@@ -1000,35 +1222,45 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
           <t>Page(s)</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Comment (what the published page shows)</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
-        <is>
-          <t>Evidence (verbatim, as published 10 Oct 2026)</t>
-        </is>
-      </c>
       <c r="H4" s="19" t="inlineStr">
         <is>
+          <t>Evidence (verbatim, as published)</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
           <t>Proposed change</t>
         </is>
       </c>
-      <c r="I4" s="19" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>Decision owner (proposed)</t>
         </is>
       </c>
-      <c r="J4" s="19" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>Decision needed</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1040,7 +1272,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>F-01</t>
+          <t>F-02</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -1050,37 +1282,47 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>international_students ↔ admissions_requirements_cs_eng_majors</t>
+          <t>Fees &amp; VAT</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
+          <t>international_students ↔ admission-from-other-universities, visiting-student-admission</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>International CS/Engineering criteria still require SAT II (SAT Subject Tests were discontinued by College Board in 2021).</t>
-        </is>
-      </c>
       <c r="G5" s="21" t="inlineStr">
         <is>
-          <t>Intl: "Computer Science &amp; Engineering Majors: Secondary School 40% / SAT I 30% / SAT II 30%" vs local "HS GPA ≥85 40% / Qudrat ≥65 30% / Tahseely ≥65 30%"; College Board ended Subject Tests (Jan 2021)</t>
+          <t>International transfer/visiting application fee shows SAR 500 (excl. VAT), while transfer and visiting pages show SAR 950 (incl. VAT).</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>Replace with the approved alternative (e.g., SAT I / Tahseely equivalent) and remove SAT II.</t>
+          <t>Intl: "SAR 500 (excl. VAT)"; local: "SAR 950 (incl. VAT)"; official Other Fees page (student_fees_tf_ro): "Admission Application Fees- Undergraduate Programs … (includes the VAT 15%) Non-refundable SAR 950"</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Colleges</t>
+          <t>Publish one approved fee and VAT treatment per applicant type.</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Finance + Admissions</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1332,7 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>F-02</t>
+          <t>F-03</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -1100,37 +1342,47 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>international_students ↔ admission-from-other-universities, visiting-student-admission</t>
+          <t>Fees &amp; VAT</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
+          <t>college_of_medicine_admission (+ medical_program_studies_fees_tf_ro)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t>International transfer/visiting application fee shows SAR 500 (excl. VAT), while transfer and visiting pages show SAR 950 (incl. VAT).</t>
-        </is>
-      </c>
       <c r="G6" s="23" t="inlineStr">
         <is>
-          <t>Intl: "SAR 500 (excl. VAT)"; local: "SAR 950 (incl. VAT)"; official Other Fees page (student_fees_tf_ro): "Admission Application Fees- Undergraduate Programs … (includes the VAT 15%) Non-refundable SAR 950"</t>
+          <t>Medicine application fee: SAR 1,000 (incl. VAT) on the admission page vs SAR 1,150 (VAT inclusive) on the medical fees page.</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>Publish one approved fee and VAT treatment per applicant type.</t>
+          <t>Medicine: "SAR 1000 (incl. VAT)"; fees page: "Medical Application Fee SAR 1,150 (VAT inclusive)"; 1000×1.15=1150</t>
         </is>
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>Finance + Admissions</t>
+          <t>Confirm the approved amount and align both pages.</t>
         </is>
       </c>
       <c r="J6" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Finance + College of Medicine</t>
+        </is>
+      </c>
+      <c r="K6" s="22" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1392,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>F-03</t>
+          <t>F-01</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -1150,37 +1402,47 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>college_of_medicine_admission (+ medical_program_studies_fees_tf_ro)</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
         <is>
+          <t>international_students ↔ admissions_requirements_cs_eng_majors</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>Medicine application fee: SAR 1,000 (incl. VAT) on the admission page vs SAR 1,150 (VAT inclusive) on the medical fees page.</t>
-        </is>
-      </c>
       <c r="G7" s="21" t="inlineStr">
         <is>
-          <t>Medicine: "SAR 1000 (incl. VAT)"; fees page: "Medical Application Fee SAR 1,150 (VAT inclusive)"; 1000×1.15=1150</t>
+          <t>International CS/Engineering criteria still require SAT II (SAT Subject Tests were discontinued by College Board in 2021).</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t>Confirm the approved amount and align both pages.</t>
+          <t>Intl: "Computer Science &amp; Engineering Majors: Secondary School 40% / SAT I 30% / SAT II 30%" vs local "HS GPA ≥85 40% / Qudrat ≥65 30% / Tahseely ≥65 30%"; College Board ended Subject Tests (Jan 2021)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>Finance + College of Medicine</t>
+          <t>Replace with the approved alternative (e.g., SAT I / Tahseely equivalent) and remove SAT II.</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Colleges</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1462,47 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
+          <t>Admission cycle, calendar &amp; application route</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
           <t>admission_calendar_fs_ro</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>Admission calendar is for Fall 2026 only; all dates have passed and results are announced before some submission deadlines close.</t>
-        </is>
-      </c>
       <c r="G8" s="23" t="inlineStr">
         <is>
+          <t>The admission calendar covers Fall 2026 only and all its dates have passed; the results window (19–21 July) also overlaps the 20 July deadlines for English test scores and transfer documents.</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
           <t>"From July 19 to July 21, 2026" vs "Last day to submit IELTS or TOEFL iBT 2026-07-20"; all dates ≤ 2026-08-30; today 2026-10-10</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>Publish the next intake (or 'Admissions closed – next intake opens on …') and fix date order.</t>
-        </is>
-      </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
+          <t>Publish the next intake (or "Admissions closed – next intake opens on …") and order the dates logically.</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
           <t>Admissions</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K8" s="22" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1512,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>F-16</t>
+          <t>F-48</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -1250,37 +1522,47 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>admissions_requirements_emgms_gdp</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
+          <t>international_students ↔ admission_calendar_fs_ro</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>EMGMS page contains another university's text ('UA Center for English as Second Language (CESL)').</t>
-        </is>
-      </c>
       <c r="G9" s="21" t="inlineStr">
         <is>
-          <t>"Graduate English Language Endorsement from UA Center for English as Second Language (CESL)"; "IELTS – minimum composite score of 7, with no subject area below a 6"; "TOEFL – minimum of 79 iBT"</t>
+          <t>Non-Saudi applicants: calendar shows the Study in Saudi route as 'Closed' with no date, and the international page does not state the application route or deadline.</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t>Remove immediately and replace with PMU-approved EMGMS requirements.</t>
+          <t>Calendar: "For non Saudi Students: Apply online through Study in Saudi platform: https://studyinsaudi.sa/ar | Closed" (no date); International page: "The application process can be completed entirely online." (no route or deadline stated)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>Graduate Studies + College of Engineering</t>
+          <t>Publish the route and deadline for non-Saudi applicants on both pages.</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1572,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>F-48</t>
+          <t>F-16</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -1300,37 +1582,47 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>international_students ↔ admission_calendar_fs_ro (+ email 19f1347de)</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
+          <t>admissions_requirements_emgms_gdp</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t>Non-Saudi applicants: calendar shows the Study in Saudi route as 'Closed' with no date, and the international page does not state the application route or deadline.</t>
-        </is>
-      </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t>Site calendar: non-Saudi "Apply online through Study in Saudi platform … Closed"; Intl page: "application process can be completed entirely online". Email (Intl Office, 29 Jun 2026): "application deadline is 30th June at 4pm … you must also submit application through the study in Saudi portal … opens on 1st of July 2026 … To be eligible for admission, you must apply through both platforms."</t>
+          <t>EMGMS page contains another university's text ('UA Center for English as Second Language (CESL)').</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t>Publish the route and deadline for non-Saudi applicants on both pages.</t>
+          <t>"Graduate English Language Endorsement from UA Center for English as Second Language (CESL)"; "IELTS – minimum composite score of 7, with no subject area below a 6"; "TOEFL – minimum of 79 iBT"</t>
         </is>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Remove immediately and replace with PMU-approved EMGMS requirements.</t>
         </is>
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies + College of Engineering</t>
+        </is>
+      </c>
+      <c r="K10" s="22" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="L10" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1632,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>F-06</t>
+          <t>F-13</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -1350,37 +1642,47 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>college_of_medicine_admission</t>
+          <t>Fees &amp; VAT</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
+          <t>aptis-placement-test (+ student_fees_tf_ro)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>Medicine: the published minimum components cannot reach the stated minimum total (0.2×95 + 0.4×80 + 0.4×80 = 83 &lt; 86).</t>
-        </is>
-      </c>
       <c r="G11" s="21" t="inlineStr">
         <is>
-          <t>"(95%)","(80)","(80)" with "20% high school + 40% Qudrat + 40% Tahseely … 86 is the minimum": 0.2×95+0.4×80+0.4×80=83</t>
+          <t>The Aptis page does not state the test fee; the fees page shows SAR 575.</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t>Clarify the minimums and formula.</t>
+          <t>Aptis page: "they will be scheduled to take Aptis test"; fees page: "APTIS Exam Fees SAR 575"</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>College of Medicine + Admissions</t>
+          <t>Show the approved Aptis fee on the Aptis page.</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>PREP + Finance</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>D-02</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1692,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>F-07</t>
+          <t>F-06</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -1400,37 +1702,47 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>undergraduate_programs_admission, admissions_requirements_cs_eng_majors</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
         <is>
+          <t>college_of_medicine_admission</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
-        <is>
-          <t>The minimum weighted total for admission is referred to but not published.</t>
-        </is>
-      </c>
       <c r="G12" s="23" t="inlineStr">
         <is>
-          <t>"the minimum weighted total, defined by the Admissions Office, should be met"</t>
+          <t>Medicine: the published minimum components cannot reach the stated minimum total (0.2×95 + 0.4×80 + 0.4×80 = 83 &lt; 86).</t>
         </is>
       </c>
       <c r="H12" s="23" t="inlineStr">
         <is>
-          <t>Decide whether to publish the minimum weighted total.</t>
+          <t>"(95%)","(80)","(80)" with "20% high school + 40% Qudrat + 40% Tahseely … 86 is the minimum": 0.2×95+0.4×80+0.4×80=83</t>
         </is>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>Admissions policy owner</t>
+          <t>Clarify the minimums and formula.</t>
         </is>
       </c>
       <c r="J12" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>College of Medicine + Admissions</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>D-07</t>
+        </is>
+      </c>
+      <c r="L12" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1752,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>F-08</t>
+          <t>F-07</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1450,37 +1762,47 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>toefl-admission, ielts-admission</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
+          <t>undergraduate_programs_admission, admissions_requirements_cs_eng_majors</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>TOEFL requirements are shown only on the 0–120 scale; ETS introduced the 1–6 reporting scale on 21 Jan 2026.</t>
-        </is>
-      </c>
       <c r="G13" s="21" t="inlineStr">
         <is>
-          <t>Core 83/19; ETS moved to 1–6 scale on 21 Jan 2026 (secondary source)</t>
+          <t>The minimum weighted total for admission is referred to but not published.</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t>Publish an approved equivalence table including the new scale.</t>
+          <t>"the minimum weighted total, defined by the Admissions Office, should be met"</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Testing Center</t>
+          <t>Decide whether to publish the minimum weighted total.</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions policy owner</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>D-03</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1812,7 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>F-10</t>
+          <t>F-42</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -1500,37 +1822,47 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>direct-admissions…, admission-from-other-universities, cs_eng vs graduate pages</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
         <is>
+          <t>admission-from-the-prep-to-ug-programs ↔ preparatory-program-study-plan</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
-        <is>
-          <t>Undergraduate pages say 'equivalent TOEFL iBT' without a score, while graduate pages state 83/19.</t>
-        </is>
-      </c>
       <c r="G14" s="23" t="inlineStr">
         <is>
-          <t>"or equivalent TOEFL iBT (Learn more)" / "with acceptable scores" vs graduate "83 overall and 19 in each skill"</t>
+          <t>Preparatory maths placement matrix footnotes contradict between two pages.</t>
         </is>
       </c>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t>Publish one equivalence table and link it.</t>
+          <t>"** Department of Architecture is excluded from PRPM 0012" yet Architecture row = PRPM 0012 "Yes"; IT footnote attached to Engineering/Architecture rows; study-plan page has different rows/footnotes</t>
         </is>
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>Admissions + Testing Center</t>
+          <t>Keep one matrix.</t>
         </is>
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="K14" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L14" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1872,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>F-11</t>
+          <t>F-43</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -1550,37 +1882,47 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>admission (menu) ↔ admission_graduate_degree_programs ↔ degrees_programs_fs_ro</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
+          <t>admissions_requirements_milbl_gdp</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>Graduate program lists differ between the hub menu, the graduate page and Degrees &amp; Programs (MSHD vs MSEHD naming).</t>
-        </is>
-      </c>
       <c r="G15" s="21" t="inlineStr">
         <is>
-          <t>Menu lists EMGMS &amp; MIBL; graduate home omits EMGMS; Degrees list omits EMGMS; labels "MSHD"/"MSEHD"/"Master of Human Development"</t>
+          <t>MIBL: GPA requirement has no number and the 30% 'written test' is not described.</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t>Maintain one graduate program catalogue.</t>
+          <t>"A minimum (Very Good) in Bachelor’s Degree"; "30% for the written test"</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>Graduate Studies + Web</t>
+          <t>Complete the requirements.</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1932,7 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>F-13</t>
+          <t>F-47</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -1600,37 +1942,47 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>aptis-placement-test (+ student_fees_tf_ro)</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
+          <t>admissions_requirements_phdba_gdp</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
-        <is>
-          <t>The Aptis page does not state the test fee; the fees page shows SAR 575.</t>
-        </is>
-      </c>
       <c r="G16" s="23" t="inlineStr">
         <is>
-          <t>Aptis page: "they will be scheduled to take Aptis test"; fees page: "APTIS Exam Fees SAR 575"</t>
+          <t>PhD BA: GPA rule unclear; accreditation claim (AACSB) not referenced.</t>
         </is>
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>Show the approved Aptis fee on the Aptis page.</t>
+          <t>"minimum cumulative GPA of 3.00 … or … 3.20"; "internationally accredited by AACSB as top 6%" (sources confirm membership, not full accreditation)</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>PREP + Finance</t>
+          <t>Clarify / reference.</t>
         </is>
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K16" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L16" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1992,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>F-18</t>
+          <t>F-71</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -1650,37 +2002,47 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>all 39 scope items</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
+          <t>apply → admissions.pmu.edu.sa/welcome</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>Pages have an empty html 'lang' attribute (accessibility / screen readers).</t>
-        </is>
-      </c>
       <c r="G17" s="21" t="inlineStr">
         <is>
-          <t>document.documentElement.lang === "" on every www.pmu.edu.sa page probed (WCAG 3.1.1)</t>
+          <t>Bachelor's minimums and weights are published only on /apply, which redirects instantly (published minima compute to 72% non-engineering and 73% engineering/AI/CS).</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
         <is>
-          <t>Set lang='en' / 'ar' appropriately.</t>
+          <t>Raw GET of /apply: meta refresh 0 + location.replace; body: non-eng HS80/Qudrat60, weights 60/40; Eng/AI/CS/Arch HS85/Qudrat65/Tahseely65, weights 40/30/30, SAT1 1200 alternative</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Show requirements on a visible page; confirm the minimum weighted score.</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>D-01, D-03</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1690,7 +2052,7 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>F-19</t>
+          <t>F-72</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -1700,37 +2062,47 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>all (main page: 4 of 6 images)</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
+          <t>admissions_requirements_phdba_gdp</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
-        <is>
-          <t>Images without alternative text (main page: 4 of 6).</t>
-        </is>
-      </c>
       <c r="G18" s="23" t="inlineStr">
         <is>
-          <t>main page images logo-name.png ×2, logo-PMU-1.png, logo_new_r.png have no alt attribute (WCAG 1.1.1)</t>
+          <t>PhD BA eligibility sentence contains a double negative and three GPA thresholds without saying which applies.</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t>Add alt text.</t>
+          <t>"if the master degree is not from another discipline they must successfully attend and complete with minimum GPA 2.80 12 credit hours of MBA"</t>
         </is>
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Rewrite as clear conditions.</t>
         </is>
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K18" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1740,7 +2112,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>F-22</t>
+          <t>F-76</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -1750,37 +2122,47 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>apply → admissions.pmu.edu.sa/welcome ↔ admission_calendar_fs_ro</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
+          <t>/apply ↔ sat-admission ↔ admissions_requirements_cs_eng_majors</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>Two conflicting calendars: the application portal shows 'No events are currently published' while the admission calendar shows Fall 2026 dates.</t>
-        </is>
-      </c>
       <c r="G19" s="21" t="inlineStr">
         <is>
-          <t>Portal: "No events are currently published. Please check back later."; site publishes dates; footer "2022 ©"</t>
+          <t>SAT 1200 alternative is described differently: /apply (instead of Qudrat and Tahseely, all Eng/AI/CS/Architecture), SAT page (international certificate holders, instead of Qudrat), CS/Eng page ('SAAT – Tahseely or SAT 1 (1200)').</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
         <is>
-          <t>Use one calendar source.</t>
+          <t>apply: "a SAT 1 total score of 1200 is accepted in place of both Qudrat and Tahseely"; sat-admission: "Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests"; cs_eng: "SAAT – Tahseely or SAT 1 (1200)"</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>Admissions + IT</t>
+          <t>Publish one rule.</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1790,7 +2172,7 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>F-23</t>
+          <t>F-78</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -1800,37 +2182,47 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>apply</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
+          <t>application_form/admissions_requirements pages (PhD ME, EMBA, MBA, MSME, MSEE, MSCE, MSID, MIBL)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
-        <is>
-          <t>Bilingual requirements content on /apply is never seen: the page redirects immediately to the portal.</t>
-        </is>
-      </c>
       <c r="G20" s="23" t="inlineStr">
         <is>
-          <t>Static HTML of /apply has AR/EN IELTS/TOEFL text; browser lands on admissions.pmu.edu.sa/welcome with no requirements</t>
+          <t>The '(Very Good)' label is attached to different GPA minimums: 2.50/4.00 on master's pages and 3.00/4.00 on the PhD page; MIBL states only 'minimum (Very Good)' with no number.</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
         <is>
-          <t>Publish requirements on a visible page.</t>
+          <t>EMBA/MBA/MSME/MSEE/MSCE/MSID: "A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good)"; PhD ME: "A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)"; MIBL: "A minimum (Very Good) in Bachelor’s Degree"</t>
         </is>
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>Admissions + Web</t>
+          <t>Keep programme-specific minimums but use consistent grade labels and state a number for MIBL.</t>
         </is>
       </c>
       <c r="J20" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L20" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1840,7 +2232,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>F-25</t>
+          <t>F-80</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -1850,37 +2242,47 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>degrees_programs_fs_ro ↔ college_of_medicine_admission, emgms</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
+          <t>direct-admissions-from-secondary-school, admissions_requirements_cs_eng_majors ↔ admission-to-the-preparatory-program, admission-from-other-universities, visiting-student-admission, international_students</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>Degrees &amp; Programs does not list Medicine or EMGMS, although both have admission pages.</t>
-        </is>
-      </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>Rendered Degrees &amp; Programs (10 tables) lacks Medicine &amp; EMGMS; both have admission pages</t>
+          <t>ID documents are inconsistent: 'Copy of Saudi ID' only on the Direct Admission and CS/Engineering pages, 'Saudi ID or Iqama (for Non-Saudis)' on others, and 'Copy of National ID' for applicants without Saudi residence.</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
         <is>
-          <t>Update the programme catalogue.</t>
+          <t>direct/cs_eng: "Copy of Saudi ID"; prep/transfer/visiting: "Copy of Saudi ID or “Iqama” (for Non-Saudis)"; international: "Copy of National ID"</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Academic Affairs</t>
+          <t>Publish one document list per applicant type.</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1890,7 +2292,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>F-29</t>
+          <t>F-22</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -1900,37 +2302,47 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>admissions_requirements_milbl_gdp vs 21 graduate pages</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
         <is>
+          <t>apply → admissions.pmu.edu.sa/welcome ↔ admission_calendar_fs_ro</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
-        <is>
-          <t>MIBL requires IELTS 6.5, while other graduate pages require 6.0.</t>
-        </is>
-      </c>
       <c r="G22" s="23" t="inlineStr">
         <is>
-          <t>MIBL: "6.5 overall and 5.5 in each skill" vs others "6.0 overall and 5.5 in each skill"</t>
+          <t>Two conflicting calendars: the application portal shows 'No events are currently published' while the admission calendar shows Fall 2026 dates.</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
         <is>
-          <t>Confirm the MIBL requirement.</t>
+          <t>Portal: "No events are currently published. Please check back later."; site publishes dates; footer "2022 ©"</t>
         </is>
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Use one calendar source.</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + IT</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1940,7 +2352,7 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>F-31</t>
+          <t>F-23</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -1950,37 +2362,47 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>admission_calendar_fs_ro (+ academic_calendar_2026_2027_ro)</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
+          <t>apply</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>Calendar: 'Orientation for new applicants – TBA'; no Spring window.</t>
-        </is>
-      </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>"Orientation for new applicants TBA" vs academic calendar "Orientation for the new students August 27, 2026"/"January 14, 2027"</t>
+          <t>Bilingual requirements content on /apply is never seen: the page redirects immediately to the portal.</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
         <is>
-          <t>Complete or remove; add next window.</t>
+          <t>Static HTML of /apply has AR/EN IELTS/TOEFL text; browser lands on admissions.pmu.edu.sa/welcome with no requirements</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Publish requirements on a visible page.</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Web</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>D-01</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2412,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>F-32</t>
+          <t>F-31</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -2000,37 +2422,47 @@
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>post_graduate_fees_tf_ro ↔ degrees_programs_fs_ro</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
         <is>
+          <t>admission_calendar_fs_ro (+ academic_calendar_2026_2027_ro)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
-        <is>
-          <t>Programmes priced on the graduate fees page (e.g., Master of Engineering in Innovation, Sustainability and Entrepreneurship) have no admission page or catalogue entry.</t>
-        </is>
-      </c>
       <c r="G24" s="23" t="inlineStr">
         <is>
-          <t>Fees list "Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33)" and "PRE-Master for Master of Education"; no admission page or Degrees row</t>
+          <t>Calendar: 'Orientation for new applicants – TBA'; no Spring window.</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
         <is>
-          <t>Confirm offering status and align.</t>
+          <t>"Orientation for new applicants TBA" vs academic calendar "Orientation for the new students August 27, 2026"/"January 14, 2027"</t>
         </is>
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies + Finance</t>
+          <t>Complete or remove; add next window.</t>
         </is>
       </c>
       <c r="J24" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K24" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L24" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2050,37 +2482,47 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
+          <t>Admission cycle, calendar &amp; application route</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
           <t>admission (main page)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>The main admission page consists mainly of link lists with little guidance.</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>Body = H1 "Admissions Office" + 4 H2 link lists; no intro, no intake status, no dates, no fees, no CTA hierarchy</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>Restructure around applicant type (journey).</t>
         </is>
       </c>
-      <c r="I25" s="21" t="inlineStr">
+      <c r="J25" s="21" t="inlineStr">
         <is>
           <t>Admissions + Web</t>
         </is>
       </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2532,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>F-39</t>
+          <t>F-11</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -2100,37 +2542,47 @@
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>11 graduate menu targets</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
         <is>
+          <t>admission (menu) ↔ admission_graduate_degree_programs ↔ degrees_programs_fs_ro</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
-        <is>
-          <t>Graduate landing pages do not show the application fee or required documents (the SAR 950 fee appears only on the individual application-form pages).</t>
-        </is>
-      </c>
       <c r="G26" s="23" t="inlineStr">
         <is>
-          <t>0 of 11 target pages contains "application fee" or "How to Apply"; these are on separate "Application Form" pages not linked from the main page; note: application-form pages state "non-refundable application fee of SAR 950 (incl. VAT)"</t>
+          <t>Graduate program lists differ between the hub menu, the graduate page and Degrees &amp; Programs (MSHD vs MSEHD naming).</t>
         </is>
       </c>
       <c r="H26" s="23" t="inlineStr">
         <is>
-          <t>Show the fee and document list on each programme page.</t>
+          <t>Menu lists EMGMS &amp; MIBL; graduate home omits EMGMS; Degrees list omits EMGMS; labels "MSHD"/"MSEHD"/"Master of Human Development"</t>
         </is>
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Maintain one graduate program catalogue.</t>
         </is>
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies + Web</t>
+        </is>
+      </c>
+      <c r="K26" s="22" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="L26" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2592,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>F-40</t>
+          <t>F-25</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -2150,37 +2602,47 @@
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>college_of_medicine_admission</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
+          <t>degrees_programs_fs_ro ↔ college_of_medicine_admission, emgms</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>Medicine page uses non-standard wording and has no English-language requirement.</t>
-        </is>
-      </c>
       <c r="G27" s="21" t="inlineStr">
         <is>
-          <t>"the process typically involves understanding the weighting and criteria that the medical college uses…"; no IELTS/TOEFL/English requirement on page</t>
+          <t>Degrees &amp; Programs does not list Medicine or EMGMS, although both have admission pages.</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>Provide approved text including language requirement.</t>
+          <t>Rendered Degrees &amp; Programs (10 tables) lacks Medicine &amp; EMGMS; both have admission pages</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>College of Medicine</t>
+          <t>Update the programme catalogue.</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Academic Affairs</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2652,7 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>F-41</t>
+          <t>F-29</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -2200,37 +2662,47 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>direct-admissions…, graduate pages, toefl-admission, ielts-admission</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E28" s="23" t="inlineStr">
         <is>
+          <t>admissions_requirements_milbl_gdp vs 21 graduate pages</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F28" s="23" t="inlineStr">
-        <is>
-          <t>'IELTS 6.0 or TOEFL iBT 83' are not equivalent per ETS tables (6.0 ≈ 60–78; 83 ≈ 6.5).</t>
-        </is>
-      </c>
       <c r="G28" s="23" t="inlineStr">
         <is>
-          <t>PMU: "6.0 overall … or equivalent TOEFL iBT 83"; ETS: 6.0≈60–78 (67 newer table), 6.5≈79–93 (81)</t>
+          <t>MIBL requires IELTS 6.5, while other graduate pages require 6.0.</t>
         </is>
       </c>
       <c r="H28" s="23" t="inlineStr">
         <is>
-          <t>Review the equivalence.</t>
+          <t>MIBL: "6.5 overall and 5.5 in each skill" vs others "6.0 overall and 5.5 in each skill"</t>
         </is>
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>Admissions + Testing Center</t>
+          <t>Confirm the MIBL requirement.</t>
         </is>
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2712,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>F-42</t>
+          <t>F-32</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -2250,37 +2722,47 @@
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>admission-from-the-prep-to-ug-programs ↔ preparatory-program-study-plan</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
+          <t>post_graduate_fees_tf_ro ↔ degrees_programs_fs_ro</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>Preparatory maths placement matrix footnotes contradict between two pages.</t>
-        </is>
-      </c>
       <c r="G29" s="21" t="inlineStr">
         <is>
-          <t>"** Department of Architecture is excluded from PRPM 0012" yet Architecture row = PRPM 0012 "Yes"; IT footnote attached to Engineering/Architecture rows; study-plan page has different rows/footnotes</t>
+          <t>Programmes priced on the graduate fees page (e.g., Master of Engineering in Innovation, Sustainability and Entrepreneurship) have no admission page or catalogue entry.</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
         <is>
-          <t>Keep one matrix.</t>
+          <t>Fees list "Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33)" and "PRE-Master for Master of Education"; no admission page or Degrees row</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>Confirm offering status and align.</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies + Finance</t>
+        </is>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2772,7 @@
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>F-43</t>
+          <t>F-39</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -2300,37 +2782,47 @@
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>admissions_requirements_milbl_gdp</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E30" s="23" t="inlineStr">
         <is>
+          <t>11 graduate menu targets</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F30" s="23" t="inlineStr">
-        <is>
-          <t>MIBL: GPA requirement has no number and the 30% 'written test' is not described.</t>
-        </is>
-      </c>
       <c r="G30" s="23" t="inlineStr">
         <is>
-          <t>"A minimum (Very Good) in Bachelor’s Degree"; "30% for the written test"</t>
+          <t>Graduate landing pages do not show the application fee or required documents (the SAR 950 fee appears only on the individual application-form pages).</t>
         </is>
       </c>
       <c r="H30" s="23" t="inlineStr">
         <is>
-          <t>Complete the requirements.</t>
+          <t>0 of 11 target pages contains "application fee" or "How to Apply"; these are on separate "Application Form" pages not linked from the main page; note: application-form pages state "non-refundable application fee of SAR 950 (incl. VAT)"</t>
         </is>
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
+          <t>Show the fee and document list on each programme page.</t>
+        </is>
+      </c>
+      <c r="J30" s="23" t="inlineStr">
+        <is>
           <t>Graduate Studies</t>
         </is>
       </c>
-      <c r="J30" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2832,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>F-45</t>
+          <t>F-40</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -2350,37 +2842,47 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>admissions_queries, admission_contact_gdp</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
+          <t>college_of_medicine_admission</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>Admission Query form collects name, email and mobile with no visible privacy notice; no phone channel.</t>
-        </is>
-      </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
-          <t>Query form collects Name/Email/Mobile with no privacy text on page; graduate contact = "Office: G-017 Admin Bld; Email" only; undergrad "Contact Us" → staff directory</t>
+          <t>Medicine page uses non-standard wording and has no English-language requirement.</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
-          <t>Add a privacy notice (legal review) and an official phone/email.</t>
+          <t>"the process typically involves understanding the weighting and criteria that the medical college uses…"; no IELTS/TOEFL/English requirement on page</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Compliance</t>
+          <t>Provide approved text including language requirement.</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>College of Medicine</t>
+        </is>
+      </c>
+      <c r="K31" s="20" t="inlineStr">
+        <is>
+          <t>D-07</t>
+        </is>
+      </c>
+      <c r="L31" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2892,7 @@
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>F-47</t>
+          <t>F-68</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -2400,37 +2902,47 @@
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>admissions_requirements_phdba_gdp</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E32" s="23" t="inlineStr">
         <is>
+          <t>admissions_requirements_milbl_gdp vs application_form_milbl_gdp</t>
+        </is>
+      </c>
+      <c r="F32" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F32" s="23" t="inlineStr">
-        <is>
-          <t>PhD BA: GPA rule unclear; accreditation claim (AACSB) not referenced.</t>
-        </is>
-      </c>
       <c r="G32" s="23" t="inlineStr">
         <is>
-          <t>"minimum cumulative GPA of 3.00 … or … 3.20"; "internationally accredited by AACSB as top 6%" (sources confirm membership, not full accreditation)</t>
+          <t>MIBL contradicts itself: requirements page IELTS 6.5, application form page 6.0.</t>
         </is>
       </c>
       <c r="H32" s="23" t="inlineStr">
         <is>
-          <t>Clarify / reference.</t>
+          <t>requirements: "6.5 overall and 5.5 in each skill"; application form: "6.0 overall and 5.5 in each skill" (both ... TOEFL iBT 83/19)</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
+          <t>Confirm and align.</t>
+        </is>
+      </c>
+      <c r="J32" s="23" t="inlineStr">
+        <is>
           <t>Graduate Studies</t>
         </is>
       </c>
-      <c r="J32" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="L32" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2952,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>F-65</t>
+          <t>F-69</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -2450,37 +2962,47 @@
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>admission page 'Contact Us' → faculty.pmu.edu.sa DepartmentStaffList/4</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
+          <t>admissions_requirements_emgms_gdp</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>'Contact Us' leads to the Student Affairs staff list; no Admissions contact.</t>
-        </is>
-      </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
-          <t>15 entries; titles Registration/Career/Campus Life; none Admissions</t>
+          <t>EMGMS: IELTS 7 vs TOEFL 79 (not equivalent) and legacy PBT test referenced.</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>Link to an Admissions contact page with official email/phone.</t>
+          <t>"TOEFL – minimum of 79 iBT (or 60 on the revised PBT…)"; "IELTS – minimum composite score of 7…"; ETS: 79≈IELTS 6.5</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Web</t>
+          <t>Replace with PMU-approved requirement.</t>
         </is>
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K33" s="20" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2490,7 +3012,7 @@
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>F-68</t>
+          <t>F-74</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -2500,37 +3022,47 @@
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>admissions_requirements_milbl_gdp vs application_form_milbl_gdp</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E34" s="23" t="inlineStr">
         <is>
+          <t>admissions_requirements_emgms_gdp ↔ admission</t>
+        </is>
+      </c>
+      <c r="F34" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F34" s="23" t="inlineStr">
-        <is>
-          <t>MIBL contradicts itself: requirements page IELTS 6.5, application form page 6.0.</t>
-        </is>
-      </c>
       <c r="G34" s="23" t="inlineStr">
         <is>
-          <t>requirements: "6.5 overall and 5.5 in each skill"; application form: "6.0 overall and 5.5 in each skill" (both ... TOEFL iBT 83/19)</t>
+          <t>EMGMS is listed on the hub but has no 'Apply' link or application route.</t>
         </is>
       </c>
       <c r="H34" s="23" t="inlineStr">
         <is>
-          <t>Confirm and align.</t>
+          <t>sidebar lists Apply for EMBA / MBA / MSHD / MSME only; hub lists 'Admissions to the EMGMS Program'</t>
         </is>
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Add the route or state the programme status.</t>
         </is>
       </c>
       <c r="J34" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies + Web</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="inlineStr">
+        <is>
+          <t>D-05</t>
+        </is>
+      </c>
+      <c r="L34" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2540,7 +3072,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>F-69</t>
+          <t>F-81</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -2550,37 +3082,47 @@
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>admissions_requirements_emgms_gdp</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
+          <t>international_students (Graduate Studies tab)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>EMGMS: IELTS 7 vs TOEFL 79 (not equivalent) and legacy PBT test referenced.</t>
-        </is>
-      </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
-          <t>"TOEFL – minimum of 79 iBT (or 60 on the revised PBT…)"; "IELTS – minimum composite score of 7…"; ETS: 79≈IELTS 6.5</t>
+          <t>The Graduate Studies tab on the international page lists only MBA, MSHD and MSME.</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>Replace with PMU-approved requirement.</t>
+          <t>Graduate Studies tab: "MBA" / "MSHD" / "MSME"</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Link to the full graduate programme list.</t>
         </is>
       </c>
       <c r="J35" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K35" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2590,7 +3132,7 @@
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>F-71</t>
+          <t>F-08</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -2600,37 +3142,47 @@
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>apply → admissions.pmu.edu.sa/welcome</t>
+          <t>English language tests</t>
         </is>
       </c>
       <c r="E36" s="23" t="inlineStr">
         <is>
+          <t>toefl-admission, ielts-admission</t>
+        </is>
+      </c>
+      <c r="F36" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F36" s="23" t="inlineStr">
-        <is>
-          <t>Bachelor's minimums and weights are published only on /apply, which redirects instantly (published minima compute to 72% non-engineering and 73% engineering/AI/CS).</t>
-        </is>
-      </c>
       <c r="G36" s="23" t="inlineStr">
         <is>
-          <t>Raw GET of /apply: meta refresh 0 + location.replace; body: non-eng HS80/Qudrat60, weights 60/40; Eng/AI/CS/Arch HS85/Qudrat65/Tahseely65, weights 40/30/30, SAT1 1200 alternative</t>
+          <t>TOEFL requirements are shown only on the 0–120 scale; ETS introduced the 1–6 reporting scale on 21 Jan 2026.</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr">
         <is>
-          <t>Show requirements on a visible page; confirm the minimum weighted score.</t>
+          <t>Core 83/19; ETS moved to 1–6 scale on 21 Jan 2026 (secondary source)</t>
         </is>
       </c>
       <c r="I36" s="23" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Publish an approved equivalence table including the new scale.</t>
         </is>
       </c>
       <c r="J36" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Testing Center</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="inlineStr">
+        <is>
+          <t>D-06</t>
+        </is>
+      </c>
+      <c r="L36" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2640,7 +3192,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>F-72</t>
+          <t>F-10</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -2650,37 +3202,47 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>admissions_requirements_phdba_gdp</t>
+          <t>English language tests</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
+          <t>direct-admissions…, admission-from-other-universities, cs_eng vs graduate pages</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>PhD BA eligibility sentence contains a double negative and three GPA thresholds without saying which applies.</t>
-        </is>
-      </c>
       <c r="G37" s="21" t="inlineStr">
         <is>
-          <t>"if the master degree is not from another discipline they must successfully attend and complete with minimum GPA 2.80 12 credit hours of MBA"</t>
+          <t>Undergraduate pages say 'equivalent TOEFL iBT' without a score, while graduate pages state 83/19.</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
         <is>
-          <t>Rewrite as clear conditions.</t>
+          <t>"or equivalent TOEFL iBT (Learn more)" / "with acceptable scores" vs graduate "83 overall and 19 in each skill"</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Publish one equivalence table and link it.</t>
         </is>
       </c>
       <c r="J37" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Testing Center</t>
+        </is>
+      </c>
+      <c r="K37" s="20" t="inlineStr">
+        <is>
+          <t>D-06</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2690,7 +3252,7 @@
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>F-74</t>
+          <t>F-41</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
@@ -2700,37 +3262,47 @@
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>admissions_requirements_emgms_gdp ↔ admission</t>
+          <t>English language tests</t>
         </is>
       </c>
       <c r="E38" s="23" t="inlineStr">
         <is>
+          <t>direct-admissions…, graduate pages, toefl-admission, ielts-admission</t>
+        </is>
+      </c>
+      <c r="F38" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F38" s="23" t="inlineStr">
-        <is>
-          <t>EMGMS is listed on the hub but has no 'Apply' link or application route.</t>
-        </is>
-      </c>
       <c r="G38" s="23" t="inlineStr">
         <is>
-          <t>sidebar lists Apply for EMBA / MBA / MSHD / MSME only; hub lists 'Admissions to the EMGMS Program'</t>
+          <t>'IELTS 6.0 or TOEFL iBT 83' are not equivalent per ETS tables (6.0 ≈ 60–78; 83 ≈ 6.5).</t>
         </is>
       </c>
       <c r="H38" s="23" t="inlineStr">
         <is>
-          <t>Add the route or state the programme status.</t>
+          <t>PMU: "6.0 overall … or equivalent TOEFL iBT 83"; ETS: 6.0≈60–78 (67 newer table), 6.5≈79–93 (81)</t>
         </is>
       </c>
       <c r="I38" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies + Web</t>
+          <t>Review the equivalence.</t>
         </is>
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Testing Center</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="inlineStr">
+        <is>
+          <t>D-06</t>
+        </is>
+      </c>
+      <c r="L38" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2740,7 +3312,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>F-76</t>
+          <t>F-45</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -2750,37 +3322,47 @@
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>/apply ↔ sat-admission ↔ admissions_requirements_cs_eng_majors</t>
+          <t>Contact &amp; privacy</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
         <is>
+          <t>admissions_queries, admission_contact_gdp</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F39" s="21" t="inlineStr">
-        <is>
-          <t>SAT 1200 alternative is described differently: /apply (instead of Qudrat and Tahseely, all Eng/AI/CS/Architecture), SAT page (international certificate holders, instead of Qudrat), CS/Eng page ('SAAT – Tahseely or SAT 1 (1200)').</t>
-        </is>
-      </c>
       <c r="G39" s="21" t="inlineStr">
         <is>
-          <t>apply: "a SAT 1 total score of 1200 is accepted in place of both Qudrat and Tahseely"; sat-admission: "Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests"; cs_eng: "SAAT – Tahseely or SAT 1 (1200)"</t>
+          <t>Admission Query form collects name, email and mobile with no visible privacy notice; no phone channel.</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
         <is>
-          <t>Publish one rule.</t>
+          <t>Query form collects Name/Email/Mobile with no privacy text on page; graduate contact = "Office: G-017 Admin Bld; Email" only; undergrad "Contact Us" → staff directory</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Add a privacy notice (legal review) and an official phone/email.</t>
         </is>
       </c>
       <c r="J39" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Compliance</t>
+        </is>
+      </c>
+      <c r="K39" s="20" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2790,7 +3372,7 @@
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>F-78</t>
+          <t>F-65</t>
         </is>
       </c>
       <c r="C40" s="22" t="inlineStr">
@@ -2800,37 +3382,47 @@
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>application_form/admissions_requirements pages (PhD ME, EMBA, MBA, MSME, MSEE, MSCE, MSID, MIBL)</t>
+          <t>Contact &amp; privacy</t>
         </is>
       </c>
       <c r="E40" s="23" t="inlineStr">
         <is>
+          <t>admission page 'Contact Us' → faculty.pmu.edu.sa DepartmentStaffList/4</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F40" s="23" t="inlineStr">
-        <is>
-          <t>The '(Very Good)' label is attached to different GPA minimums: 2.50/4.00 on master's pages and 3.00/4.00 on the PhD page; MIBL states only 'minimum (Very Good)' with no number.</t>
-        </is>
-      </c>
       <c r="G40" s="23" t="inlineStr">
         <is>
-          <t>EMBA/MBA/MSME/MSEE/MSCE/MSID: "A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good)"; PhD ME: "A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)"; MIBL: "A minimum (Very Good) in Bachelor’s Degree"</t>
+          <t>'Contact Us' leads to the Student Affairs staff list; no Admissions contact.</t>
         </is>
       </c>
       <c r="H40" s="23" t="inlineStr">
         <is>
-          <t>Keep programme-specific minimums but use consistent grade labels and state a number for MIBL.</t>
+          <t>15 entries; titles Registration/Career/Campus Life; none Admissions</t>
         </is>
       </c>
       <c r="I40" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Link to an Admissions contact page with official email/phone.</t>
         </is>
       </c>
       <c r="J40" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Web</t>
+        </is>
+      </c>
+      <c r="K40" s="22" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="L40" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2840,7 +3432,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>F-80</t>
+          <t>F-18</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -2850,37 +3442,47 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>direct-admissions-from-secondary-school, admissions_requirements_cs_eng_majors ↔ admission-to-the-preparatory-program, admission-from-other-universities, visiting-student-admission, international_students</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
         <is>
+          <t>all 39 scope items</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
-        <is>
-          <t>ID documents are inconsistent: 'Copy of Saudi ID' only on the Direct Admission and CS/Engineering pages, 'Saudi ID or Iqama (for Non-Saudis)' on others, and 'Copy of National ID' for applicants without Saudi residence.</t>
-        </is>
-      </c>
       <c r="G41" s="21" t="inlineStr">
         <is>
-          <t>direct/cs_eng: "Copy of Saudi ID"; prep/transfer/visiting: "Copy of Saudi ID or “Iqama” (for Non-Saudis)"; international: "Copy of National ID"</t>
+          <t>Pages have an empty html 'lang' attribute (accessibility / screen readers).</t>
         </is>
       </c>
       <c r="H41" s="21" t="inlineStr">
         <is>
-          <t>Publish one document list per applicant type.</t>
+          <t>document.documentElement.lang === "" on every www.pmu.edu.sa page probed (WCAG 3.1.1)</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Set lang='en' / 'ar' appropriately.</t>
         </is>
       </c>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2890,7 +3492,7 @@
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>F-81</t>
+          <t>F-19</t>
         </is>
       </c>
       <c r="C42" s="22" t="inlineStr">
@@ -2900,37 +3502,47 @@
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>international_students (Graduate Studies tab)</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E42" s="23" t="inlineStr">
         <is>
+          <t>all (main page: 4 of 6 images)</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F42" s="23" t="inlineStr">
-        <is>
-          <t>The Graduate Studies tab on the international page lists only MBA, MSHD and MSME.</t>
-        </is>
-      </c>
       <c r="G42" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies tab: "MBA" / "MSHD" / "MSME"</t>
+          <t>Images without alternative text (main page: 4 of 6).</t>
         </is>
       </c>
       <c r="H42" s="23" t="inlineStr">
         <is>
-          <t>Link to the full graduate programme list.</t>
+          <t>main page images logo-name.png ×2, logo-PMU-1.png, logo_new_r.png have no alt attribute (WCAG 1.1.1)</t>
         </is>
       </c>
       <c r="I42" s="23" t="inlineStr">
         <is>
-          <t>Admissions + Graduate Studies</t>
+          <t>Add alt text.</t>
         </is>
       </c>
       <c r="J42" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K42" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L42" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2940,7 +3552,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>F-14</t>
+          <t>F-35</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -2950,37 +3562,47 @@
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>multiple</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E43" s="21" t="inlineStr">
         <is>
+          <t>sat-admission ↔ admissions_requirements_cs_eng_majors</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr">
-        <is>
-          <t>Spelling/wording errors (e.g., 'Visting Students', 'wave' for 'waive', 'Verifaction Code').</t>
-        </is>
-      </c>
       <c r="G43" s="21" t="inlineStr">
         <is>
-          <t>"Visting Students","wave one or more","Verifaction Code","College of Medical","ADMISSSIONS"×4,"Admisssions"×2</t>
+          <t>The list of majors with higher requirements differs between the SAT page and the CS/Engineering page.</t>
         </is>
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
-          <t>Proofread.</t>
+          <t>SAT page lists "Artificial Intelligence … etc."; CS/Eng page omits AI &amp; Cybersecurity</t>
         </is>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Web</t>
+          <t>Publish one list.</t>
         </is>
       </c>
       <c r="J43" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K43" s="20" t="inlineStr">
+        <is>
+          <t>D-04</t>
+        </is>
+      </c>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -2990,7 +3612,7 @@
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>F-20</t>
+          <t>F-46</t>
         </is>
       </c>
       <c r="C44" s="22" t="inlineStr">
@@ -3000,37 +3622,47 @@
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E44" s="23" t="inlineStr">
         <is>
+          <t>international_students</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F44" s="23" t="inlineStr">
-        <is>
-          <t>No meta description/canonical; several hosts/URL forms for the same page.</t>
-        </is>
-      </c>
       <c r="G44" s="23" t="inlineStr">
         <is>
-          <t>Main page served at pmu.edu.sa without redirect to www; links use "../Admission/X.aspx" (legacy case/extension)</t>
+          <t>International page: empty 'Transportation' section; 'Acceptable SAT I' with no score.</t>
         </is>
       </c>
       <c r="H44" s="23" t="inlineStr">
         <is>
-          <t>Set canonical URLs.</t>
+          <t>"Transportation" heading with no text; "Acceptable SAT I" (no threshold) vs 1200/1300 elsewhere</t>
         </is>
       </c>
       <c r="I44" s="23" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Complete or remove.</t>
         </is>
       </c>
       <c r="J44" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L44" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3672,7 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>F-24</t>
+          <t>F-73</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -3050,37 +3682,47 @@
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>admission_calendar_fs_ro</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E45" s="21" t="inlineStr">
         <is>
+          <t>admissions_requirements_emba_gdp</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F45" s="21" t="inlineStr">
-        <is>
-          <t>Calendar 'Apply Now' uses javascript:__doPostBack instead of a normal link.</t>
-        </is>
-      </c>
       <c r="G45" s="21" t="inlineStr">
         <is>
-          <t>href="javascript:WebForm_DoPostBackWithOptions(… Apply_Now_ADS …)"; 7 URL forms reach the same portal</t>
+          <t>EMBA: 'from three to five years of professional work experience' implies a maximum.</t>
         </is>
       </c>
       <c r="H45" s="21" t="inlineStr">
         <is>
-          <t>Use a standard link.</t>
+          <t>"Successful candidates should have from three to five years of professional work experience"</t>
         </is>
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>State the minimum only (if intended).</t>
         </is>
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K45" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3732,7 @@
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>F-26</t>
+          <t>F-87</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
@@ -3100,37 +3742,47 @@
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>undergraduate_programs_admission, international_students, calendar</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E46" s="23" t="inlineStr">
         <is>
+          <t>admission-from-the-prep-to-ug-programs</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F46" s="23" t="inlineStr">
-        <is>
-          <t>Heading levels out of order on several pages.</t>
-        </is>
-      </c>
       <c r="G46" s="23" t="inlineStr">
         <is>
-          <t>H2 before H1; H1→H3→H4 then H3; H2→H4</t>
+          <t>Footnote markers in the preparatory maths table point to the wrong colleges.</t>
         </is>
       </c>
       <c r="H46" s="23" t="inlineStr">
         <is>
-          <t>Fix heading order.</t>
+          <t>"College of Engineering*", "College of Architecture &amp; Design*" but "* Department of Information Technology is excluded from PRPM 0022"; "College of Computer Engineering &amp; Science**" but "** Department of Architecture is excluded from PRPM 0012"</t>
         </is>
       </c>
       <c r="I46" s="23" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Re-link each footnote to the correct row.</t>
         </is>
       </c>
       <c r="J46" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>PREP + Web</t>
+        </is>
+      </c>
+      <c r="K46" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L46" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3792,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>F-35</t>
+          <t>F-24</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -3150,37 +3802,47 @@
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>sat-admission ↔ admissions_requirements_cs_eng_majors</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E47" s="21" t="inlineStr">
         <is>
+          <t>admission_calendar_fs_ro</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F47" s="21" t="inlineStr">
-        <is>
-          <t>The list of majors with higher requirements differs between the SAT page and the CS/Engineering page.</t>
-        </is>
-      </c>
       <c r="G47" s="21" t="inlineStr">
         <is>
-          <t>SAT page lists "Artificial Intelligence … etc."; CS/Eng page omits AI &amp; Cybersecurity</t>
+          <t>Calendar 'Apply Now' uses javascript:__doPostBack instead of a normal link.</t>
         </is>
       </c>
       <c r="H47" s="21" t="inlineStr">
         <is>
-          <t>Publish one list.</t>
+          <t>href="javascript:WebForm_DoPostBackWithOptions(… Apply_Now_ADS …)"; 7 URL forms reach the same portal</t>
         </is>
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>Use a standard link.</t>
         </is>
       </c>
       <c r="J47" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3852,7 @@
       </c>
       <c r="B48" s="22" t="inlineStr">
         <is>
-          <t>F-37</t>
+          <t>F-49</t>
         </is>
       </c>
       <c r="C48" s="22" t="inlineStr">
@@ -3200,37 +3862,47 @@
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>admission; admission_graduate_degree_programs</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E48" s="23" t="inlineStr">
         <is>
+          <t>admission_calendar_fs_ro</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F48" s="23" t="inlineStr">
-        <is>
-          <t>Ambiguous/duplicated link labels (e.g., several 'Home').</t>
-        </is>
-      </c>
       <c r="G48" s="23" t="inlineStr">
         <is>
-          <t>"Home"×3 (3 different targets); "Tuition &amp; Fees"×2 (different targets); "Application Form"/"Admissions Requirements"×5 identical</t>
+          <t>Calendar blocks are duplicated in the page source.</t>
         </is>
       </c>
       <c r="H48" s="23" t="inlineStr">
         <is>
-          <t>Use unique labels.</t>
+          <t>Rendered text repeats Undergraduate and Graduate calendar blocks twice</t>
         </is>
       </c>
       <c r="I48" s="23" t="inlineStr">
         <is>
+          <t>Remove duplication.</t>
+        </is>
+      </c>
+      <c r="J48" s="23" t="inlineStr">
+        <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="J48" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K48" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L48" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3912,7 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>F-38</t>
+          <t>F-77</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -3250,37 +3922,47 @@
       </c>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t>admission (main page)</t>
+          <t>Admission cycle, calendar &amp; application route</t>
         </is>
       </c>
       <c r="E49" s="21" t="inlineStr">
         <is>
+          <t>admissions.pmu.edu.sa/welcome</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F49" s="21" t="inlineStr">
-        <is>
-          <t>Structural accessibility issues on the main page (empty link, landmarks).</t>
-        </is>
-      </c>
       <c r="G49" s="21" t="inlineStr">
         <is>
-          <t>No &lt;main&gt; landmark (HEADER,NAV,HEADER,NAV,FOOTER,FOOTER); empty anchor href="#sidebar"; iframe search/new-search.html has no title; logo-PMU-1.png 301 (case)</t>
+          <t>Application portal is English-only, shows no privacy link and no admission calendar.</t>
         </is>
       </c>
       <c r="H49" s="21" t="inlineStr">
         <is>
-          <t>Fix structure.</t>
+          <t>Browser probe 2026-10-10: lang=en; privacy links=0; 'No events are currently published' (prior observation)</t>
         </is>
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Add Arabic and privacy notice (after compliance review).</t>
         </is>
       </c>
       <c r="J49" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + IT</t>
+        </is>
+      </c>
+      <c r="K49" s="20" t="inlineStr">
+        <is>
+          <t>D-09</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3972,7 @@
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>F-44</t>
+          <t>F-75</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
@@ -3300,37 +3982,47 @@
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>aptis-placement-test</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E50" s="23" t="inlineStr">
         <is>
+          <t>application_form_deme_gdp</t>
+        </is>
+      </c>
+      <c r="F50" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F50" s="23" t="inlineStr">
-        <is>
-          <t>Aptis score bands are not published; 'Core Program' term unexplained.</t>
-        </is>
-      </c>
       <c r="G50" s="23" t="inlineStr">
         <is>
-          <t>Levels listed (Pre Beginner…Advanced) without score bands; "direct entry into the Core Program"</t>
+          <t>PhD Mechanical Engineering page title says 'Application Form for MSDH'.</t>
         </is>
       </c>
       <c r="H50" s="23" t="inlineStr">
         <is>
-          <t>Publish bands.</t>
+          <t>TITLE: Application Form for MSDH :: Graduate Degree Programs … ; H: PhD in Mechanical Engineering ADMISSSIONS REQUIREMENTS</t>
         </is>
       </c>
       <c r="I50" s="23" t="inlineStr">
         <is>
-          <t>PREP</t>
+          <t>Correct the page title.</t>
         </is>
       </c>
       <c r="J50" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="K50" s="22" t="inlineStr">
+        <is>
+          <t>D-08</t>
+        </is>
+      </c>
+      <c r="L50" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3340,7 +4032,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>F-46</t>
+          <t>F-83</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -3350,37 +4042,47 @@
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>international_students</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E51" s="21" t="inlineStr">
         <is>
+          <t>admissions_requirements_msehd_gdp</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F51" s="21" t="inlineStr">
-        <is>
-          <t>International page: empty 'Transportation' section; 'Acceptable SAT I' with no score.</t>
-        </is>
-      </c>
       <c r="G51" s="21" t="inlineStr">
         <is>
-          <t>"Transportation" heading with no text; "Acceptable SAT I" (no threshold) vs 1200/1300 elsewhere</t>
+          <t>The MSHD page has a 'Work Experience' heading with no requirement under it.</t>
         </is>
       </c>
       <c r="H51" s="21" t="inlineStr">
         <is>
-          <t>Complete or remove.</t>
+          <t>"Work Experience" followed by "Personal Data Sheet/Curriculum Vita: …"</t>
         </is>
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
-          <t>Admissions</t>
+          <t>State the requirement or remove the heading.</t>
         </is>
       </c>
       <c r="J51" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies</t>
+        </is>
+      </c>
+      <c r="K51" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3390,7 +4092,7 @@
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>F-49</t>
+          <t>F-86</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
@@ -3400,37 +4102,47 @@
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>admission_calendar_fs_ro</t>
+          <t>Graduate programmes &amp; catalogue</t>
         </is>
       </c>
       <c r="E52" s="23" t="inlineStr">
         <is>
+          <t>post_graduate_fees_tf_ro ↔ graduate pages</t>
+        </is>
+      </c>
+      <c r="F52" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F52" s="23" t="inlineStr">
-        <is>
-          <t>Calendar blocks are duplicated in the page source.</t>
-        </is>
-      </c>
       <c r="G52" s="23" t="inlineStr">
         <is>
-          <t>Rendered text repeats Undergraduate and Graduate calendar blocks twice</t>
+          <t>Programme names in the graduate fee table differ from the admission pages (e.g. 'Human Development' vs 'Education and Human Development'; 'Doctoral program' vs 'PhD'; a 'Pre-Master for Master of Education' row with no matching programme).</t>
         </is>
       </c>
       <c r="H52" s="23" t="inlineStr">
         <is>
-          <t>Remove duplication.</t>
+          <t>"Master of Science in Human Development" and "Master of Science in Education and Human Development"; "Doctoral program in Mechanical Engineering" vs "PhD in Mechanical Engineering"; "PRE-Master for Master of Education" (no Master of Education admission page)</t>
         </is>
       </c>
       <c r="I52" s="23" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Use one official name per programme.</t>
         </is>
       </c>
       <c r="J52" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Graduate Studies + Finance</t>
+        </is>
+      </c>
+      <c r="K52" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L52" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3440,7 +4152,7 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>F-66</t>
+          <t>F-44</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -3450,37 +4162,47 @@
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>Staff_List?DEpt=4&amp;Name=Staff Name</t>
+          <t>English language tests</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
         <is>
+          <t>aptis-placement-test</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F53" s="21" t="inlineStr">
-        <is>
-          <t>Duplicated staff entry; placeholder parameter 'Name=Staff Name' in the link.</t>
-        </is>
-      </c>
       <c r="G53" s="21" t="inlineStr">
         <is>
-          <t>duplicate entry; Name=Staff Name dropped on redirect</t>
+          <t>Aptis score bands are not published; 'Core Program' term unexplained.</t>
         </is>
       </c>
       <c r="H53" s="21" t="inlineStr">
         <is>
-          <t>Clean up.</t>
+          <t>Levels listed (Pre Beginner…Advanced) without score bands; "direct entry into the Core Program"</t>
         </is>
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Publish bands.</t>
         </is>
       </c>
       <c r="J53" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>PREP</t>
+        </is>
+      </c>
+      <c r="K53" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3490,7 +4212,7 @@
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>F-67</t>
+          <t>F-66</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
@@ -3500,37 +4222,47 @@
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>/default</t>
+          <t>Contact &amp; privacy</t>
         </is>
       </c>
       <c r="E54" s="23" t="inlineStr">
         <is>
+          <t>Staff_List?DEpt=4&amp;Name=Staff Name</t>
+        </is>
+      </c>
+      <c r="F54" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
-        <is>
-          <t>Home page shows the NCAAA paragraph twice (visible, mobile).</t>
-        </is>
-      </c>
       <c r="G54" s="23" t="inlineStr">
         <is>
-          <t>Mobile DOM probe (390px): the NCAAA paragraph appears twice, both visible, not inside a slider; lang attr empty; no &lt;h1&gt;</t>
+          <t>Duplicated staff entry; placeholder parameter 'Name=Staff Name' in the link.</t>
         </is>
       </c>
       <c r="H54" s="23" t="inlineStr">
         <is>
-          <t>Remove duplicate.</t>
+          <t>duplicate entry; Name=Staff Name dropped on redirect</t>
         </is>
       </c>
       <c r="I54" s="23" t="inlineStr">
         <is>
+          <t>Clean up.</t>
+        </is>
+      </c>
+      <c r="J54" s="23" t="inlineStr">
+        <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="J54" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K54" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L54" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3540,7 +4272,7 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>F-70</t>
+          <t>F-14</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -3550,37 +4282,47 @@
       </c>
       <c r="D55" s="21" t="inlineStr">
         <is>
-          <t>/default</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E55" s="21" t="inlineStr">
         <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>Home page has no lang attribute and no H1.</t>
-        </is>
-      </c>
       <c r="G55" s="21" t="inlineStr">
         <is>
-          <t>result8_home.json: lang="", h1=[]</t>
+          <t>Spelling/wording errors (e.g., 'Visting Students', 'wave' for 'waive', 'Verifaction Code').</t>
         </is>
       </c>
       <c r="H55" s="21" t="inlineStr">
         <is>
-          <t>Add.</t>
+          <t>"Visting Students","wave one or more","Verifaction Code","College of Medical","ADMISSSIONS"×4,"Admisssions"×2</t>
         </is>
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Proofread.</t>
         </is>
       </c>
       <c r="J55" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Web</t>
+        </is>
+      </c>
+      <c r="K55" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3590,7 +4332,7 @@
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>F-73</t>
+          <t>F-20</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
@@ -3600,37 +4342,47 @@
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>admissions_requirements_emba_gdp</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E56" s="23" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F56" s="23" t="inlineStr">
-        <is>
-          <t>EMBA: 'from three to five years of professional work experience' implies a maximum.</t>
-        </is>
-      </c>
       <c r="G56" s="23" t="inlineStr">
         <is>
-          <t>"Successful candidates should have from three to five years of professional work experience"</t>
+          <t>No meta description/canonical; several hosts/URL forms for the same page.</t>
         </is>
       </c>
       <c r="H56" s="23" t="inlineStr">
         <is>
-          <t>State the minimum only (if intended).</t>
+          <t>Main page served at pmu.edu.sa without redirect to www; links use "../Admission/X.aspx" (legacy case/extension)</t>
         </is>
       </c>
       <c r="I56" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Set canonical URLs.</t>
         </is>
       </c>
       <c r="J56" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K56" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L56" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3640,7 +4392,7 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>F-75</t>
+          <t>F-26</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
@@ -3650,37 +4402,47 @@
       </c>
       <c r="D57" s="21" t="inlineStr">
         <is>
-          <t>application_form_deme_gdp</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E57" s="21" t="inlineStr">
         <is>
+          <t>undergraduate_programs_admission, international_students, calendar</t>
+        </is>
+      </c>
+      <c r="F57" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F57" s="21" t="inlineStr">
-        <is>
-          <t>PhD Mechanical Engineering page title says 'Application Form for MSDH'.</t>
-        </is>
-      </c>
       <c r="G57" s="21" t="inlineStr">
         <is>
-          <t>TITLE: Application Form for MSDH :: Graduate Degree Programs … ; H: PhD in Mechanical Engineering ADMISSSIONS REQUIREMENTS</t>
+          <t>Heading levels out of order on several pages.</t>
         </is>
       </c>
       <c r="H57" s="21" t="inlineStr">
         <is>
-          <t>Correct the page title.</t>
+          <t>H2 before H1; H1→H3→H4 then H3; H2→H4</t>
         </is>
       </c>
       <c r="I57" s="21" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Fix heading order.</t>
         </is>
       </c>
       <c r="J57" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K57" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L57" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3690,7 +4452,7 @@
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>F-77</t>
+          <t>F-37</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
@@ -3700,37 +4462,47 @@
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>admissions.pmu.edu.sa/welcome</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E58" s="23" t="inlineStr">
         <is>
+          <t>admission; admission_graduate_degree_programs</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F58" s="23" t="inlineStr">
-        <is>
-          <t>Application portal is English-only, shows no privacy link and no admission calendar.</t>
-        </is>
-      </c>
       <c r="G58" s="23" t="inlineStr">
         <is>
-          <t>Browser probe 2026-10-10: lang=en; privacy links=0; 'No events are currently published' (prior observation)</t>
+          <t>Ambiguous/duplicated link labels (e.g., several 'Home').</t>
         </is>
       </c>
       <c r="H58" s="23" t="inlineStr">
         <is>
-          <t>Add Arabic and privacy notice (after compliance review).</t>
+          <t>"Home"×3 (3 different targets); "Tuition &amp; Fees"×2 (different targets); "Application Form"/"Admissions Requirements"×5 identical</t>
         </is>
       </c>
       <c r="I58" s="23" t="inlineStr">
         <is>
-          <t>Admissions + IT</t>
+          <t>Use unique labels.</t>
         </is>
       </c>
       <c r="J58" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="K58" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L58" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3740,7 +4512,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>F-79</t>
+          <t>F-38</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
@@ -3750,37 +4522,47 @@
       </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>application_form_deme_gdp, admissions_requirements_msme_gdp, application_form_msee/msce/msid_gdp, admissions_requirements_milbl_gdp</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E59" s="21" t="inlineStr">
         <is>
+          <t>admission (main page)</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F59" s="21" t="inlineStr">
-        <is>
-          <t>'ADMISSSIONS' is misspelt in the headings of six graduate pages (PhD ME, MSME, MSEE, MSCE, MSID, MIBL).</t>
-        </is>
-      </c>
       <c r="G59" s="21" t="inlineStr">
         <is>
-          <t>"PHD IN MECHANICAL ENGINEERING ADMISSSIONS REQUIREMENTS"; "MSME ADMISSSIONS REQUIREMENTS"; "MIBL ADMISSSIONS REQUIREMENTS"</t>
+          <t>Structural accessibility issues on the main page (empty link, landmarks).</t>
         </is>
       </c>
       <c r="H59" s="21" t="inlineStr">
         <is>
-          <t>Correct to 'ADMISSIONS'.</t>
+          <t>No &lt;main&gt; landmark (HEADER,NAV,HEADER,NAV,FOOTER,FOOTER); empty anchor href="#sidebar"; iframe search/new-search.html has no title; logo-PMU-1.png 301 (case)</t>
         </is>
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Fix structure.</t>
         </is>
       </c>
       <c r="J59" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K59" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L59" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3790,7 +4572,7 @@
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>F-82</t>
+          <t>F-67</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
@@ -3800,37 +4582,47 @@
       </c>
       <c r="D60" s="23" t="inlineStr">
         <is>
-          <t>undergraduate_programs_admission, college_of_medicine_admission</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E60" s="23" t="inlineStr">
         <is>
+          <t>/default</t>
+        </is>
+      </c>
+      <c r="F60" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>Medicine pages use 'College of Medical' instead of 'College of Medicine', contain the typo 'were 86', and show 'Population Health (to be developed in launch phase)'.</t>
-        </is>
-      </c>
       <c r="G60" s="23" t="inlineStr">
         <is>
-          <t>"PMU College of Medical curriculum"; "College of Medical Admissions"; "were 86 is the minimum acceptable score"; "Population Health (to be developed in launch phase)"</t>
+          <t>Home page shows the NCAAA paragraph twice (visible, mobile).</t>
         </is>
       </c>
       <c r="H60" s="23" t="inlineStr">
         <is>
-          <t>Proofread and update the curriculum text.</t>
+          <t>Mobile DOM probe (390px): the NCAAA paragraph appears twice, both visible, not inside a slider; lang attr empty; no &lt;h1&gt;</t>
         </is>
       </c>
       <c r="I60" s="23" t="inlineStr">
         <is>
-          <t>College of Medicine + Web</t>
+          <t>Remove duplicate.</t>
         </is>
       </c>
       <c r="J60" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="K60" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L60" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3840,7 +4632,7 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>F-83</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
@@ -3850,37 +4642,47 @@
       </c>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>admissions_requirements_msehd_gdp</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E61" s="21" t="inlineStr">
         <is>
+          <t>/default</t>
+        </is>
+      </c>
+      <c r="F61" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F61" s="21" t="inlineStr">
-        <is>
-          <t>The MSHD page has a 'Work Experience' heading with no requirement under it.</t>
-        </is>
-      </c>
       <c r="G61" s="21" t="inlineStr">
         <is>
-          <t>"Work Experience" followed by "Personal Data Sheet/Curriculum Vita: …"</t>
+          <t>Home page has no lang attribute and no H1.</t>
         </is>
       </c>
       <c r="H61" s="21" t="inlineStr">
         <is>
-          <t>State the requirement or remove the heading.</t>
+          <t>Browser check (mobile, 10 Oct 2026): the page has no language attribute and no H1 heading</t>
         </is>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
-          <t>Graduate Studies</t>
+          <t>Add.</t>
         </is>
       </c>
       <c r="J61" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K61" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L61" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3890,7 +4692,7 @@
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>F-84</t>
+          <t>F-79</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
@@ -3900,37 +4702,47 @@
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>/default (Home)</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E62" s="23" t="inlineStr">
         <is>
+          <t>application_form_deme_gdp, admissions_requirements_msme_gdp, application_form_msee/msce/msid_gdp, admissions_requirements_milbl_gdp</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F62" s="23" t="inlineStr">
-        <is>
-          <t>Home page shows dated/inconsistent items: 'STUDENT ORIENTATION 2027-2028', 'THE Ranking 2024', and different copyright years (2020, 2021, 2022).</t>
-        </is>
-      </c>
       <c r="G62" s="23" t="inlineStr">
         <is>
-          <t>"STUDENT ORIENTATION 2027-2028"; "THE Ranking 2024"; "2020 © PMU"; "2021 © PMU"; "2022 © PMU"</t>
+          <t>'ADMISSSIONS' is misspelt in the headings of six graduate pages (PhD ME, MSME, MSEE, MSCE, MSID, MIBL).</t>
         </is>
       </c>
       <c r="H62" s="23" t="inlineStr">
         <is>
-          <t>Update news tiles and standardise the footer.</t>
+          <t>"PHD IN MECHANICAL ENGINEERING ADMISSSIONS REQUIREMENTS"; "MSME ADMISSSIONS REQUIREMENTS"; "MIBL ADMISSSIONS REQUIREMENTS"</t>
         </is>
       </c>
       <c r="I62" s="23" t="inlineStr">
         <is>
-          <t>Communications + Web</t>
+          <t>Correct to 'ADMISSIONS'.</t>
         </is>
       </c>
       <c r="J62" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="K62" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L62" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3940,7 +4752,7 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>F-85</t>
+          <t>F-82</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
@@ -3950,37 +4762,47 @@
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>admissions_queries; apply (Arabic)</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E63" s="21" t="inlineStr">
         <is>
+          <t>undergraduate_programs_admission, college_of_medicine_admission</t>
+        </is>
+      </c>
+      <c r="F63" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F63" s="21" t="inlineStr">
-        <is>
-          <t>Arabic spelling errors on the admission query form and /apply (e.g. 'الأسم', 'الإستفسار', 'الإللكتروني', 'نسب الموزونة').</t>
-        </is>
-      </c>
       <c r="G63" s="21" t="inlineStr">
         <is>
-          <t>"Name [الأسم]"; "Query [الإستفسار]"; "إستفساراتكم"; "Email [البريد الإللكتروني]"; "نسب الموزونة"</t>
+          <t>Medicine pages use 'College of Medical' instead of 'College of Medicine', contain the typo 'were 86', and show 'Population Health (to be developed in launch phase)'.</t>
         </is>
       </c>
       <c r="H63" s="21" t="inlineStr">
         <is>
-          <t>Correct to 'الاسم', 'الاستفسار', 'الإلكتروني', 'النسب الموزونة'.</t>
+          <t>"PMU College of Medical curriculum"; "College of Medical Admissions"; "were 86 is the minimum acceptable score"; "Population Health (to be developed in launch phase)"</t>
         </is>
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
-          <t>Admissions + Web</t>
+          <t>Proofread and update the curriculum text.</t>
         </is>
       </c>
       <c r="J63" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>College of Medicine + Web</t>
+        </is>
+      </c>
+      <c r="K63" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4812,7 @@
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>F-86</t>
+          <t>F-84</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
@@ -4000,37 +4822,47 @@
       </c>
       <c r="D64" s="23" t="inlineStr">
         <is>
-          <t>post_graduate_fees_tf_ro ↔ graduate pages</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E64" s="23" t="inlineStr">
         <is>
+          <t>/default (Home)</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F64" s="23" t="inlineStr">
-        <is>
-          <t>Programme names in the graduate fee table differ from the admission pages (e.g. 'Human Development' vs 'Education and Human Development'; 'Doctoral program' vs 'PhD'; a 'Pre-Master for Master of Education' row with no matching programme).</t>
-        </is>
-      </c>
       <c r="G64" s="23" t="inlineStr">
         <is>
-          <t>"Master of Science in Human Development" and "Master of Science in Education and Human Development"; "Doctoral program in Mechanical Engineering" vs "PhD in Mechanical Engineering"; "PRE-Master for Master of Education" (no Master of Education admission page)</t>
+          <t>Home page shows dated/inconsistent items: 'STUDENT ORIENTATION 2027-2028', 'THE Ranking 2024', and different copyright years (2020, 2021, 2022).</t>
         </is>
       </c>
       <c r="H64" s="23" t="inlineStr">
         <is>
-          <t>Use one official name per programme.</t>
+          <t>"STUDENT ORIENTATION 2027-2028"; "THE Ranking 2024"; "2020 © PMU"; "2021 © PMU"; "2022 © PMU"</t>
         </is>
       </c>
       <c r="I64" s="23" t="inlineStr">
         <is>
-          <t>Graduate Studies + Finance</t>
+          <t>Update news tiles and standardise the footer.</t>
         </is>
       </c>
       <c r="J64" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Communications + Web</t>
+        </is>
+      </c>
+      <c r="K64" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L64" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4040,7 +4872,7 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>F-87</t>
+          <t>F-85</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
@@ -4050,37 +4882,47 @@
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>admission-from-the-prep-to-ug-programs</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E65" s="21" t="inlineStr">
         <is>
+          <t>admissions_queries; apply (Arabic)</t>
+        </is>
+      </c>
+      <c r="F65" s="21" t="inlineStr">
+        <is>
           <t>Linked from Admissions page</t>
         </is>
       </c>
-      <c r="F65" s="21" t="inlineStr">
-        <is>
-          <t>Footnote markers in the preparatory maths table point to the wrong colleges.</t>
-        </is>
-      </c>
       <c r="G65" s="21" t="inlineStr">
         <is>
-          <t>"College of Engineering*", "College of Architecture &amp; Design*" but "* Department of Information Technology is excluded from PRPM 0022"; "College of Computer Engineering &amp; Science**" but "** Department of Architecture is excluded from PRPM 0012"</t>
+          <t>Arabic spelling errors on the admission query form and /apply (e.g. 'الأسم', 'الإستفسار', 'الإللكتروني', 'نسب الموزونة').</t>
         </is>
       </c>
       <c r="H65" s="21" t="inlineStr">
         <is>
-          <t>Re-link each footnote to the correct row.</t>
+          <t>"Name [الأسم]"; "Query [الإستفسار]"; "إستفساراتكم"; "Email [البريد الإللكتروني]"; "نسب الموزونة"</t>
         </is>
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
-          <t>PREP + Web</t>
+          <t>Correct to 'الاسم', 'الاستفسار', 'الإلكتروني', 'النسب الموزونة'.</t>
         </is>
       </c>
       <c r="J65" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Web</t>
+        </is>
+      </c>
+      <c r="K65" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4932,7 @@
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>F-17</t>
+          <t>F-27</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
@@ -4100,37 +4942,47 @@
       </c>
       <c r="D66" s="23" t="inlineStr">
         <is>
-          <t>freshman_admission (orphan)</t>
+          <t>Fees &amp; VAT</t>
         </is>
       </c>
       <c r="E66" s="23" t="inlineStr">
         <is>
+          <t>payment_schedule_tf_ro_fall; faq_tf_ro</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F66" s="23" t="inlineStr">
-        <is>
-          <t>Legacy page 'freshman_admission' (not linked from the hub) still shows old weights (30/50/20) and exemptions.</t>
-        </is>
-      </c>
       <c r="G66" s="23" t="inlineStr">
         <is>
-          <t>"High school 30% / Aptitude Test 50% / Personal Interview 20%"; "TOEFL … 513 (CBT 183, iBT 65)"</t>
+          <t>Payment schedule and fees FAQ still show 2025/26 fees.</t>
         </is>
       </c>
       <c r="H66" s="23" t="inlineStr">
         <is>
-          <t>Redirect or unpublish.</t>
+          <t>10,000+10,000+9,000=29,000 vs 2026/27 "SAR 30,000 / semester"</t>
         </is>
       </c>
       <c r="I66" s="23" t="inlineStr">
         <is>
-          <t>Admissions + Web</t>
+          <t>Update or archive.</t>
         </is>
       </c>
       <c r="J66" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="K66" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L66" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4992,7 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>F-27</t>
+          <t>F-17</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
@@ -4150,37 +5002,47 @@
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>payment_schedule_tf_ro_fall; faq_tf_ro</t>
+          <t>Eligibility &amp; admission criteria</t>
         </is>
       </c>
       <c r="E67" s="21" t="inlineStr">
         <is>
+          <t>freshman_admission (orphan)</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F67" s="21" t="inlineStr">
-        <is>
-          <t>Payment schedule and fees FAQ still show 2025/26 fees.</t>
-        </is>
-      </c>
       <c r="G67" s="21" t="inlineStr">
         <is>
-          <t>10,000+10,000+9,000=29,000 vs 2026/27 "SAR 30,000 / semester"</t>
+          <t>Legacy page 'freshman_admission' (not linked from the hub) still shows old weights (30/50/20) and exemptions.</t>
         </is>
       </c>
       <c r="H67" s="21" t="inlineStr">
         <is>
-          <t>Update or archive.</t>
+          <t>"High school 30% / Aptitude Test 50% / Personal Interview 20%"; "TOEFL … 513 (CBT 183, iBT 65)"</t>
         </is>
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Redirect or unpublish.</t>
         </is>
       </c>
       <c r="J67" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Web</t>
+        </is>
+      </c>
+      <c r="K67" s="20" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4190,7 +5052,7 @@
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>F-05</t>
+          <t>F-28</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
@@ -4200,37 +5062,47 @@
       </c>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t>transfer-student-admission (orphan)</t>
+          <t>Fees &amp; VAT</t>
         </is>
       </c>
       <c r="E68" s="23" t="inlineStr">
         <is>
+          <t>payment_method_tf_ro</t>
+        </is>
+      </c>
+      <c r="F68" s="23" t="inlineStr">
+        <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F68" s="23" t="inlineStr">
-        <is>
-          <t>Legacy transfer page states IELTS 5.0 per skill.</t>
-        </is>
-      </c>
       <c r="G68" s="23" t="inlineStr">
         <is>
-          <t>"minimum score of 5.0 on each test component"</t>
+          <t>Refund policy statements contradict on the payment method page.</t>
         </is>
       </c>
       <c r="H68" s="23" t="inlineStr">
         <is>
-          <t>Redirect or unpublish.</t>
+          <t>"All tuition payments are non-refundable." + 25%/50%/75% deductions</t>
         </is>
       </c>
       <c r="I68" s="23" t="inlineStr">
         <is>
-          <t>Admissions + Web</t>
+          <t>Clarify.</t>
         </is>
       </c>
       <c r="J68" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="K68" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L68" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4240,7 +5112,7 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>F-09</t>
+          <t>F-05</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -4250,37 +5122,47 @@
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>ielts_course (orphan)</t>
+          <t>English language tests</t>
         </is>
       </c>
       <c r="E69" s="21" t="inlineStr">
         <is>
+          <t>transfer-student-admission (orphan)</t>
+        </is>
+      </c>
+      <c r="F69" s="21" t="inlineStr">
+        <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F69" s="21" t="inlineStr">
-        <is>
-          <t>2019 IELTS course page still online.</t>
-        </is>
-      </c>
       <c r="G69" s="21" t="inlineStr">
         <is>
-          <t>"From July 14, 2019 to August 02, 2019"</t>
+          <t>Legacy transfer page states IELTS 5.0 per skill.</t>
         </is>
       </c>
       <c r="H69" s="21" t="inlineStr">
         <is>
-          <t>Archive.</t>
+          <t>"minimum score of 5.0 on each test component"</t>
         </is>
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Redirect or unpublish.</t>
         </is>
       </c>
       <c r="J69" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Admissions + Web</t>
+        </is>
+      </c>
+      <c r="K69" s="20" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L69" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4290,7 +5172,7 @@
       </c>
       <c r="B70" s="22" t="inlineStr">
         <is>
-          <t>F-21</t>
+          <t>F-09</t>
         </is>
       </c>
       <c r="C70" s="22" t="inlineStr">
@@ -4300,37 +5182,47 @@
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>next-steps</t>
+          <t>English language tests</t>
         </is>
       </c>
       <c r="E70" s="23" t="inlineStr">
         <is>
+          <t>ielts_course (orphan)</t>
+        </is>
+      </c>
+      <c r="F70" s="23" t="inlineStr">
+        <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F70" s="23" t="inlineStr">
-        <is>
-          <t>'Next steps' page scrolls horizontally on mobile (440 &gt; 390 px).</t>
-        </is>
-      </c>
       <c r="G70" s="23" t="inlineStr">
         <is>
-          <t>scrollWidth 440 vs 390</t>
+          <t>2019 IELTS course page still online.</t>
         </is>
       </c>
       <c r="H70" s="23" t="inlineStr">
         <is>
-          <t>Fix layout.</t>
+          <t>"From July 14, 2019 to August 02, 2019"</t>
         </is>
       </c>
       <c r="I70" s="23" t="inlineStr">
         <is>
-          <t>Web / IT</t>
+          <t>Archive.</t>
         </is>
       </c>
       <c r="J70" s="23" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="K70" s="22" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L70" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4340,7 +5232,7 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>F-28</t>
+          <t>F-21</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
@@ -4350,37 +5242,47 @@
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>payment_method_tf_ro</t>
+          <t>Wording, accessibility &amp; web quality</t>
         </is>
       </c>
       <c r="E71" s="21" t="inlineStr">
         <is>
+          <t>next-steps</t>
+        </is>
+      </c>
+      <c r="F71" s="21" t="inlineStr">
+        <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F71" s="21" t="inlineStr">
-        <is>
-          <t>Refund policy statements contradict on the payment method page.</t>
-        </is>
-      </c>
       <c r="G71" s="21" t="inlineStr">
         <is>
-          <t>"All tuition payments are non-refundable." + 25%/50%/75% deductions</t>
+          <t>'Next steps' page scrolls horizontally on mobile (440 &gt; 390 px).</t>
         </is>
       </c>
       <c r="H71" s="21" t="inlineStr">
         <is>
-          <t>Clarify.</t>
+          <t>scrollWidth 440 vs 390</t>
         </is>
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Fix layout.</t>
         </is>
       </c>
       <c r="J71" s="21" t="inlineStr">
         <is>
-          <t>Open – awaiting owner decision</t>
+          <t>Web / IT</t>
+        </is>
+      </c>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4400,37 +5302,47 @@
       </c>
       <c r="D72" s="23" t="inlineStr">
         <is>
+          <t>Wording, accessibility &amp; web quality</t>
+        </is>
+      </c>
+      <c r="E72" s="23" t="inlineStr">
+        <is>
           <t>sidebar targets (scholarships, GPA calculator)</t>
         </is>
       </c>
-      <c r="E72" s="23" t="inlineStr">
+      <c r="F72" s="23" t="inlineStr">
         <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="G72" s="23" t="inlineStr">
         <is>
           <t>Four sidebar links return 404; financial aid page empty.</t>
         </is>
       </c>
-      <c r="G72" s="23" t="inlineStr">
+      <c r="H72" s="23" t="inlineStr">
         <is>
           <t>404 - File or directory not found</t>
         </is>
       </c>
-      <c r="H72" s="23" t="inlineStr">
+      <c r="I72" s="23" t="inlineStr">
         <is>
           <t>Fix links.</t>
         </is>
       </c>
-      <c r="I72" s="23" t="inlineStr">
+      <c r="J72" s="23" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="J72" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K72" s="22" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L72" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4450,37 +5362,47 @@
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
+          <t>Wording, accessibility &amp; web quality</t>
+        </is>
+      </c>
+      <c r="E73" s="21" t="inlineStr">
+        <is>
           <t>news/2010; news?ID=1115</t>
         </is>
       </c>
-      <c r="E73" s="21" t="inlineStr">
+      <c r="F73" s="21" t="inlineStr">
         <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F73" s="21" t="inlineStr">
+      <c r="G73" s="21" t="inlineStr">
         <is>
           <t>Old news items (2010, 1435/1436H) still reachable.</t>
         </is>
       </c>
-      <c r="G73" s="21" t="inlineStr">
+      <c r="H73" s="21" t="inlineStr">
         <is>
           <t>"العام الجامعي 1436/1435هـ"</t>
         </is>
       </c>
-      <c r="H73" s="21" t="inlineStr">
+      <c r="I73" s="21" t="inlineStr">
         <is>
           <t>Archive.</t>
         </is>
       </c>
-      <c r="I73" s="21" t="inlineStr">
+      <c r="J73" s="21" t="inlineStr">
         <is>
           <t>Web</t>
         </is>
       </c>
-      <c r="J73" s="21" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K73" s="20" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4500,37 +5422,47 @@
       </c>
       <c r="D74" s="23" t="inlineStr">
         <is>
+          <t>Wording, accessibility &amp; web quality</t>
+        </is>
+      </c>
+      <c r="E74" s="23" t="inlineStr">
+        <is>
           <t>13 academic calendars; PDFs</t>
         </is>
       </c>
-      <c r="E74" s="23" t="inlineStr">
+      <c r="F74" s="23" t="inlineStr">
         <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F74" s="23" t="inlineStr">
+      <c r="G74" s="23" t="inlineStr">
         <is>
           <t>13 generations of academic calendars and old PDFs online.</t>
         </is>
       </c>
-      <c r="G74" s="23" t="inlineStr">
+      <c r="H74" s="23" t="inlineStr">
         <is>
           <t>calendars 2014/15→2026/27; Aptis guide PDF created 2017</t>
         </is>
       </c>
-      <c r="H74" s="23" t="inlineStr">
+      <c r="I74" s="23" t="inlineStr">
         <is>
           <t>Archive.</t>
         </is>
       </c>
-      <c r="I74" s="23" t="inlineStr">
+      <c r="J74" s="23" t="inlineStr">
         <is>
           <t>Registrar + Web</t>
         </is>
       </c>
-      <c r="J74" s="23" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K74" s="22" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="L74" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4550,42 +5482,52 @@
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
+          <t>Wording, accessibility &amp; web quality</t>
+        </is>
+      </c>
+      <c r="E75" s="21" t="inlineStr">
+        <is>
           <t>registration_office</t>
         </is>
       </c>
-      <c r="E75" s="21" t="inlineStr">
+      <c r="F75" s="21" t="inlineStr">
         <is>
           <t>Legacy page (not linked from hub)</t>
         </is>
       </c>
-      <c r="F75" s="21" t="inlineStr">
+      <c r="G75" s="21" t="inlineStr">
         <is>
           <t>Link to an internal host (http://web1:8066/...) on a public page.</t>
         </is>
       </c>
-      <c r="G75" s="21" t="inlineStr">
+      <c r="H75" s="21" t="inlineStr">
         <is>
           <t>http://web1:8066/Online_Room_Reservation_Form.aspx</t>
         </is>
       </c>
-      <c r="H75" s="21" t="inlineStr">
+      <c r="I75" s="21" t="inlineStr">
         <is>
           <t>Remove.</t>
         </is>
       </c>
-      <c r="I75" s="21" t="inlineStr">
+      <c r="J75" s="21" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="J75" s="21" t="inlineStr">
-        <is>
-          <t>Open – awaiting owner decision</t>
+      <c r="K75" s="20" t="inlineStr">
+        <is>
+          <t>No – direct correction</t>
+        </is>
+      </c>
+      <c r="L75" s="20" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J75"/>
+  <autoFilter ref="A4:L75"/>
   <conditionalFormatting sqref="C5:C75">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="P1"</formula>
@@ -4719,7 +5661,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>Admissions Office</t>
+          <t>Admissions Office page</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -4744,7 +5686,7 @@
       </c>
       <c r="I5" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P00.txt: "ADMISSIONS OFFICE | Future Students | Overview | Degrees &amp; Programs | ... Scholastic Aptitude Test (SAT) | STAY CONNECTED"</t>
+          <t>"ADMISSIONS OFFICE | Future Students | Overview | Degrees &amp; Programs | ... Scholastic Aptitude Test (SAT) | STAY CONNECTED"</t>
         </is>
       </c>
     </row>
@@ -4764,7 +5706,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Admissions Office</t>
+          <t>Admissions Office page</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -4789,7 +5731,7 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>admission_page_dom.json: 'Admissions to the MIBL' -&gt; ../Admission/Admissions_Requirements_MIlBL_GDP.aspx; P21.txt: "Admissions to the Master of Arts (MA) in International Business Law Program"</t>
+          <t>'Admissions to the MIBL' -&gt; ../Admission/Admissions_Requirements_MIlBL_GDP.aspx; "Admissions to the Master of Arts (MA) in International Business Law Program"</t>
         </is>
       </c>
     </row>
@@ -4809,7 +5751,7 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>Admissions Office</t>
+          <t>Admissions Office page</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -4834,7 +5776,7 @@
       </c>
       <c r="I7" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P00.txt: "Admission to the College of Medicine" vs "Admissions to the Preparatory Program", "Admissions from Other Universities"</t>
+          <t>"Admission to the College of Medicine" vs "Admissions to the Preparatory Program", "Admissions from Other Universities"</t>
         </is>
       </c>
     </row>
@@ -4854,7 +5796,7 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Admissions Office</t>
+          <t>Admissions Office page</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -4879,7 +5821,7 @@
       </c>
       <c r="I8" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P00.txt: "Visting Students"</t>
+          <t>"Visting Students"</t>
         </is>
       </c>
     </row>
@@ -4899,7 +5841,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>Admissions Office</t>
+          <t>Admissions Office page</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -4924,7 +5866,7 @@
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P22.txt: "Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000 | SAR 80,000"; no such entry in P00.txt Graduate Admissions list</t>
+          <t>"Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000 | SAR 80,000"; no such entry in Graduate Admissions list</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5886,7 @@
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Study @ PMU</t>
+          <t>Study @ PMU page</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4969,7 +5911,7 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>register.json: "url": ".../academic_calendar_2023_2024_ro" "foundOn": ".../admission/admission-registration" title "Academic Year 2023/2024"</t>
+          <t>"url": ".../academic_calendar_2023_2024_ro" "foundOn": ".../admission/admission-registration" title "Academic Year 2023/2024"</t>
         </is>
       </c>
     </row>
@@ -4989,7 +5931,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>Study @ PMU</t>
+          <t>Study @ PMU page</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -5014,7 +5956,7 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P02.txt: "STUDY AT PMU | Previous | Next | Admissions Office | Home | Future Students ..." (no 'Apply' text)</t>
+          <t>"STUDY AT PMU | Previous | Next | Admissions Office | Home | Future Students ..." (no 'Apply' text)</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5976,7 @@
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Study @ PMU</t>
+          <t>Study @ PMU page</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -5059,7 +6001,7 @@
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P02.txt: "Student Registration- Quick Guide"</t>
+          <t>"Student Registration- Quick Guide"</t>
         </is>
       </c>
     </row>
@@ -5079,7 +6021,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Future Students overview</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -5104,7 +6046,7 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P03.txt: "When you are looking for an institution that not only provides you with a degree in a competent subject, but also prepares you ... wherever you go."</t>
+          <t>"When you are looking for an institution that not only provides you with a degree in a competent subject, but also prepares you ... wherever you go."</t>
         </is>
       </c>
     </row>
@@ -5124,7 +6066,7 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Future Students overview</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -5149,7 +6091,7 @@
       </c>
       <c r="I14" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_future_students_ro.txt: "We offer different programs accredited by prestigious national and international organizations."</t>
+          <t>"We offer different programs accredited by prestigious national and international organizations."</t>
         </is>
       </c>
     </row>
@@ -5169,7 +6111,7 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>Future Students overview</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -5194,7 +6136,7 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_future_students_ro.txt: "To explore the opportunities and the admission requirements more please visit the below links:"</t>
+          <t>"To explore the opportunities and the admission requirements more please visit the below links:"</t>
         </is>
       </c>
     </row>
@@ -5214,7 +6156,7 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Degrees &amp; Programs</t>
+          <t>Degrees &amp; Programs page</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -5239,7 +6181,7 @@
       </c>
       <c r="I16" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_degrees_programs_fs_ro.txt: Undergraduate Programs list ends "College of Law | Degree Program | B.A. in Law | Graduate Programs" (no Medicine); P24.txt: "College of Medical curriculum is based on a 7-year hybrid model"</t>
+          <t>Undergraduate Programs list ends "College of Law | Degree Program | B.A. in Law | Graduate Programs" (no Medicine); "College of Medical curriculum is based on a 7-year hybrid model"</t>
         </is>
       </c>
     </row>
@@ -5259,7 +6201,7 @@
       </c>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t>Degrees &amp; Programs</t>
+          <t>Degrees &amp; Programs page</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -5284,7 +6226,7 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_degrees_programs_fs_ro.txt Graduate Programs: no 'Engineering Management' entry; P00.txt: "Admissions to the EMGMS Program"; P22.txt: "Master of Science in Engineering Management (30) | SAR 80,000"</t>
+          <t>Graduate Programs: no 'Engineering Management' entry; "Admissions to the EMGMS Program"; "Master of Science in Engineering Management (30) | SAR 80,000"</t>
         </is>
       </c>
     </row>
@@ -5304,7 +6246,7 @@
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Degrees &amp; Programs</t>
+          <t>Degrees &amp; Programs page</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -5329,7 +6271,7 @@
       </c>
       <c r="I18" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_degrees_programs_fs_ro.txt: "PhD. in Mechanical Engineering", "PhD. in Business Administration"; P22.txt: "Doctor of Philosophy (Ph.D.)"</t>
+          <t>"PhD. in Mechanical Engineering", "PhD. in Business Administration"; "Doctor of Philosophy (Ph.D.)"</t>
         </is>
       </c>
     </row>
@@ -5349,7 +6291,7 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>Degrees &amp; Programs</t>
+          <t>Degrees &amp; Programs page</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -5374,7 +6316,7 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_degrees_programs_fs_ro.txt: "Executive Master in Business Administration (EMBA)" / "Masters in Business Administration (MBA)"</t>
+          <t>"Executive Master in Business Administration (EMBA)" / "Masters in Business Administration (MBA)"</t>
         </is>
       </c>
     </row>
@@ -5394,7 +6336,7 @@
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Degrees &amp; Programs</t>
+          <t>Degrees &amp; Programs page</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -5419,7 +6361,7 @@
       </c>
       <c r="I20" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_degrees_programs_fs_ro.txt: "College of Computer Engineering and Science"; P07.txt footer: "College of Computer Engineering &amp; Sciences"</t>
+          <t>"College of Computer Engineering and Science"; footer: "College of Computer Engineering &amp; Sciences"</t>
         </is>
       </c>
     </row>
@@ -5439,7 +6381,7 @@
       </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
-          <t>Admissions Calendar</t>
+          <t>Admission Calendar</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -5464,7 +6406,7 @@
       </c>
       <c r="I21" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P05.txt: "Last day to submit IELTS or TOEFL iBT | 2026-07-20", "Last day for Transfer applicants to submit documents in person | 2026-07-20", "Announcement of admission results through Qabool platform | From July 19 to July 21, 2026"</t>
+          <t>"Last day to submit IELTS or TOEFL iBT | 2026-07-20", "Last day for Transfer applicants to submit documents in person | 2026-07-20", "Announcement of admission results through Qabool platform | From July 19 to July 21, 2026"</t>
         </is>
       </c>
     </row>
@@ -5484,7 +6426,7 @@
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>Admissions Calendar</t>
+          <t>Admission Calendar</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -5509,7 +6451,7 @@
       </c>
       <c r="I22" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P05.txt: "First day of classes | 2026-08-30", "Orientation for new applicants | TBA"</t>
+          <t>"First day of classes | 2026-08-30", "Orientation for new applicants | TBA"</t>
         </is>
       </c>
     </row>
@@ -5529,7 +6471,7 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>Admissions Calendar</t>
+          <t>Admission Calendar</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -5554,7 +6496,7 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_admission_calendar_fs_ro.txt: second 'Fall 2026-2027 Undergraduate Admission Calendar' block with "First day of classes 2026-08-30 / For non Saudi Students: ... Closed"; rendered/pages/P05.txt shows each table once</t>
+          <t>second 'Fall 2026-2027 Undergraduate Admission Calendar' block with "First day of classes 2026-08-30 / For non Saudi Students: ... Closed"; shows each table once</t>
         </is>
       </c>
     </row>
@@ -5574,7 +6516,7 @@
       </c>
       <c r="D24" s="23" t="inlineStr">
         <is>
-          <t>Admissions Calendar</t>
+          <t>Admission Calendar</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -5599,7 +6541,7 @@
       </c>
       <c r="I24" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P05.txt: "For non Saudi Students: Apply online through Study in Saudi platform"</t>
+          <t>"For non Saudi Students: Apply online through Study in Saudi platform"</t>
         </is>
       </c>
     </row>
@@ -5619,7 +6561,7 @@
       </c>
       <c r="D25" s="21" t="inlineStr">
         <is>
-          <t>Admissions Calendar</t>
+          <t>Admission Calendar</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -5644,7 +6586,7 @@
       </c>
       <c r="I25" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P05.txt: "Start of English Placement Test and personal Interviews | 2026-05-17"</t>
+          <t>"Start of English Placement Test and personal Interviews | 2026-05-17"</t>
         </is>
       </c>
     </row>
@@ -5664,7 +6606,7 @@
       </c>
       <c r="D26" s="23" t="inlineStr">
         <is>
-          <t>Admissions Calendar</t>
+          <t>Admission Calendar</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -5689,7 +6631,7 @@
       </c>
       <c r="I26" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P05.txt: "Announcement of admission results through Qabool platform | From July 19 to July 21, 2026"; "For non Saudi Students: ... Study in Saudi platform ... | Closed"</t>
+          <t>"Announcement of admission results through Qabool platform | From July 19 to July 21, 2026"; "For non Saudi Students: ... Study in Saudi platform ... | Closed"</t>
         </is>
       </c>
     </row>
@@ -5709,7 +6651,7 @@
       </c>
       <c r="D27" s="21" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -5734,7 +6676,7 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "Enter Verifaction Code[أدخل رمز التحقق]:*"</t>
+          <t>"Enter Verifaction Code[أدخل رمز التحقق]:*"</t>
         </is>
       </c>
     </row>
@@ -5754,7 +6696,7 @@
       </c>
       <c r="D28" s="23" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -5779,7 +6721,7 @@
       </c>
       <c r="I28" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "Name [الأسم]: *"</t>
+          <t>"Name [الأسم]: *"</t>
         </is>
       </c>
     </row>
@@ -5799,7 +6741,7 @@
       </c>
       <c r="D29" s="21" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -5824,7 +6766,7 @@
       </c>
       <c r="I29" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "على إستفساراتكم" ; "Query [الإستفسار]:*"</t>
+          <t>"على إستفساراتكم" ; "Query [الإستفسار]:*"</t>
         </is>
       </c>
     </row>
@@ -5844,7 +6786,7 @@
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -5869,7 +6811,7 @@
       </c>
       <c r="I30" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "Email [البريد الإللكتروني] | Mobile [جوال]" vs "Email [البريد الإلكتروني]:*"</t>
+          <t>"Email [البريد الإللكتروني] | Mobile [جوال]" vs "Email [البريد الإلكتروني]:*"</t>
         </is>
       </c>
     </row>
@@ -5889,7 +6831,7 @@
       </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -5914,7 +6856,7 @@
       </c>
       <c r="I31" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: ":مرحباً بكم بجامعة الأمير محمد بن فهد، مكتب القبول يسعد بالإجابة على إستفساراتكم. الرجاء ملء الطلب أدناه"</t>
+          <t>":مرحباً بكم بجامعة الأمير محمد بن فهد، مكتب القبول يسعد بالإجابة على إستفساراتكم. الرجاء ملء الطلب أدناه"</t>
         </is>
       </c>
     </row>
@@ -5934,7 +6876,7 @@
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -5959,7 +6901,7 @@
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "Please fill the below request:"</t>
+          <t>"Please fill the below request:"</t>
         </is>
       </c>
     </row>
@@ -5979,7 +6921,7 @@
       </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -6004,7 +6946,7 @@
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "Verification Code[رمز التحقق]:*" / "Enter Verifaction Code[أدخل رمز التحقق]:*"</t>
+          <t>"Verification Code[رمز التحقق]:*" / "Enter Verifaction Code[أدخل رمز التحقق]:*"</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6966,7 @@
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>Admission Query</t>
+          <t>Admission Query page</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -6049,7 +6991,7 @@
       </c>
       <c r="I34" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P07.txt: "ADMISSION QUERY | Welcome to PMU, the Admissions Office is glad to answer your inquiries ... Enter Verifaction Code[أدخل رمز التحقق]:* | STAY CONNECTED"</t>
+          <t>"ADMISSION QUERY | Welcome to PMU, the Admissions Office is glad to answer your inquiries ... Enter Verifaction Code[أدخل رمز التحقق]:* | STAY CONNECTED"</t>
         </is>
       </c>
     </row>
@@ -6069,7 +7011,7 @@
       </c>
       <c r="D35" s="21" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -6094,7 +7036,7 @@
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "Bachelor’s Programs — Admission Requirements" ... "A non-refundable application fee of SAR 950 must be paid"; P25.txt: "Pay a non-refundable application fee of SAR 1000 (incl. VAT)", "(SAT 1) 1300"</t>
+          <t>"Bachelor’s Programs — Admission Requirements" ... "A non-refundable application fee of SAR 950 must be paid"; "Pay a non-refundable application fee of SAR 1000 (incl. VAT)", "(SAT 1) 1300"</t>
         </is>
       </c>
     </row>
@@ -6114,7 +7056,7 @@
       </c>
       <c r="D36" s="23" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -6139,7 +7081,7 @@
       </c>
       <c r="I36" s="23" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "A non-refundable application fee of SAR 950 must be paid to complete the admission process."; P24.txt: "SAR 950 (incl. VAT)"; pages/admission_international_students.txt: "SAR 500 (excl. VAT)"</t>
+          <t>"A non-refundable application fee of SAR 950 must be paid to complete the admission process."; "SAR 950 (incl. VAT)"; "SAR 500 (excl. VAT)"</t>
         </is>
       </c>
     </row>
@@ -6159,7 +7101,7 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E37" s="20" t="inlineStr">
@@ -6184,7 +7126,7 @@
       </c>
       <c r="I37" s="21" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "Qudrat 60% or equivalent SAT 1 score" vs "Alternatively, a SAT 1 total score of 1200 is accepted"</t>
+          <t>"Qudrat 60% or equivalent SAT 1 score" vs "Alternatively, a SAT 1 total score of 1200 is accepted"</t>
         </is>
       </c>
     </row>
@@ -6204,7 +7146,7 @@
       </c>
       <c r="D38" s="23" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -6229,7 +7171,7 @@
       </c>
       <c r="I38" s="23" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "* Students with a lower percentage can apply; however, acceptance will depend on the overall weight." (only under AI/Engineering); P24.txt: "*Students with a lower percentage can apply" under General requirements</t>
+          <t>"* Students with a lower percentage can apply; however, acceptance will depend on the overall weight." (only under AI/Engineering); "*Students with a lower percentage can apply" under General requirements</t>
         </is>
       </c>
     </row>
@@ -6249,7 +7191,7 @@
       </c>
       <c r="D39" s="21" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E39" s="20" t="inlineStr">
@@ -6274,7 +7216,7 @@
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "نسب الموزونة" (appears twice)</t>
+          <t>"نسب الموزونة" (appears twice)</t>
         </is>
       </c>
     </row>
@@ -6294,7 +7236,7 @@
       </c>
       <c r="D40" s="23" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
@@ -6319,7 +7261,7 @@
       </c>
       <c r="I40" s="23" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_source.html: "القدرات / &lt;span dir=\"ltr\"&gt;1 SAT&lt;/span&gt;" vs "القدرات / SAT 1"</t>
+          <t>"القدرات / &lt;span dir=\"ltr\"&gt;1 SAT&lt;/span&gt;" vs "القدرات / SAT 1"</t>
         </is>
       </c>
     </row>
@@ -6339,7 +7281,7 @@
       </c>
       <c r="D41" s="21" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E41" s="20" t="inlineStr">
@@ -6364,7 +7306,7 @@
       </c>
       <c r="I41" s="21" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "ملاحظة: لا يُقبل اختبار النسخة المنزلية." vs "Note: TOEFL Home Edition is not accepted."</t>
+          <t>"ملاحظة: لا يُقبل اختبار النسخة المنزلية." vs "Note: TOEFL Home Edition is not accepted."</t>
         </is>
       </c>
     </row>
@@ -6384,7 +7326,7 @@
       </c>
       <c r="D42" s="23" t="inlineStr">
         <is>
-          <t>Apply Now</t>
+          <t>/apply page</t>
         </is>
       </c>
       <c r="E42" s="22" t="inlineStr">
@@ -6409,7 +7351,7 @@
       </c>
       <c r="I42" s="23" t="inlineStr">
         <is>
-          <t>pages_v5/apply_raw_text.txt: "Have the certificate stamped by the Saudi Embassy in their country" vs P24.txt: "attested, in advance, by the Saudi Consulate and other authorized organizations"</t>
+          <t>"Have the certificate stamped by the Saudi Embassy in their country" vs "attested, in advance, by the Saudi Consulate and other authorized organizations"</t>
         </is>
       </c>
     </row>
@@ -6429,7 +7371,7 @@
       </c>
       <c r="D43" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
@@ -6449,12 +7391,12 @@
       </c>
       <c r="H43" s="21" t="inlineStr">
         <is>
-          <t>Rename the group to match P31/P37 (AI, Computer Science, Architecture and Engineering majors) and list the majors in each group.</t>
+          <t>Rename the group to match the CS &amp; Engineering Requirements page/the SAT page (AI, Computer Science, Architecture and Engineering majors) and list the majors in each group.</t>
         </is>
       </c>
       <c r="I43" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Non-Engineering Majors: Secondary School 60% SAT I 40% Computer Science &amp; Engineering Majors:"; P31.txt: "These majors are Architecture, Computer Science, ... Civil Engineering"</t>
+          <t>"Non-Engineering Majors: Secondary School 60% SAT I 40% Computer Science &amp; Engineering Majors:"; "These majors are Architecture, Computer Science, ... Civil Engineering"</t>
         </is>
       </c>
     </row>
@@ -6474,7 +7416,7 @@
       </c>
       <c r="D44" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E44" s="22" t="inlineStr">
@@ -6499,7 +7441,7 @@
       </c>
       <c r="I44" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Acceptable SAT I"; P37.txt: "Students with international high school certificate might submit SAT with minimum score of 1200"</t>
+          <t>"Acceptable SAT I"; "Students with international high school certificate might submit SAT with minimum score of 1200"</t>
         </is>
       </c>
     </row>
@@ -6519,7 +7461,7 @@
       </c>
       <c r="D45" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E45" s="20" t="inlineStr">
@@ -6544,7 +7486,7 @@
       </c>
       <c r="I45" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Acceptable secondary school GPA *80% or equivalent"; P31.txt: "HS GPA out of 100 | ≥ 85 | 40% / Qudrat | ≥ 65 | 30% / Tahseely | ≥ 65 | 30%"</t>
+          <t>"Acceptable secondary school GPA *80% or equivalent"; "HS GPA out of 100 | ≥ 85 | 40% / Qudrat | ≥ 65 | 30% / Tahseely | ≥ 65 | 30%"</t>
         </is>
       </c>
     </row>
@@ -6564,7 +7506,7 @@
       </c>
       <c r="D46" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E46" s="22" t="inlineStr">
@@ -6589,7 +7531,7 @@
       </c>
       <c r="I46" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "minimum scores of 6.0 overall and 5.5 in writing or equivalent TOEFL iBT"; pages_v5/apply_raw_text.txt: "TOEFL iBT: Overall 83, Writing 19"</t>
+          <t>"minimum scores of 6.0 overall and 5.5 in writing or equivalent TOEFL iBT"; "TOEFL iBT: Overall 83, Writing 19"</t>
         </is>
       </c>
     </row>
@@ -6609,7 +7551,7 @@
       </c>
       <c r="D47" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E47" s="20" t="inlineStr">
@@ -6634,7 +7576,7 @@
       </c>
       <c r="I47" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Graduate Studies MBA MSHD MSME"; P10.txt lists 10 programmes plus EMGMS on P00</t>
+          <t>"Graduate Studies MBA MSHD MSME"; lists 10 programmes plus EMGMS on Admissions Office page</t>
         </is>
       </c>
     </row>
@@ -6654,7 +7596,7 @@
       </c>
       <c r="D48" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E48" s="22" t="inlineStr">
@@ -6679,7 +7621,7 @@
       </c>
       <c r="I48" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Transportation\n Transportation\n Campus Life\n Campus Life"</t>
+          <t>"Transportation\n Transportation\n Campus Life\n Campus Life"</t>
         </is>
       </c>
     </row>
@@ -6699,7 +7641,7 @@
       </c>
       <c r="D49" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E49" s="20" t="inlineStr">
@@ -6724,7 +7666,7 @@
       </c>
       <c r="I49" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt contains no email/phone; only CTA 'Contact' -&gt; https://www.pmu.edu.sa/About/Contact_Us.aspx (browser/result2_mobile_probes.json)</t>
+          <t>No email address or phone number on the page; the only contact link is "Contact" → https://www.pmu.edu.sa/About/Contact_Us.aspx</t>
         </is>
       </c>
     </row>
@@ -6744,7 +7686,7 @@
       </c>
       <c r="D50" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E50" s="22" t="inlineStr">
@@ -6769,7 +7711,7 @@
       </c>
       <c r="I50" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Copy of National ID\n Copy of passport"</t>
+          <t>"Copy of National ID\n Copy of passport"</t>
         </is>
       </c>
     </row>
@@ -6789,7 +7731,7 @@
       </c>
       <c r="D51" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E51" s="20" t="inlineStr">
@@ -6814,7 +7756,7 @@
       </c>
       <c r="I51" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "The total GPA is 2.0 out of 4.0 from the previous institution"</t>
+          <t>"The total GPA is 2.0 out of 4.0 from the previous institution"</t>
         </is>
       </c>
     </row>
@@ -6834,7 +7776,7 @@
       </c>
       <c r="D52" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E52" s="22" t="inlineStr">
@@ -6859,7 +7801,7 @@
       </c>
       <c r="I52" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "In order to be consider as a transfer candidate"</t>
+          <t>"In order to be consider as a transfer candidate"</t>
         </is>
       </c>
     </row>
@@ -6879,7 +7821,7 @@
       </c>
       <c r="D53" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E53" s="20" t="inlineStr">
@@ -6904,7 +7846,7 @@
       </c>
       <c r="I53" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "acceptable scores (if available) or For direct entry, submit original IELTS (Academic version) certificate"</t>
+          <t>"acceptable scores (if available) or For direct entry, submit original IELTS (Academic version) certificate"</t>
         </is>
       </c>
     </row>
@@ -6924,7 +7866,7 @@
       </c>
       <c r="D54" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E54" s="22" t="inlineStr">
@@ -6949,7 +7891,7 @@
       </c>
       <c r="I54" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Acceptable SAT I" ... "Copy of SAT 1 - if available"</t>
+          <t>"Acceptable SAT I" ... "Copy of SAT 1 - if available"</t>
         </is>
       </c>
     </row>
@@ -6969,7 +7911,7 @@
       </c>
       <c r="D55" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E55" s="20" t="inlineStr">
@@ -6994,7 +7936,7 @@
       </c>
       <c r="I55" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "From choosing a program to applying to accept Admission Offer to issuing student visa to housing to start the study"</t>
+          <t>"From choosing a program to applying to accept Admission Offer to issuing student visa to housing to start the study"</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7956,7 @@
       </c>
       <c r="D56" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E56" s="22" t="inlineStr">
@@ -7039,7 +7981,7 @@
       </c>
       <c r="I56" s="23" t="inlineStr">
         <is>
-          <t>P09.txt: "International Students' Office &gt; International Students without Saudi residence" then heading "International Students without Saudi Residence"</t>
+          <t>"International Students' Office &gt; International Students without Saudi residence" then heading "International Students without Saudi Residence"</t>
         </is>
       </c>
     </row>
@@ -7059,7 +8001,7 @@
       </c>
       <c r="D57" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E57" s="20" t="inlineStr">
@@ -7084,7 +8026,7 @@
       </c>
       <c r="I57" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "various academic support elements will be located in the residence halls for the convenience of students"</t>
+          <t>"various academic support elements will be located in the residence halls for the convenience of students"</t>
         </is>
       </c>
     </row>
@@ -7104,7 +8046,7 @@
       </c>
       <c r="D58" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E58" s="22" t="inlineStr">
@@ -7129,7 +8071,7 @@
       </c>
       <c r="I58" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Curriculum (TIEC)"</t>
+          <t>"Curriculum (TIEC)"</t>
         </is>
       </c>
     </row>
@@ -7149,7 +8091,7 @@
       </c>
       <c r="D59" s="21" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E59" s="20" t="inlineStr">
@@ -7174,7 +8116,7 @@
       </c>
       <c r="I59" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Life @ pmu"</t>
+          <t>"Life @ pmu"</t>
         </is>
       </c>
     </row>
@@ -7194,7 +8136,7 @@
       </c>
       <c r="D60" s="23" t="inlineStr">
         <is>
-          <t>International Students without Saudi Residence</t>
+          <t>International Students page</t>
         </is>
       </c>
       <c r="E60" s="22" t="inlineStr">
@@ -7219,7 +8161,7 @@
       </c>
       <c r="I60" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_international_students.txt: "Issuing IQAMA" ... "All registration’s functions"</t>
+          <t>"Issuing IQAMA" ... "All registration’s functions"</t>
         </is>
       </c>
     </row>
@@ -7239,7 +8181,7 @@
       </c>
       <c r="D61" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Graduate Programs page</t>
         </is>
       </c>
       <c r="E61" s="20" t="inlineStr">
@@ -7264,7 +8206,7 @@
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
-          <t>P10.txt lists 10 programmes ending "Admissions to the Master of Arts (MA) in International Business Law Program" (no EMGMS); admission_page_dom.json: "Admissions to the EMGMS Program"; P22.txt: "Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000"</t>
+          <t>lists 10 programmes ending "Admissions to the Master of Arts (MA) in International Business Law Program" (no EMGMS); "Admissions to the EMGMS Program"; "Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000"</t>
         </is>
       </c>
     </row>
@@ -7284,7 +8226,7 @@
       </c>
       <c r="D62" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Graduate Programs page</t>
         </is>
       </c>
       <c r="E62" s="22" t="inlineStr">
@@ -7309,7 +8251,7 @@
       </c>
       <c r="I62" s="23" t="inlineStr">
         <is>
-          <t>browser/result2_mobile_probes.json (P10 hrefs, in order): "...Admissions_Requirements_PHDBA_GDP.aspx", "https://www.pmu.edu.sa/Admission/application_form_gr.aspx", "...Application_Form_DEME_GDP.aspx", "...application_form_msce_gdp.aspx"; P10.txt: unlabeled "Application Form" for PhD ME, MSCE, MSEE, MSID</t>
+          <t>"...Admissions_Requirements_PHDBA_GDP.aspx", "https://www.pmu.edu.sa/Admission/application_form_gr.aspx", "...Application_Form_DEME_GDP.aspx", "...application_form_msce_gdp.aspx"; unlabeled "Application Form" for PhD ME, MSCE, MSEE, MSID</t>
         </is>
       </c>
     </row>
@@ -7329,7 +8271,7 @@
       </c>
       <c r="D63" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Graduate Programs page</t>
         </is>
       </c>
       <c r="E63" s="20" t="inlineStr">
@@ -7354,7 +8296,7 @@
       </c>
       <c r="I63" s="21" t="inlineStr">
         <is>
-          <t>P10.txt: "Admissions to the Doctorate in Mechanical Engineering Program"; P11.txt: "PhD in Mechanical Engineering"; P22.txt: "Doctoral program in Mechanical Engineering (72)"</t>
+          <t>"Admissions to the Doctorate in Mechanical Engineering Program"; "PhD in Mechanical Engineering"; "Doctoral program in Mechanical Engineering (72)"</t>
         </is>
       </c>
     </row>
@@ -7374,7 +8316,7 @@
       </c>
       <c r="D64" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Graduate Programs page</t>
         </is>
       </c>
       <c r="E64" s="22" t="inlineStr">
@@ -7399,7 +8341,7 @@
       </c>
       <c r="I64" s="23" t="inlineStr">
         <is>
-          <t>P10.txt: "Admission to the Master of Human Development"; P15.txt: "Admissions to the Master of Science in Human Development (MSHD) program"</t>
+          <t>"Admission to the Master of Human Development"; "Admissions to the Master of Science in Human Development (MSHD) program"</t>
         </is>
       </c>
     </row>
@@ -7419,7 +8361,7 @@
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Graduate Programs page</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
@@ -7444,7 +8386,7 @@
       </c>
       <c r="I65" s="21" t="inlineStr">
         <is>
-          <t>P10.txt: "Admissions to the PhD in Business Administration" / "Admission to the Executive MBA Program" / "Admission to the MBA"</t>
+          <t>"Admissions to the PhD in Business Administration" / "Admission to the Executive MBA Program" / "Admission to the MBA"</t>
         </is>
       </c>
     </row>
@@ -7464,7 +8406,7 @@
       </c>
       <c r="D66" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Graduate Programs page</t>
         </is>
       </c>
       <c r="E66" s="22" t="inlineStr">
@@ -7489,7 +8431,7 @@
       </c>
       <c r="I66" s="23" t="inlineStr">
         <is>
-          <t>P10 href: "Admission/admissions_Requirements_MILBL_GDP.aspx"; admission_page_dom.json: "Admissions to the MIBL | .../Admissions_Requirements_MIlBL_GDP.aspx"; P21.txt: "MIBL ADMISSSIONS REQUIREMENTS"</t>
+          <t>Graduate Programs page href: "Admission/admissions_Requirements_MILBL_GDP.aspx"; "Admissions to the MIBL | .../Admissions_Requirements_MIlBL_GDP.aspx"; "MIBL ADMISSSIONS REQUIREMENTS"</t>
         </is>
       </c>
     </row>
@@ -7509,7 +8451,7 @@
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Mechanical Engineering Program</t>
+          <t>PhD Mechanical Engineering page</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
@@ -7534,7 +8476,7 @@
       </c>
       <c r="I67" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_application_form_deme_gdp.txt: "TITLE: Application Form for MSDH :: Graduate Degree Programs"; P11.txt heading: "PHD IN MECHANICAL ENGINEERING ADMISSSIONS REQUIREMENTS"</t>
+          <t>"TITLE: Application Form for MSDH :: Graduate Degree Programs"; heading: "PHD IN MECHANICAL ENGINEERING ADMISSSIONS REQUIREMENTS"</t>
         </is>
       </c>
     </row>
@@ -7554,7 +8496,7 @@
       </c>
       <c r="D68" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Mechanical Engineering Program</t>
+          <t>PhD Mechanical Engineering page</t>
         </is>
       </c>
       <c r="E68" s="22" t="inlineStr">
@@ -7579,7 +8521,7 @@
       </c>
       <c r="I68" s="23" t="inlineStr">
         <is>
-          <t>P11.txt: "PhD in Mechanical Engineering ADMISSSIONS REQUIREMENTS"</t>
+          <t>"PhD in Mechanical Engineering ADMISSSIONS REQUIREMENTS"</t>
         </is>
       </c>
     </row>
@@ -7599,7 +8541,7 @@
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Mechanical Engineering Program</t>
+          <t>PhD Mechanical Engineering page</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
@@ -7624,7 +8566,7 @@
       </c>
       <c r="I69" s="21" t="inlineStr">
         <is>
-          <t>P11.txt has no credit hours/duration/apply link; P22.txt: "Doctoral program in Mechanical Engineering (72) | SAR 150,000"</t>
+          <t>has no credit hours/duration/apply link; "Doctoral program in Mechanical Engineering (72) | SAR 150,000"</t>
         </is>
       </c>
     </row>
@@ -7644,7 +8586,7 @@
       </c>
       <c r="D70" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Mechanical Engineering Program</t>
+          <t>PhD Mechanical Engineering page</t>
         </is>
       </c>
       <c r="E70" s="22" t="inlineStr">
@@ -7669,7 +8611,7 @@
       </c>
       <c r="I70" s="23" t="inlineStr">
         <is>
-          <t>P11.txt: "A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)"; P13.txt: "A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good)"</t>
+          <t>"A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)"; "A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good)"</t>
         </is>
       </c>
     </row>
@@ -7689,7 +8631,7 @@
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Mechanical Engineering Program</t>
+          <t>PhD Mechanical Engineering page</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
@@ -7714,7 +8656,7 @@
       </c>
       <c r="I71" s="21" t="inlineStr">
         <is>
-          <t>P11.txt: "widen the horizons of engineer professionals. The PhD program provides employees with the skills"</t>
+          <t>"widen the horizons of engineer professionals. The PhD program provides employees with the skills"</t>
         </is>
       </c>
     </row>
@@ -7734,7 +8676,7 @@
       </c>
       <c r="D72" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Mechanical Engineering Program</t>
+          <t>PhD Mechanical Engineering page</t>
         </is>
       </c>
       <c r="E72" s="22" t="inlineStr">
@@ -7759,7 +8701,7 @@
       </c>
       <c r="I72" s="23" t="inlineStr">
         <is>
-          <t>P11.txt: "Work experience: Successful candidates are preferred to have industrial experience."</t>
+          <t>"Work experience: Successful candidates are preferred to have industrial experience."</t>
         </is>
       </c>
     </row>
@@ -7779,7 +8721,7 @@
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Business Administration Program</t>
+          <t>PhD Business Administration page</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
@@ -7804,7 +8746,7 @@
       </c>
       <c r="I73" s="21" t="inlineStr">
         <is>
-          <t>P12.txt contains no credit hours/duration/apply link; P22.txt: "Doctor of Philosophy (Ph.D.) In Business Administration (72) | SAR 150,000"</t>
+          <t>contains no credit hours/duration/apply link; "Doctor of Philosophy (Ph.D.) In Business Administration (72) | SAR 150,000"</t>
         </is>
       </c>
     </row>
@@ -7824,7 +8766,7 @@
       </c>
       <c r="D74" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Business Administration Program</t>
+          <t>PhD Business Administration page</t>
         </is>
       </c>
       <c r="E74" s="22" t="inlineStr">
@@ -7849,7 +8791,7 @@
       </c>
       <c r="I74" s="23" t="inlineStr">
         <is>
-          <t>P12.txt: "Doctor of Philosophy (Ph.D.) in Business Administration program is to develop scholars"</t>
+          <t>"Doctor of Philosophy (Ph.D.) in Business Administration program is to develop scholars"</t>
         </is>
       </c>
     </row>
@@ -7869,7 +8811,7 @@
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Business Administration Program</t>
+          <t>PhD Business Administration page</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
@@ -7894,7 +8836,7 @@
       </c>
       <c r="I75" s="21" t="inlineStr">
         <is>
-          <t>P12.txt: "The Ph.D. program is internationally accredited by AACSB as top 6% of business schools worldwide."</t>
+          <t>"The Ph.D. program is internationally accredited by AACSB as top 6% of business schools worldwide."</t>
         </is>
       </c>
     </row>
@@ -7914,7 +8856,7 @@
       </c>
       <c r="D76" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the PhD in Business Administration Program</t>
+          <t>PhD Business Administration page</t>
         </is>
       </c>
       <c r="E76" s="22" t="inlineStr">
@@ -7939,7 +8881,7 @@
       </c>
       <c r="I76" s="23" t="inlineStr">
         <is>
-          <t>P12.txt: "(scale is 4.00 = \"A”)"</t>
+          <t>"(scale is 4.00 = \"A”)"</t>
         </is>
       </c>
     </row>
@@ -7959,7 +8901,7 @@
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the EMBA Program</t>
+          <t>EMBA page</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
@@ -7979,12 +8921,12 @@
       </c>
       <c r="H77" s="21" t="inlineStr">
         <is>
-          <t>Remove the '(Very Good)' descriptor or define it consistently (same fix as P11).</t>
+          <t>Remove the '(Very Good)' descriptor or define it consistently.</t>
         </is>
       </c>
       <c r="I77" s="21" t="inlineStr">
         <is>
-          <t>P13.txt: "A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good)"; P11.txt: "3.00 out of 4.00 or equivalent (Very Good)"</t>
+          <t>"A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good)"; "3.00 out of 4.00 or equivalent (Very Good)"</t>
         </is>
       </c>
     </row>
@@ -8004,7 +8946,7 @@
       </c>
       <c r="D78" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the EMBA Program</t>
+          <t>EMBA page</t>
         </is>
       </c>
       <c r="E78" s="22" t="inlineStr">
@@ -8029,7 +8971,7 @@
       </c>
       <c r="I78" s="23" t="inlineStr">
         <is>
-          <t>P13.txt content has no apply link or dates; pages/admission_admissions_requirements_emba_gdp.txt sidebar: "Apply for EMBA"; P05.txt: "Graduate Admission Calendar"</t>
+          <t>content has no apply link or dates; sidebar: "Apply for EMBA"; "Graduate Admission Calendar"</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8991,7 @@
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the EMBA Program</t>
+          <t>EMBA page</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
@@ -8074,7 +9016,7 @@
       </c>
       <c r="I79" s="21" t="inlineStr">
         <is>
-          <t>P13.txt: "Three reference letters from supervisors and others in superior positions within the employing organization"</t>
+          <t>"Three reference letters from supervisors and others in superior positions within the employing organization"</t>
         </is>
       </c>
     </row>
@@ -8094,7 +9036,7 @@
       </c>
       <c r="D80" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MBA Program</t>
+          <t>MBA page</t>
         </is>
       </c>
       <c r="E80" s="22" t="inlineStr">
@@ -8119,7 +9061,7 @@
       </c>
       <c r="I80" s="23" t="inlineStr">
         <is>
-          <t>P14.txt: content ends with 'Personal Interview: Candidates will be personally interviewed...' (no documents); pages/admission_admissions_requirements_mba_gdp.txt sidebar: 'MBA Admissions / Apply for MBA'</t>
+          <t>content ends with 'Personal Interview: Candidates will be personally interviewed...' (no documents); sidebar: 'MBA Admissions / Apply for MBA'</t>
         </is>
       </c>
     </row>
@@ -8139,7 +9081,7 @@
       </c>
       <c r="D81" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MBA Program</t>
+          <t>MBA page</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
@@ -8164,7 +9106,7 @@
       </c>
       <c r="I81" s="21" t="inlineStr">
         <is>
-          <t>P11.txt: 'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs P14.txt: 'A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good) in Bachelor’s Degree'</t>
+          <t>'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs 'A minimum GPA of 2.50 out of 4.00 or equivalent (Very Good) in Bachelor’s Degree'</t>
         </is>
       </c>
     </row>
@@ -8184,7 +9126,7 @@
       </c>
       <c r="D82" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MBA Program</t>
+          <t>MBA page</t>
         </is>
       </c>
       <c r="E82" s="22" t="inlineStr">
@@ -8209,7 +9151,7 @@
       </c>
       <c r="I82" s="23" t="inlineStr">
         <is>
-          <t>P14.txt: 'non-business majors may be given the opportunity to take four business foundation courses before beginning their MBA coursework'</t>
+          <t>'non-business majors may be given the opportunity to take four business foundation courses before beginning their MBA coursework'</t>
         </is>
       </c>
     </row>
@@ -8229,7 +9171,7 @@
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSHD Program</t>
+          <t>MSHD page</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
@@ -8254,7 +9196,7 @@
       </c>
       <c r="I83" s="21" t="inlineStr">
         <is>
-          <t>P15.txt: 'Work Experience' followed directly by 'Personal Data Sheet/Curriculum Vita: The Personal Data Sheet should include relevant biographical information...'</t>
+          <t>'Work Experience' followed directly by 'Personal Data Sheet/Curriculum Vita: The Personal Data Sheet should include relevant biographical information...'</t>
         </is>
       </c>
     </row>
@@ -8274,7 +9216,7 @@
       </c>
       <c r="D84" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSHD Program</t>
+          <t>MSHD page</t>
         </is>
       </c>
       <c r="E84" s="22" t="inlineStr">
@@ -8299,7 +9241,7 @@
       </c>
       <c r="I84" s="23" t="inlineStr">
         <is>
-          <t>P15.txt: no credit hours/duration in content; P22.txt: 'Master of Science in Human Development | SAR 50,000 | SAR 60,000' (no hours); pages/admission_admissions_requirements_msehd_gdp.txt sidebar: 'Apply for MSHD'</t>
+          <t>no credit hours/duration in content; 'Master of Science in Human Development | SAR 50,000 | SAR 60,000' (no hours); sidebar: 'Apply for MSHD'</t>
         </is>
       </c>
     </row>
@@ -8319,7 +9261,7 @@
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSHD Program</t>
+          <t>MSHD page</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
@@ -8344,7 +9286,7 @@
       </c>
       <c r="I85" s="21" t="inlineStr">
         <is>
-          <t>P15.txt: page heading 'ADMISSIONS REQUIREMENTS' (other pages: 'MBA ADMISSIONS REQUIREMENTS', 'MSME ADMISSSIONS REQUIREMENTS')</t>
+          <t>page heading 'ADMISSIONS REQUIREMENTS' (other pages: 'MBA ADMISSIONS REQUIREMENTS', 'MSME ADMISSSIONS REQUIREMENTS')</t>
         </is>
       </c>
     </row>
@@ -8364,7 +9306,7 @@
       </c>
       <c r="D86" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSHD Program</t>
+          <t>MSHD page</t>
         </is>
       </c>
       <c r="E86" s="22" t="inlineStr">
@@ -8389,7 +9331,7 @@
       </c>
       <c r="I86" s="23" t="inlineStr">
         <is>
-          <t>P15.txt: 'Personal Data Sheet/Curriculum Vita:'</t>
+          <t>'Personal Data Sheet/Curriculum Vita:'</t>
         </is>
       </c>
     </row>
@@ -8409,7 +9351,7 @@
       </c>
       <c r="D87" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSHD Program</t>
+          <t>MSHD page</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
@@ -8434,7 +9376,7 @@
       </c>
       <c r="I87" s="21" t="inlineStr">
         <is>
-          <t>P15.txt (rendered, single line): 'one letter should be from a college or university professor who can discuss the Applicant’s academic abilities'</t>
+          <t>'one letter should be from a college or university professor who can discuss the Applicant’s academic abilities'</t>
         </is>
       </c>
     </row>
@@ -8454,7 +9396,7 @@
       </c>
       <c r="D88" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSHD Program</t>
+          <t>MSHD page</t>
         </is>
       </c>
       <c r="E88" s="22" t="inlineStr">
@@ -8479,7 +9421,7 @@
       </c>
       <c r="I88" s="23" t="inlineStr">
         <is>
-          <t>P15.txt: 'from an accredited and/or recognized university'; P14/P16/P17.txt: 'from a recognized university'</t>
+          <t>'from an accredited and/or recognized university'; MBA page/MSME page/'from a recognized university'</t>
         </is>
       </c>
     </row>
@@ -8499,7 +9441,7 @@
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSME Program</t>
+          <t>MSME page</t>
         </is>
       </c>
       <c r="E89" s="20" t="inlineStr">
@@ -8524,7 +9466,7 @@
       </c>
       <c r="I89" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_admissions_requirements_msme_gdp.txt: 'MSME Admisssions Requirements'; P16.txt: 'MSME ADMISSSIONS REQUIREMENTS'</t>
+          <t>'MSME Admisssions Requirements'; 'MSME ADMISSSIONS REQUIREMENTS'</t>
         </is>
       </c>
     </row>
@@ -8544,7 +9486,7 @@
       </c>
       <c r="D90" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSME Program</t>
+          <t>MSME page</t>
         </is>
       </c>
       <c r="E90" s="22" t="inlineStr">
@@ -8569,7 +9511,7 @@
       </c>
       <c r="I90" s="23" t="inlineStr">
         <is>
-          <t>P16.txt: 'The MSME is offered in Two tracks: Thermofluids track and Mechanical Systems track.'</t>
+          <t>'The MSME is offered in Two tracks: Thermofluids track and Mechanical Systems track.'</t>
         </is>
       </c>
     </row>
@@ -8589,7 +9531,7 @@
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSME Program</t>
+          <t>MSME page</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
@@ -8614,7 +9556,7 @@
       </c>
       <c r="I91" s="21" t="inlineStr">
         <is>
-          <t>P11.txt: 'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs P16.txt: 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
+          <t>'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
         </is>
       </c>
     </row>
@@ -8634,7 +9576,7 @@
       </c>
       <c r="D92" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSME Program</t>
+          <t>MSME page</t>
         </is>
       </c>
       <c r="E92" s="22" t="inlineStr">
@@ -8659,7 +9601,7 @@
       </c>
       <c r="I92" s="23" t="inlineStr">
         <is>
-          <t>P16.txt: content ends at 'Personal Interview: Candidates will be personally interviewed...' with no apply link; pages/admission_admissions_requirements_msme_gdp.txt sidebar: 'Apply for MSME'</t>
+          <t>content ends at 'Personal Interview: Candidates will be personally interviewed...' with no apply link; sidebar: 'Apply for MSME'</t>
         </is>
       </c>
     </row>
@@ -8679,7 +9621,7 @@
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSEE Program</t>
+          <t>MSEE page</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
@@ -8704,7 +9646,7 @@
       </c>
       <c r="I93" s="21" t="inlineStr">
         <is>
-          <t>P17.txt: 'MSEE ADMISSSIONS REQUIREMENTS'; rendered_all.json source: 'Graduate Programs &gt; MSEE  ADMISSSIONS REQUIREMENT' (double space in source; collapsed when displayed)</t>
+          <t>'MSEE ADMISSSIONS REQUIREMENTS'; source: 'Graduate Programs &gt; MSEE  ADMISSSIONS REQUIREMENT' (double space in source; collapsed when displayed)</t>
         </is>
       </c>
     </row>
@@ -8724,7 +9666,7 @@
       </c>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSEE Program</t>
+          <t>MSEE page</t>
         </is>
       </c>
       <c r="E94" s="22" t="inlineStr">
@@ -8749,7 +9691,7 @@
       </c>
       <c r="I94" s="23" t="inlineStr">
         <is>
-          <t>P17.txt: 'The program will be offered under the College of Engineering.'; P22.txt: 'Master of Science in Electrical Engineering (30) | SAR 65,000 | SAR 80,000'</t>
+          <t>'The program will be offered under the College of Engineering.'; 'Master of Science in Electrical Engineering (30) | SAR 65,000 | SAR 80,000'</t>
         </is>
       </c>
     </row>
@@ -8769,7 +9711,7 @@
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSEE Program</t>
+          <t>MSEE page</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
@@ -8794,7 +9736,7 @@
       </c>
       <c r="I95" s="21" t="inlineStr">
         <is>
-          <t>P17.txt: no credit hours, duration or apply link in content; pages/admission_application_form_msee_gdp.txt sidebar lists only 'Apply for EMBA/MBA/MSHD/MSME'; P22.txt: 'Master of Science in Electrical Engineering (30)'</t>
+          <t>no credit hours, duration or apply link in content; sidebar lists only 'Apply for EMBA/MBA/MSHD/MSME'; 'Master of Science in Electrical Engineering (30)'</t>
         </is>
       </c>
     </row>
@@ -8814,7 +9756,7 @@
       </c>
       <c r="D96" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSEE Program</t>
+          <t>MSEE page</t>
         </is>
       </c>
       <c r="E96" s="22" t="inlineStr">
@@ -8839,7 +9781,7 @@
       </c>
       <c r="I96" s="23" t="inlineStr">
         <is>
-          <t>P17.txt: 'A Bachelor’s Degree of Science in Engineering from a recognized university' then '*Students with Bachelor of Science degrees in closely related disciplines to Engineering...'; P18.txt: 'Civil Engineering* from'</t>
+          <t>'A Bachelor’s Degree of Science in Engineering from a recognized university' then '*Students with Bachelor of Science degrees in closely related disciplines to Engineering...'; 'Civil Engineering* from'</t>
         </is>
       </c>
     </row>
@@ -8859,7 +9801,7 @@
       </c>
       <c r="D97" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSEE Program</t>
+          <t>MSEE page</t>
         </is>
       </c>
       <c r="E97" s="20" t="inlineStr">
@@ -8884,7 +9826,7 @@
       </c>
       <c r="I97" s="21" t="inlineStr">
         <is>
-          <t>P17.txt: 'PMU) Masters in Electrical Engineering is designed...' and 'The core curriculum has two tracks; Communication Systems and Signal Processing track and Power Systems track.'</t>
+          <t>'PMU) Masters in Electrical Engineering is designed...' and 'The core curriculum has two tracks; Communication Systems and Signal Processing track and Power Systems track.'</t>
         </is>
       </c>
     </row>
@@ -8904,7 +9846,7 @@
       </c>
       <c r="D98" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSEE Program</t>
+          <t>MSEE page</t>
         </is>
       </c>
       <c r="E98" s="22" t="inlineStr">
@@ -8929,7 +9871,7 @@
       </c>
       <c r="I98" s="23" t="inlineStr">
         <is>
-          <t>P11.txt: 'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs P17.txt: 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
+          <t>'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
         </is>
       </c>
     </row>
@@ -8949,7 +9891,7 @@
       </c>
       <c r="D99" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSCE Program</t>
+          <t>MSCE page</t>
         </is>
       </c>
       <c r="E99" s="20" t="inlineStr">
@@ -8974,7 +9916,7 @@
       </c>
       <c r="I99" s="21" t="inlineStr">
         <is>
-          <t>P18.txt: 'MSCE ADMISSSIONS REQUIREMENTS' (breadcrumb and heading); pages file TITLE: 'MSCE ADMISSSIONS REQUIREMENTS :: Graduate Degree Programs'</t>
+          <t>'MSCE ADMISSSIONS REQUIREMENTS' (breadcrumb and heading); page title: 'MSCE ADMISSSIONS REQUIREMENTS :: Graduate Degree Programs'</t>
         </is>
       </c>
     </row>
@@ -8994,7 +9936,7 @@
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSCE Program</t>
+          <t>MSCE page</t>
         </is>
       </c>
       <c r="E100" s="22" t="inlineStr">
@@ -9019,7 +9961,7 @@
       </c>
       <c r="I100" s="23" t="inlineStr">
         <is>
-          <t>P18.txt: 'The program will be offered under the College of Engineering.'</t>
+          <t>'The program will be offered under the College of Engineering.'</t>
         </is>
       </c>
     </row>
@@ -9039,7 +9981,7 @@
       </c>
       <c r="D101" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSCE Program</t>
+          <t>MSCE page</t>
         </is>
       </c>
       <c r="E101" s="20" t="inlineStr">
@@ -9064,7 +10006,7 @@
       </c>
       <c r="I101" s="21" t="inlineStr">
         <is>
-          <t>P18.txt: 'The core curriculum has two tracks Structural and Geotechnical Engineering, Environment and Water Resources Engineering.'</t>
+          <t>'The core curriculum has two tracks Structural and Geotechnical Engineering, Environment and Water Resources Engineering.'</t>
         </is>
       </c>
     </row>
@@ -9084,7 +10026,7 @@
       </c>
       <c r="D102" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSCE Program</t>
+          <t>MSCE page</t>
         </is>
       </c>
       <c r="E102" s="22" t="inlineStr">
@@ -9109,7 +10051,7 @@
       </c>
       <c r="I102" s="23" t="inlineStr">
         <is>
-          <t>P18.txt: 'Statement of purpose:A statement of purpose (usually around 500 words)'</t>
+          <t>'Statement of purpose:A statement of purpose (usually around 500 words)'</t>
         </is>
       </c>
     </row>
@@ -9129,7 +10071,7 @@
       </c>
       <c r="D103" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSCE Program</t>
+          <t>MSCE page</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
@@ -9154,7 +10096,7 @@
       </c>
       <c r="I103" s="21" t="inlineStr">
         <is>
-          <t>P18.txt: no credit hours/duration/apply link in content; pages/admission_application_form_msce_gdp.txt sidebar has no MSCE apply link; P22.txt: 'Master of Science in Civil Engineering (30)'</t>
+          <t>no credit hours/duration/apply link in content; sidebar has no MSCE apply link; 'Master of Science in Civil Engineering (30)'</t>
         </is>
       </c>
     </row>
@@ -9174,7 +10116,7 @@
       </c>
       <c r="D104" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSCE Program</t>
+          <t>MSCE page</t>
         </is>
       </c>
       <c r="E104" s="22" t="inlineStr">
@@ -9199,7 +10141,7 @@
       </c>
       <c r="I104" s="23" t="inlineStr">
         <is>
-          <t>P11.txt: 'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs P18.txt: 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
+          <t>'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
         </is>
       </c>
     </row>
@@ -9219,7 +10161,7 @@
       </c>
       <c r="D105" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSID Program</t>
+          <t>MSID page</t>
         </is>
       </c>
       <c r="E105" s="20" t="inlineStr">
@@ -9244,7 +10186,7 @@
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
-          <t>P19.txt: 'MSID ADMISSSIONS REQUIREMENTS' (breadcrumb and heading); pages file TITLE: 'MSID ADMISSSIONS REQUIREMENTS :: Graduate Degree Programs'</t>
+          <t>'MSID ADMISSSIONS REQUIREMENTS' (breadcrumb and heading); page title: 'MSID ADMISSSIONS REQUIREMENTS :: Graduate Degree Programs'</t>
         </is>
       </c>
     </row>
@@ -9264,7 +10206,7 @@
       </c>
       <c r="D106" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSID Program</t>
+          <t>MSID page</t>
         </is>
       </c>
       <c r="E106" s="22" t="inlineStr">
@@ -9289,7 +10231,7 @@
       </c>
       <c r="I106" s="23" t="inlineStr">
         <is>
-          <t>P19.txt: 'The Department of Interior Design at PMU will educate tomorrow’s interior design leaders...' / '...(PMU) will be to provide an environment conducive...'</t>
+          <t>'The Department of Interior Design at PMU will educate tomorrow’s interior design leaders...' / '...(PMU) will be to provide an environment conducive...'</t>
         </is>
       </c>
     </row>
@@ -9309,7 +10251,7 @@
       </c>
       <c r="D107" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MSID Program</t>
+          <t>MSID page</t>
         </is>
       </c>
       <c r="E107" s="20" t="inlineStr">
@@ -9334,7 +10276,7 @@
       </c>
       <c r="I107" s="21" t="inlineStr">
         <is>
-          <t>P19.txt: Supporting Documents list only 'Statement of purpose' and 'Letters of reference' (no 'Work experience' line, unlike P17/P18); no credit hours or apply link; P22.txt: 'Master of Science in Interior Design (30)'</t>
+          <t>Supporting Documents list only 'Statement of purpose' and 'Letters of reference' (no 'Work experience' line, unlike MSEE page/MSCE page); no credit hours or apply link; 'Master of Science in Interior Design (30)'</t>
         </is>
       </c>
     </row>
@@ -9354,7 +10296,7 @@
       </c>
       <c r="D108" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MSID Program</t>
+          <t>MSID page</t>
         </is>
       </c>
       <c r="E108" s="22" t="inlineStr">
@@ -9379,7 +10321,7 @@
       </c>
       <c r="I108" s="23" t="inlineStr">
         <is>
-          <t>P11.txt: 'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs P19.txt: 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
+          <t>'A minimum cumulative GPA of 3.00 out of 4.00 or equivalent (Very Good)' vs 'A minimum cumulative GPA of 2.50 out of 4.00 or equivalent (Very Good)'</t>
         </is>
       </c>
     </row>
@@ -9399,7 +10341,7 @@
       </c>
       <c r="D109" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the EMGMS Program</t>
+          <t>EMGMS page</t>
         </is>
       </c>
       <c r="E109" s="20" t="inlineStr">
@@ -9414,7 +10356,7 @@
       </c>
       <c r="G109" s="21" t="inlineStr">
         <is>
-          <t>The Engineering Management page requires a 3.00/4.00 GPA (versus 2.50 on other engineering master's pages) and appears to contain content copied from another institution (it refers to the 'UA Center for English as Second Language'), so its requirements cannot be relied on.</t>
+          <t>The Engineering Management page requires a 3.00/4.00 GPA (versus 2.50 on other engineering master's pages) and contains text from another institution (it refers to the 'UA Center for English as Second Language'), so its requirements cannot be relied on.</t>
         </is>
       </c>
       <c r="H109" s="21" t="inlineStr">
@@ -9424,7 +10366,7 @@
       </c>
       <c r="I109" s="21" t="inlineStr">
         <is>
-          <t>P20.txt: 'Must show completion of a Bachelor’s degree. (minimum 3.00 out of 4.00)' ... 'Graduate English Language Endorsement from UA Center for English as Second Language (CESL)'; P17.txt: 'minimum cumulative GPA of 2.50 out of 4.00'</t>
+          <t>'Must show completion of a Bachelor’s degree. (minimum 3.00 out of 4.00)' ... 'Graduate English Language Endorsement from UA Center for English as Second Language (CESL)'; 'minimum cumulative GPA of 2.50 out of 4.00'</t>
         </is>
       </c>
     </row>
@@ -9444,7 +10386,7 @@
       </c>
       <c r="D110" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the EMGMS Program</t>
+          <t>EMGMS page</t>
         </is>
       </c>
       <c r="E110" s="22" t="inlineStr">
@@ -9459,7 +10401,7 @@
       </c>
       <c r="G110" s="23" t="inlineStr">
         <is>
-          <t>The Engineering Management page requires at least three recommendation letters on letterhead, while other engineering master's pages require two; this needs confirmation given the page appears to be copied from another institution.</t>
+          <t>The Engineering Management page requires at least three recommendation letters on letterhead, while other engineering master's pages require two; this needs confirmation given the page contains text from another institution.</t>
         </is>
       </c>
       <c r="H110" s="23" t="inlineStr">
@@ -9469,7 +10411,7 @@
       </c>
       <c r="I110" s="23" t="inlineStr">
         <is>
-          <t>P20.txt: 'Letters of Recommendation (Minimum 3)' / 'Must be written on university/company letterhead and signed by the recommender.'; P17.txt: 'at least two letters of recommendation'</t>
+          <t>'Letters of Recommendation (Minimum 3)' / 'Must be written on university/company letterhead and signed by the recommender.'; 'at least two letters of recommendation'</t>
         </is>
       </c>
     </row>
@@ -9489,7 +10431,7 @@
       </c>
       <c r="D111" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the EMGMS Program</t>
+          <t>EMGMS page</t>
         </is>
       </c>
       <c r="E111" s="20" t="inlineStr">
@@ -9514,7 +10456,7 @@
       </c>
       <c r="I111" s="21" t="inlineStr">
         <is>
-          <t>P20.txt: 'Master of Science in Engineering Management Application(EMGMS) Checklist'; P22.txt: 'Master of Science in Engineering Management (30)'</t>
+          <t>'Master of Science in Engineering Management Application(EMGMS) Checklist'; 'Master of Science in Engineering Management (30)'</t>
         </is>
       </c>
     </row>
@@ -9534,7 +10476,7 @@
       </c>
       <c r="D112" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E112" s="22" t="inlineStr">
@@ -9559,7 +10501,7 @@
       </c>
       <c r="I112" s="23" t="inlineStr">
         <is>
-          <t>P21.txt: 'A Bachelor’s Degree in law from a recognized university' / 'A minimum (Very Good) in Bachelor’s Degree'</t>
+          <t>'A Bachelor’s Degree in law from a recognized university' / 'A minimum (Very Good) in Bachelor’s Degree'</t>
         </is>
       </c>
     </row>
@@ -9579,7 +10521,7 @@
       </c>
       <c r="D113" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E113" s="20" t="inlineStr">
@@ -9604,7 +10546,7 @@
       </c>
       <c r="I113" s="21" t="inlineStr">
         <is>
-          <t>P21.txt: 'minimum scores of 6.5 overall and 5.5 in each skill or equivalent TOEFL iBT minimum scores of 83 overall'; P14.txt: 'minimum scores of 6.0 overall ... or equivalent TOEFL iBT minimum scores of 83 overall'</t>
+          <t>'minimum scores of 6.5 overall and 5.5 in each skill or equivalent TOEFL iBT minimum scores of 83 overall'; 'minimum scores of 6.0 overall ... or equivalent TOEFL iBT minimum scores of 83 overall'</t>
         </is>
       </c>
     </row>
@@ -9624,7 +10566,7 @@
       </c>
       <c r="D114" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E114" s="22" t="inlineStr">
@@ -9649,7 +10591,7 @@
       </c>
       <c r="I114" s="23" t="inlineStr">
         <is>
-          <t>P21.txt: 'complete the program within two years in a full-time mode (maximum 6 credits in each semester)'; P22.txt: 'Master of Arts in International Business Law (36)'</t>
+          <t>'complete the program within two years in a full-time mode (maximum 6 credits in each semester)'; 'Master of Arts in International Business Law (36)'</t>
         </is>
       </c>
     </row>
@@ -9669,7 +10611,7 @@
       </c>
       <c r="D115" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E115" s="20" t="inlineStr">
@@ -9694,7 +10636,7 @@
       </c>
       <c r="I115" s="21" t="inlineStr">
         <is>
-          <t>P21.txt: 'The year 2025 marks another milestone for PMU Law with the approval of the postgraduate program'</t>
+          <t>'The year 2025 marks another milestone for PMU Law with the approval of the postgraduate program'</t>
         </is>
       </c>
     </row>
@@ -9714,7 +10656,7 @@
       </c>
       <c r="D116" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E116" s="22" t="inlineStr">
@@ -9739,7 +10681,7 @@
       </c>
       <c r="I116" s="23" t="inlineStr">
         <is>
-          <t>P21.txt: criteria list only Educational Background, English test, Personal Interview, then '30% for the written test.'; P10.txt: 'Admissions to the Master of Arts (MA) in International Business Law Program / Application Form'</t>
+          <t>criteria list only Educational Background, English test, Personal Interview, then '30% for the written test.'; 'Admissions to the Master of Arts (MA) in International Business Law Program / Application Form'</t>
         </is>
       </c>
     </row>
@@ -9759,7 +10701,7 @@
       </c>
       <c r="D117" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E117" s="20" t="inlineStr">
@@ -9784,7 +10726,7 @@
       </c>
       <c r="I117" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_admissions_requirements_milbl_gdp.txt: 'MIBL Admisssions Requirements'; P21.txt: 'MIBL ADMISSSIONS REQUIREMENTS'</t>
+          <t>'MIBL Admisssions Requirements'; 'MIBL ADMISSSIONS REQUIREMENTS'</t>
         </is>
       </c>
     </row>
@@ -9804,7 +10746,7 @@
       </c>
       <c r="D118" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the MIBL</t>
+          <t>MIBL page</t>
         </is>
       </c>
       <c r="E118" s="22" t="inlineStr">
@@ -9829,7 +10771,7 @@
       </c>
       <c r="I118" s="23" t="inlineStr">
         <is>
-          <t>P21.txt: 'admission on a part-time basis may be considered subject to the applicable regulation, delivered and facilitated by qualified and experienced academics'</t>
+          <t>'admission on a part-time basis may be considered subject to the applicable regulation, delivered and facilitated by qualified and experienced academics'</t>
         </is>
       </c>
     </row>
@@ -9849,7 +10791,7 @@
       </c>
       <c r="D119" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E119" s="20" t="inlineStr">
@@ -9874,7 +10816,7 @@
       </c>
       <c r="I119" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_post_graduate_fees_tf_ro.txt sidebar: 'Payment Schedule / Spring Semester 2025/2026 / Summer Semester 2025/2026 / Fall Semester 2026/2027'; pages/admission_payment_schedule_tf_ro_summer.txt: '1st 01-July-2026 10-July-2026'</t>
+          <t>sidebar: 'Payment Schedule / Spring Semester 2025/2026 / Summer Semester 2025/2026 / Fall Semester 2026/2027'; '1st 01-July-2026 10-July-2026'</t>
         </is>
       </c>
     </row>
@@ -9894,7 +10836,7 @@
       </c>
       <c r="D120" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E120" s="22" t="inlineStr">
@@ -9919,7 +10861,7 @@
       </c>
       <c r="I120" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_post_graduate_fees_tf_ro.txt sidebar: 'Undergraduate Fees for / Continuing 2024-2025'; pages/admission_fees_tf_ro_2024_2025.txt: 'Undergraduate Fees (For continuing students admitted before Fall Semester 2025/2026)'</t>
+          <t>sidebar: 'Undergraduate Fees for / Continuing 2024-2025'; 'Undergraduate Fees (For continuing students admitted before Fall Semester 2025/2026)'</t>
         </is>
       </c>
     </row>
@@ -9939,7 +10881,7 @@
       </c>
       <c r="D121" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
@@ -9964,7 +10906,7 @@
       </c>
       <c r="I121" s="21" t="inlineStr">
         <is>
-          <t>P22.txt: 'PRE-Master for Master of Education | NA | SAR 30,000' and 'Master of Science in Education and Human Development | 1,191 SAR /Credit hour'; P10.txt lists 'Admission to the Master of Human Development'</t>
+          <t>'PRE-Master for Master of Education | NA | SAR 30,000' and 'Master of Science in Education and Human Development | 1,191 SAR /Credit hour'; lists 'Admission to the Master of Human Development'</t>
         </is>
       </c>
     </row>
@@ -9984,7 +10926,7 @@
       </c>
       <c r="D122" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E122" s="22" t="inlineStr">
@@ -10009,7 +10951,7 @@
       </c>
       <c r="I122" s="23" t="inlineStr">
         <is>
-          <t>P22.txt: 'Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000'; pages/admission_list_majors_ro.txt: 'Master of Science in Engineering Innovation, Sustainability, and Entrepreneurship / Degree Plan / Catalog'</t>
+          <t>'Master of Engineering in Innovation, Sustainability, and Entrepreneurship (33) | SAR 80,000'; 'Master of Science in Engineering Innovation, Sustainability, and Entrepreneurship / Degree Plan / Catalog'</t>
         </is>
       </c>
     </row>
@@ -10029,7 +10971,7 @@
       </c>
       <c r="D123" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -10054,7 +10996,7 @@
       </c>
       <c r="I123" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P22.txt: "Graduate FULL-TIME Students Tuition" ... "EMBA | SAR 60,000 | SAR 75,000"; later "EMBA Starting from Fall Semester (2025/2026) | 1,818.18 SAR /Credit hour" (60,000/1,818.18 = 33)</t>
+          <t>"Graduate FULL-TIME Students Tuition" ... "EMBA | SAR 60,000 | SAR 75,000"; later "EMBA Starting from Fall Semester (2025/2026) | 1,818.18 SAR /Credit hour" (60,000/1,818.18 = 33)</t>
         </is>
       </c>
     </row>
@@ -10074,7 +11016,7 @@
       </c>
       <c r="D124" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E124" s="22" t="inlineStr">
@@ -10099,7 +11041,7 @@
       </c>
       <c r="I124" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P22.txt: "Not successfully completing a course in Graduate program ... and having to repeat it will cost as per the credit hour fee as follows:" followed by two per-credit-hour tables</t>
+          <t>"Not successfully completing a course in Graduate program ... and having to repeat it will cost as per the credit hour fee as follows:" followed by two per-credit-hour tables</t>
         </is>
       </c>
     </row>
@@ -10119,7 +11061,7 @@
       </c>
       <c r="D125" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -10144,7 +11086,7 @@
       </c>
       <c r="I125" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P22.txt: "Master of Science in Human Development | SAR 50,000" vs "Master of Science in Education and Human Development | 1,191 SAR /Credit hour"</t>
+          <t>"Master of Science in Human Development | SAR 50,000" vs "Master of Science in Education and Human Development | 1,191 SAR /Credit hour"</t>
         </is>
       </c>
     </row>
@@ -10164,7 +11106,7 @@
       </c>
       <c r="D126" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E126" s="22" t="inlineStr">
@@ -10189,7 +11131,7 @@
       </c>
       <c r="I126" s="23" t="inlineStr">
         <is>
-          <t>P22: "Doctoral program in Mechanical Engineering (72)"; P11: "PhD in Mechanical Engineering"; P10: "Admissions to the Doctorate in Mechanical Engineering Program"</t>
+          <t>Post Graduate Fees: "Doctoral program in Mechanical Engineering (72)"; PhD ME page: "PhD in Mechanical Engineering"; Graduate Programs page: "Admissions to the Doctorate in Mechanical Engineering Program"</t>
         </is>
       </c>
     </row>
@@ -10209,7 +11151,7 @@
       </c>
       <c r="D127" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -10234,7 +11176,7 @@
       </c>
       <c r="I127" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P22.txt: "1,818.18 SAR" / "2,083.3 SAR" / "2,424.25 SAR" / "1,191 SAR" / "2,167 SAR"</t>
+          <t>"1,818.18 SAR" / "2,083.3 SAR" / "2,424.25 SAR" / "1,191 SAR" / "2,167 SAR"</t>
         </is>
       </c>
     </row>
@@ -10254,7 +11196,7 @@
       </c>
       <c r="D128" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Post Graduate Fees page</t>
         </is>
       </c>
       <c r="E128" s="22" t="inlineStr">
@@ -10279,7 +11221,7 @@
       </c>
       <c r="I128" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P22.txt: "EMBA - Continuing Students ... | 1,334 SAR /Credit hour | 1,667 SAR" vs "MBA - Continuing Students ... | 1,354 SAR /Credit hour | 1,667 SAR"</t>
+          <t>"EMBA - Continuing Students ... | 1,334 SAR /Credit hour | 1,667 SAR" vs "MBA - Continuing Students ... | 1,354 SAR /Credit hour | 1,667 SAR"</t>
         </is>
       </c>
     </row>
@@ -10299,7 +11241,7 @@
       </c>
       <c r="D129" s="21" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Graduate Contact page</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -10324,7 +11266,7 @@
       </c>
       <c r="I129" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P23.txt: "Graduate Study Admission Coordinator / Office: G-017 Admin Bld / Email: graduateadm@pmu.edu.sa"</t>
+          <t>"Graduate Study Admission Coordinator / Office: G-017 Admin Bld / Email: graduateadm@pmu.edu.sa"</t>
         </is>
       </c>
     </row>
@@ -10344,7 +11286,7 @@
       </c>
       <c r="D130" s="23" t="inlineStr">
         <is>
-          <t>Contact Info</t>
+          <t>Graduate Contact page</t>
         </is>
       </c>
       <c r="E130" s="22" t="inlineStr">
@@ -10369,7 +11311,7 @@
       </c>
       <c r="I130" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P23.txt sidebar: "Web Admission Guide"; browser/result2_mobile_probes.json: "https://www.pmu.edu.sa/PDF/Viewer.aspx?ID=203"</t>
+          <t>sidebar: "Web Admission Guide"; "https://www.pmu.edu.sa/PDF/Viewer.aspx?ID=203"</t>
         </is>
       </c>
     </row>
@@ -10389,7 +11331,7 @@
       </c>
       <c r="D131" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -10414,7 +11356,7 @@
       </c>
       <c r="I131" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P24.txt: "PMU offers various degrees under the College of Architecture and Design, College of Computer Engineering and Science, College of Business Administration, College of Law and College of Engineering."; same page: "College of Medical Admissions"</t>
+          <t>"PMU offers various degrees under the College of Architecture and Design, College of Computer Engineering and Science, College of Business Administration, College of Law and College of Engineering."; same page: "College of Medical Admissions"</t>
         </is>
       </c>
     </row>
@@ -10434,7 +11376,7 @@
       </c>
       <c r="D132" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E132" s="22" t="inlineStr">
@@ -10459,7 +11401,7 @@
       </c>
       <c r="I132" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P24.txt: "College of Medical Admissions" / "The PMU College of Medical curriculum is based on a 7-year hybrid model"; P25 title: "ADMISSIONS TO THE COLLEGE OF MEDICINE"</t>
+          <t>"College of Medical Admissions" / "The PMU College of Medical curriculum is based on a 7-year hybrid model"; Medicine page title: "ADMISSIONS TO THE COLLEGE OF MEDICINE"</t>
         </is>
       </c>
     </row>
@@ -10479,7 +11421,7 @@
       </c>
       <c r="D133" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
@@ -10504,7 +11446,7 @@
       </c>
       <c r="I133" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P24.txt: "This 7-year curriculum combines a variety of course-type: (Read more)"</t>
+          <t>"This 7-year curriculum combines a variety of course-type: (Read more)"</t>
         </is>
       </c>
     </row>
@@ -10524,7 +11466,7 @@
       </c>
       <c r="D134" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E134" s="22" t="inlineStr">
@@ -10549,7 +11491,7 @@
       </c>
       <c r="I134" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P24.txt: "Admission to each of the undergraduate program is based on different criteria."</t>
+          <t>"Admission to each of the undergraduate program is based on different criteria."</t>
         </is>
       </c>
     </row>
@@ -10569,7 +11511,7 @@
       </c>
       <c r="D135" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -10594,7 +11536,7 @@
       </c>
       <c r="I135" s="21" t="inlineStr">
         <is>
-          <t>P24: "Computer Science and Engineering Majors Admission Requirements"; P31: "These majors are Architecture, Computer Science, Computer Engineering, Software Engineering..."; P08: "AI and Computer Science, Architecture and Engineering Majors"</t>
+          <t>Undergraduate Admissions page: "Computer Science and Engineering Majors Admission Requirements"; CS &amp; Engineering page: "These majors are Architecture, Computer Science, Computer Engineering, Software Engineering..."; /apply: "AI and Computer Science, Architecture and Engineering Majors"</t>
         </is>
       </c>
     </row>
@@ -10614,7 +11556,7 @@
       </c>
       <c r="D136" s="23" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E136" s="22" t="inlineStr">
@@ -10639,7 +11581,7 @@
       </c>
       <c r="I136" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P05.txt: "Fall 2026-2027 ... Last day for Freshman and Re-Admitting applicants to Apply Online | 2026-06-24 ... First day of classes | 2026-08-30"</t>
+          <t>"Fall 2026-2027 ... Last day for Freshman and Re-Admitting applicants to Apply Online | 2026-06-24 ... First day of classes | 2026-08-30"</t>
         </is>
       </c>
     </row>
@@ -10659,7 +11601,7 @@
       </c>
       <c r="D137" s="21" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Undergraduate Admissions page</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
@@ -10684,7 +11626,7 @@
       </c>
       <c r="I137" s="21" t="inlineStr">
         <is>
-          <t>P24: "attested, in advance, by the Saudi Consulate and other authorized organizations"; pages_v5/apply_raw_text.txt: "Have the certificate stamped by the Saudi Embassy in their country"</t>
+          <t>Undergraduate Admissions page: "attested, in advance, by the Saudi Consulate and other authorized organizations"; "Have the certificate stamped by the Saudi Embassy in their country"</t>
         </is>
       </c>
     </row>
@@ -10704,7 +11646,7 @@
       </c>
       <c r="D138" s="23" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E138" s="22" t="inlineStr">
@@ -10729,7 +11671,7 @@
       </c>
       <c r="I138" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt: "*20% high school + 40% Qudrat + 40% Tahseely were 86 is the minimum acceptable score"</t>
+          <t>"*20% high school + 40% Qudrat + 40% Tahseely were 86 is the minimum acceptable score"</t>
         </is>
       </c>
     </row>
@@ -10749,7 +11691,7 @@
       </c>
       <c r="D139" s="21" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -10774,7 +11716,7 @@
       </c>
       <c r="I139" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt: "admissions to College of Medical major ... the process typically involves understanding the weighting ... Here’s how each factor can contribute" followed by "Total weighted score* | 60% / Interview | 40%"</t>
+          <t>"admissions to College of Medical major ... the process typically involves understanding the weighting ... Here’s how each factor can contribute" followed by "Total weighted score* | 60% / Interview | 40%"</t>
         </is>
       </c>
     </row>
@@ -10794,7 +11736,7 @@
       </c>
       <c r="D140" s="23" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E140" s="22" t="inlineStr">
@@ -10819,7 +11761,7 @@
       </c>
       <c r="I140" s="23" t="inlineStr">
         <is>
-          <t>P25: "Pay a non-refundable application fee of SAR 1000 (incl. VAT)"; P24/P26/P27/P28/P29/P31: "SAR 950 (incl. VAT)"; P08: "application fee of SAR 950"</t>
+          <t>Medicine page: "Pay a non-refundable application fee of SAR 1000 (incl. VAT)"; Undergraduate Admissions page/Preparatory Program page/Direct Admissions page/Transfer page/Visiting page/CS &amp; Engineering page: "SAR 950 (incl. VAT)"; /apply: "application fee of SAR 950"</t>
         </is>
       </c>
     </row>
@@ -10839,7 +11781,7 @@
       </c>
       <c r="D141" s="21" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E141" s="20" t="inlineStr">
@@ -10864,7 +11806,7 @@
       </c>
       <c r="I141" s="21" t="inlineStr">
         <is>
-          <t>crawl/scope_inventory.csv: "https://www.uap.sa/ ... admission/college_of_medicine_admission"; P05: "For Saudi Students: Apply online through Qabool platform: https://www.uap.sa/"</t>
+          <t>College of Medicine page links to https://www.uap.sa/ ; Admission Calendar: "For Saudi Students: Apply online through Qabool platform: https://www.uap.sa/"</t>
         </is>
       </c>
     </row>
@@ -10884,7 +11826,7 @@
       </c>
       <c r="D142" s="23" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E142" s="22" t="inlineStr">
@@ -10909,7 +11851,7 @@
       </c>
       <c r="I142" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt: "Copy of General Aptitude Test score report (Qudrat) (80) or equivalent (SAT 1)" / "(SAAT – Tahseely) (80) or equivalent (SAT 1) 1300"</t>
+          <t>"Copy of General Aptitude Test score report (Qudrat) (80) or equivalent (SAT 1)" / "(SAAT – Tahseely) (80) or equivalent (SAT 1) 1300"</t>
         </is>
       </c>
     </row>
@@ -10929,7 +11871,7 @@
       </c>
       <c r="D143" s="21" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E143" s="20" t="inlineStr">
@@ -10954,7 +11896,7 @@
       </c>
       <c r="I143" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt How to Apply lists only: application, documents, school certificate (95%), Qudrat, Tahseely, "Copy of Saudi ID or Iqama", passport, "SAR 1000" fee - no IELTS/TOEFL, photos, Family ID or no-objection letter</t>
+          <t>How to Apply lists only: application, documents, school certificate (95%), Qudrat, Tahseely, "Copy of Saudi ID or Iqama", passport, "SAR 1000" fee - no IELTS/TOEFL, photos, Family ID or no-objection letter</t>
         </is>
       </c>
     </row>
@@ -10974,7 +11916,7 @@
       </c>
       <c r="D144" s="23" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E144" s="22" t="inlineStr">
@@ -10999,7 +11941,7 @@
       </c>
       <c r="I144" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt: "Population Health (to be developed in launch phase)" (appears in Year 5 list and Year 6 electives)</t>
+          <t>"Population Health (to be developed in launch phase)" (appears in Year 5 list and Year 6 electives)</t>
         </is>
       </c>
     </row>
@@ -11019,7 +11961,7 @@
       </c>
       <c r="D145" s="21" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E145" s="20" t="inlineStr">
@@ -11044,7 +11986,7 @@
       </c>
       <c r="I145" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_college_of_medicine_admission.txt: "Block 9: Transition to Clerkship (Part 1 of CCC – see section below for explanation of CCC)"; only other mention: "Clinical Intersections (Part 2 of CCC)"</t>
+          <t>"Block 9: Transition to Clerkship (Part 1 of CCC – see section below for explanation of CCC)"; only other mention: "Clinical Intersections (Part 2 of CCC)"</t>
         </is>
       </c>
     </row>
@@ -11064,7 +12006,7 @@
       </c>
       <c r="D146" s="23" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E146" s="22" t="inlineStr">
@@ -11089,7 +12031,7 @@
       </c>
       <c r="I146" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt: "Elective Rotations" / "Surgery 8 weeks (Two 4-week electives)" / "Required Rotations" / "Advanced Surgery and one of the following electives:" ... "Vascular Surgery (2-week elective)"</t>
+          <t>"Elective Rotations" / "Surgery 8 weeks (Two 4-week electives)" / "Required Rotations" / "Advanced Surgery and one of the following electives:" ... "Vascular Surgery (2-week elective)"</t>
         </is>
       </c>
     </row>
@@ -11109,7 +12051,7 @@
       </c>
       <c r="D147" s="21" t="inlineStr">
         <is>
-          <t>Admission to the College of Medicine</t>
+          <t>College of Medicine page</t>
         </is>
       </c>
       <c r="E147" s="20" t="inlineStr">
@@ -11134,7 +12076,7 @@
       </c>
       <c r="I147" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P25.txt: "The PMU College of Medical curriculum ... combines a variety of course-type:"</t>
+          <t>"The PMU College of Medical curriculum ... combines a variety of course-type:"</t>
         </is>
       </c>
     </row>
@@ -11154,7 +12096,7 @@
       </c>
       <c r="D148" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the Preparatory Program</t>
+          <t>Preparatory Program page</t>
         </is>
       </c>
       <c r="E148" s="22" t="inlineStr">
@@ -11179,7 +12121,7 @@
       </c>
       <c r="I148" s="23" t="inlineStr">
         <is>
-          <t>P26: "Submit documents before due date"; P05 only: "Fall 2026-2027 ... Last day for Transfer applicants to submit documents in person | 2026-07-20"</t>
+          <t>Preparatory Program page: "Submit documents before due date"; Admission Calendar only: "Fall 2026-2027 ... Last day for Transfer applicants to submit documents in person | 2026-07-20"</t>
         </is>
       </c>
     </row>
@@ -11199,7 +12141,7 @@
       </c>
       <c r="D149" s="21" t="inlineStr">
         <is>
-          <t>Admissions to the Preparatory Program</t>
+          <t>Preparatory Program page</t>
         </is>
       </c>
       <c r="E149" s="20" t="inlineStr">
@@ -11224,7 +12166,7 @@
       </c>
       <c r="I149" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P26.txt: "mathematics and learning skills**" ... "**Based on the student’s English level, the following study skills courses are required:"</t>
+          <t>"mathematics and learning skills**" ... "**Based on the student’s English level, the following study skills courses are required:"</t>
         </is>
       </c>
     </row>
@@ -11244,7 +12186,7 @@
       </c>
       <c r="D150" s="23" t="inlineStr">
         <is>
-          <t>Admissions to the Preparatory Program</t>
+          <t>Preparatory Program page</t>
         </is>
       </c>
       <c r="E150" s="22" t="inlineStr">
@@ -11269,7 +12211,7 @@
       </c>
       <c r="I150" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P26.txt: "How to Apply:" / "Completed online application"; P27: "How to Apply:" / "Complete online application"</t>
+          <t>"How to Apply:" / "Completed online application"; Direct Admissions page: "How to Apply:" / "Complete online application"</t>
         </is>
       </c>
     </row>
@@ -11289,7 +12231,7 @@
       </c>
       <c r="D151" s="21" t="inlineStr">
         <is>
-          <t>Direct Admissions from Secondary School</t>
+          <t>Direct Admissions page</t>
         </is>
       </c>
       <c r="E151" s="20" t="inlineStr">
@@ -11314,7 +12256,7 @@
       </c>
       <c r="I151" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P27.txt: "Copy of Saudi ID"; P26 and P28: "Copy of Saudi ID or “Iqama” (for Non-Saudis)"</t>
+          <t>"Copy of Saudi ID"; Preparatory Program page and Transfer page: "Copy of Saudi ID or “Iqama” (for Non-Saudis)"</t>
         </is>
       </c>
     </row>
@@ -11334,7 +12276,7 @@
       </c>
       <c r="D152" s="23" t="inlineStr">
         <is>
-          <t>Direct Admissions from Secondary School</t>
+          <t>Direct Admissions page</t>
         </is>
       </c>
       <c r="E152" s="22" t="inlineStr">
@@ -11359,7 +12301,7 @@
       </c>
       <c r="I152" s="23" t="inlineStr">
         <is>
-          <t>P27: "A valid IELTS certificate (Academic version) with Minimum scores of 6.0 overall and 5.5 in writing." and "...or equivalent TOEFL iBT (Learn more)"; P08: "TOEFL iBT: Overall 83, Writing 19"; P36: "Core | 83 | 19"</t>
+          <t>Direct Admissions page: "A valid IELTS certificate (Academic version) with Minimum scores of 6.0 overall and 5.5 in writing." and "...or equivalent TOEFL iBT (Learn more)"; /apply: "TOEFL iBT: Overall 83, Writing 19"; TOEFL page: "Core | 83 | 19"</t>
         </is>
       </c>
     </row>
@@ -11379,7 +12321,7 @@
       </c>
       <c r="D153" s="21" t="inlineStr">
         <is>
-          <t>Admissions from Other Universities</t>
+          <t>Transfer Admissions page</t>
         </is>
       </c>
       <c r="E153" s="20" t="inlineStr">
@@ -11404,7 +12346,7 @@
       </c>
       <c r="I153" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P28.txt: "In order to be consider as a transfer candidate"</t>
+          <t>"In order to be consider as a transfer candidate"</t>
         </is>
       </c>
     </row>
@@ -11424,7 +12366,7 @@
       </c>
       <c r="D154" s="23" t="inlineStr">
         <is>
-          <t>Admissions from Other Universities</t>
+          <t>Transfer Admissions page</t>
         </is>
       </c>
       <c r="E154" s="22" t="inlineStr">
@@ -11449,7 +12391,7 @@
       </c>
       <c r="I154" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P28.txt: "The total GPA is 2.0 out of 4.0 from the previous institution"</t>
+          <t>"The total GPA is 2.0 out of 4.0 from the previous institution"</t>
         </is>
       </c>
     </row>
@@ -11469,7 +12411,7 @@
       </c>
       <c r="D155" s="21" t="inlineStr">
         <is>
-          <t>Admissions from Other Universities</t>
+          <t>Transfer Admissions page</t>
         </is>
       </c>
       <c r="E155" s="20" t="inlineStr">
@@ -11494,7 +12436,7 @@
       </c>
       <c r="I155" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P28.txt: "...or equivalent TOEFL iBT with acceptable scores (read more...)"; P08: "TOEFL iBT: Overall 83, Writing 19"</t>
+          <t>"...or equivalent TOEFL iBT with acceptable scores (read more...)"; /apply: "TOEFL iBT: Overall 83, Writing 19"</t>
         </is>
       </c>
     </row>
@@ -11514,7 +12456,7 @@
       </c>
       <c r="D156" s="23" t="inlineStr">
         <is>
-          <t>Admissions from Other Universities</t>
+          <t>Transfer Admissions page</t>
         </is>
       </c>
       <c r="E156" s="22" t="inlineStr">
@@ -11539,7 +12481,7 @@
       </c>
       <c r="I156" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P28.txt: "international university or can be a college/community college in a Western country (Associate Degree or above)"</t>
+          <t>"international university or can be a college/community college in a Western country (Associate Degree or above)"</t>
         </is>
       </c>
     </row>
@@ -11559,7 +12501,7 @@
       </c>
       <c r="D157" s="21" t="inlineStr">
         <is>
-          <t>Visting Students</t>
+          <t>Visiting Students page</t>
         </is>
       </c>
       <c r="E157" s="20" t="inlineStr">
@@ -11584,7 +12526,7 @@
       </c>
       <c r="I157" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P00.txt: "Visting Students"; crawl/admission_page_dom.json: "t": "Visting Students", "raw": "../Admission/Visiting-Student-Admission.aspx"</t>
+          <t>Admissions Office page link text: "Visting Students"</t>
         </is>
       </c>
     </row>
@@ -11604,7 +12546,7 @@
       </c>
       <c r="D158" s="23" t="inlineStr">
         <is>
-          <t>Visting Students</t>
+          <t>Visiting Students page</t>
         </is>
       </c>
       <c r="E158" s="22" t="inlineStr">
@@ -11629,7 +12571,7 @@
       </c>
       <c r="I158" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_visiting-student-admission.txt: "TITLE: Visiting Student Admission :: Undergraduate :: Admission Office" / breadcrumb "Admission Office &gt; Undergraduate &gt; Visiting Student Admissions"</t>
+          <t>"TITLE: Visiting Student Admission :: Undergraduate :: Admission Office" / breadcrumb "Admission Office &gt; Undergraduate &gt; Visiting Student Admissions"</t>
         </is>
       </c>
     </row>
@@ -11649,7 +12591,7 @@
       </c>
       <c r="D159" s="21" t="inlineStr">
         <is>
-          <t>Visting Students</t>
+          <t>Visiting Students page</t>
         </is>
       </c>
       <c r="E159" s="20" t="inlineStr">
@@ -11674,7 +12616,7 @@
       </c>
       <c r="I159" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P29.txt: "...or equivalent to TOEFL iBT (learn more...), if the medium of instruction at the home institute is other than English"; earlier: "approval from the home institution"</t>
+          <t>"...or equivalent to TOEFL iBT (learn more...), if the medium of instruction at the home institute is other than English"; earlier: "approval from the home institution"</t>
         </is>
       </c>
     </row>
@@ -11694,7 +12636,7 @@
       </c>
       <c r="D160" s="23" t="inlineStr">
         <is>
-          <t>Visting Students</t>
+          <t>Visiting Students page</t>
         </is>
       </c>
       <c r="E160" s="22" t="inlineStr">
@@ -11719,7 +12661,7 @@
       </c>
       <c r="I160" s="23" t="inlineStr">
         <is>
-          <t>P29: "Submit documents before due date"; P05 events cover only Freshman, Re-Admitting and Transfer applicants, e.g. "Last day for Transfer applicants to submit documents in person | 2026-07-20"</t>
+          <t>Visiting page: "Submit documents before due date"; Admission Calendar events cover only Freshman, Re-Admitting and Transfer applicants, e.g. "Last day for Transfer applicants to submit documents in person | 2026-07-20"</t>
         </is>
       </c>
     </row>
@@ -11739,7 +12681,7 @@
       </c>
       <c r="D161" s="21" t="inlineStr">
         <is>
-          <t>Admissions from the Preparatory Program</t>
+          <t>Preparatory-to-Undergraduate page</t>
         </is>
       </c>
       <c r="E161" s="20" t="inlineStr">
@@ -11764,7 +12706,7 @@
       </c>
       <c r="I161" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P30.txt: "College of Engineering* | Yes | No | Yes" ... "College of Computer Engineering &amp; Science** | Yes | No | Yes" ... "College of Architecture &amp; Design* | Yes | Yes | No" ... "* Department of Information Technology is excluded from PRPM 0022" / "** Department of Architecture is excluded from PRPM 0012"</t>
+          <t>"College of Engineering* | Yes | No | Yes" ... "College of Computer Engineering &amp; Science** | Yes | No | Yes" ... "College of Architecture &amp; Design* | Yes | Yes | No" ... "* Department of Information Technology is excluded from PRPM 0022" / "** Department of Architecture is excluded from PRPM 0012"</t>
         </is>
       </c>
     </row>
@@ -11784,7 +12726,7 @@
       </c>
       <c r="D162" s="23" t="inlineStr">
         <is>
-          <t>Admissions from the Preparatory Program</t>
+          <t>Preparatory-to-Undergraduate page</t>
         </is>
       </c>
       <c r="E162" s="22" t="inlineStr">
@@ -11809,7 +12751,7 @@
       </c>
       <c r="I162" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P30.txt: "Successfully pass the EXIT exam"</t>
+          <t>"Successfully pass the EXIT exam"</t>
         </is>
       </c>
     </row>
@@ -11829,7 +12771,7 @@
       </c>
       <c r="D163" s="21" t="inlineStr">
         <is>
-          <t>Admissions from the Preparatory Program</t>
+          <t>Preparatory-to-Undergraduate page</t>
         </is>
       </c>
       <c r="E163" s="20" t="inlineStr">
@@ -11854,7 +12796,7 @@
       </c>
       <c r="I163" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P30.txt table rows: Engineering, Business Administration, Computer Engineering &amp; Science, IT, Sciences &amp; Human Studies, Architecture &amp; Design, Interior Design; P04 lists "B.S. in Artificial Intelligence" under College of Computer Engineering and Science</t>
+          <t>table rows: Engineering, Business Administration, Computer Engineering &amp; Science, IT, Sciences &amp; Human Studies, Architecture &amp; Design, Interior Design; Degrees &amp; Programs lists "B.S. in Artificial Intelligence" under College of Computer Engineering and Science</t>
         </is>
       </c>
     </row>
@@ -11874,7 +12816,7 @@
       </c>
       <c r="D164" s="23" t="inlineStr">
         <is>
-          <t>Admissions from the Preparatory Program</t>
+          <t>Preparatory-to-Undergraduate page</t>
         </is>
       </c>
       <c r="E164" s="22" t="inlineStr">
@@ -11899,7 +12841,7 @@
       </c>
       <c r="I164" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P30.txt: "College/Department | PRPM 0011 | PRPM 0012 | PRPM0022" ... "PRPM 0022 - Pre-Calculus"</t>
+          <t>"College/Department | PRPM 0011 | PRPM 0012 | PRPM0022" ... "PRPM 0022 - Pre-Calculus"</t>
         </is>
       </c>
     </row>
@@ -11919,7 +12861,7 @@
       </c>
       <c r="D165" s="21" t="inlineStr">
         <is>
-          <t>Admissions from the Preparatory Program</t>
+          <t>Preparatory-to-Undergraduate page</t>
         </is>
       </c>
       <c r="E165" s="20" t="inlineStr">
@@ -11944,7 +12886,7 @@
       </c>
       <c r="I165" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P30.txt: "Depending on students desired major at the university, the various colleges and majors require the following mathematics courses:"</t>
+          <t>"Depending on students desired major at the university, the various colleges and majors require the following mathematics courses:"</t>
         </is>
       </c>
     </row>
@@ -11964,7 +12906,7 @@
       </c>
       <c r="D166" s="23" t="inlineStr">
         <is>
-          <t>Admissions from the Preparatory Program</t>
+          <t>Preparatory-to-Undergraduate page</t>
         </is>
       </c>
       <c r="E166" s="22" t="inlineStr">
@@ -11989,7 +12931,7 @@
       </c>
       <c r="I166" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P30.txt: "... &gt; Undergraduate &gt; Preparatory Program to Undergraduate Programs" / "ADMISSIONS FROM THE PREPARATORY PROGRAM TO UNDERGRADUATE PROGRAMS"; pages/...txt TITLE: "Admission from the Preparatory Program to Undergraduate Programs"</t>
+          <t>"... &gt; Undergraduate &gt; Preparatory Program to Undergraduate Programs" / "ADMISSIONS FROM THE PREPARATORY PROGRAM TO UNDERGRADUATE PROGRAMS"</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12951,7 @@
       </c>
       <c r="D167" s="21" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering Majors Admission Requirements</t>
+          <t>CS &amp; Engineering Requirements page</t>
         </is>
       </c>
       <c r="E167" s="20" t="inlineStr">
@@ -12029,12 +12971,12 @@
       </c>
       <c r="H167" s="21" t="inlineStr">
         <is>
-          <t>Add Artificial Intelligence (after confirming the definitive list with Admissions) and use the same list on P31, P37 and /apply.</t>
+          <t>Add Artificial Intelligence (after confirming the definitive list with Admissions) and use the same list on the CS &amp; Engineering Requirements page, the SAT page and /apply.</t>
         </is>
       </c>
       <c r="I167" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P31.txt: "These majors are Architecture, Computer Science, Computer Engineering, Software Engineering, Mechanical Engineering, Electrical Engineering and Civil Engineering."; P37: "...Software Engineering, Artificial Intelligence, ..."; apply_raw_text.txt: "AI and Computer Science, Architecture and Engineering Majors"</t>
+          <t>"These majors are Architecture, Computer Science, Computer Engineering, Software Engineering, Mechanical Engineering, Electrical Engineering and Civil Engineering."; SAT page: "...Software Engineering, Artificial Intelligence, ..."; "AI and Computer Science, Architecture and Engineering Majors"</t>
         </is>
       </c>
     </row>
@@ -12054,7 +12996,7 @@
       </c>
       <c r="D168" s="23" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering Majors Admission Requirements</t>
+          <t>CS &amp; Engineering Requirements page</t>
         </is>
       </c>
       <c r="E168" s="22" t="inlineStr">
@@ -12079,7 +13021,7 @@
       </c>
       <c r="I168" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P31.txt: "*Students with lower marks may apply, however, the minimum weighted total, defined by the Admissions Office, should be met."; P25: "...40% Tahseely were 86 is the minimum acceptable score"</t>
+          <t>"*Students with lower marks may apply, however, the minimum weighted total, defined by the Admissions Office, should be met."; Medicine page: "...40% Tahseely were 86 is the minimum acceptable score"</t>
         </is>
       </c>
     </row>
@@ -12099,7 +13041,7 @@
       </c>
       <c r="D169" s="21" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering Majors Admission Requirements</t>
+          <t>CS &amp; Engineering Requirements page</t>
         </is>
       </c>
       <c r="E169" s="20" t="inlineStr">
@@ -12124,7 +13066,7 @@
       </c>
       <c r="I169" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P31.txt: "In order to be considered for admissions to Computer Science or Engineering majors, the candidate should meet the major specific requirements."</t>
+          <t>"In order to be considered for admissions to Computer Science or Engineering majors, the candidate should meet the major specific requirements."</t>
         </is>
       </c>
     </row>
@@ -12144,7 +13086,7 @@
       </c>
       <c r="D170" s="23" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering Majors Admission Requirements</t>
+          <t>CS &amp; Engineering Requirements page</t>
         </is>
       </c>
       <c r="E170" s="22" t="inlineStr">
@@ -12169,7 +13111,7 @@
       </c>
       <c r="I170" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P31.txt: "Submit original IELTS (Academic version) certificate or equivalent TOEFL iBT with acceptable scores (if available) or" / "For direct entry, submit original IELTS ... 6.0 overall and 5.5 in writing or equivalent TOEFL iBT with acceptable scores"; apply_raw_text.txt: "TOEFL iBT: Overall 83, Writing 19"</t>
+          <t>"Submit original IELTS (Academic version) certificate or equivalent TOEFL iBT with acceptable scores (if available) or" / "For direct entry, submit original IELTS ... 6.0 overall and 5.5 in writing or equivalent TOEFL iBT with acceptable scores"; "TOEFL iBT: Overall 83, Writing 19"</t>
         </is>
       </c>
     </row>
@@ -12189,7 +13131,7 @@
       </c>
       <c r="D171" s="21" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering Majors Admission Requirements</t>
+          <t>CS &amp; Engineering Requirements page</t>
         </is>
       </c>
       <c r="E171" s="20" t="inlineStr">
@@ -12214,7 +13156,7 @@
       </c>
       <c r="I171" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P31.txt: "Applicants who scored 400 or more in SAT Math section may wave one or more of the mathematics courses"</t>
+          <t>"Applicants who scored 400 or more in SAT Math section may wave one or more of the mathematics courses"</t>
         </is>
       </c>
     </row>
@@ -12234,7 +13176,7 @@
       </c>
       <c r="D172" s="23" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering Majors Admission Requirements</t>
+          <t>CS &amp; Engineering Requirements page</t>
         </is>
       </c>
       <c r="E172" s="22" t="inlineStr">
@@ -12259,7 +13201,7 @@
       </c>
       <c r="I172" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P31.txt: "Copy of Saudi ID" ... "Copy of passport"; P26: "Copy of Saudi ID or “Iqama” (for Non-Saudis)"</t>
+          <t>"Copy of Saudi ID" ... "Copy of passport"; Preparatory Program page: "Copy of Saudi ID or “Iqama” (for Non-Saudis)"</t>
         </is>
       </c>
     </row>
@@ -12279,7 +13221,7 @@
       </c>
       <c r="D173" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E173" s="20" t="inlineStr">
@@ -12304,7 +13246,7 @@
       </c>
       <c r="I173" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_fees_tf_ro.txt: "Undergraduate Fees for / Continuing 2024-2025"; pages/admission_fees_tf_ro_2024_2025.txt: "Undergraduate Fees (For continuing students admitted before Fall Semester 2025/2026) Full-Time Students"</t>
+          <t>"Undergraduate Fees for / Continuing 2024-2025"; "Undergraduate Fees (For continuing students admitted before Fall Semester 2025/2026) Full-Time Students"</t>
         </is>
       </c>
     </row>
@@ -12324,7 +13266,7 @@
       </c>
       <c r="D174" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E174" s="22" t="inlineStr">
@@ -12349,7 +13291,7 @@
       </c>
       <c r="I174" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P32.txt: "Medical Program Fees / Fall Semester 2026/2027 / Fall Semester 2025/2026 / Continuing Students 2024–2025"</t>
+          <t>"Medical Program Fees / Fall Semester 2026/2027 / Fall Semester 2025/2026 / Continuing Students 2024–2025"</t>
         </is>
       </c>
     </row>
@@ -12369,7 +13311,7 @@
       </c>
       <c r="D175" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E175" s="20" t="inlineStr">
@@ -12394,7 +13336,7 @@
       </c>
       <c r="I175" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_fees_tf_ro.txt: "Payment Schedule / Spring Semester 2025/2026 / Summer Semester 2025/2026 / Fall Semester 2026/2027"; payment_schedule_tf_ro_spring.txt deadlines "01-Mar-2026 ... 10-May-2026"</t>
+          <t>"Payment Schedule / Spring Semester 2025/2026 / Summer Semester 2025/2026 / Fall Semester 2026/2027"; deadlines "01-Mar-2026 ... 10-May-2026"</t>
         </is>
       </c>
     </row>
@@ -12414,7 +13356,7 @@
       </c>
       <c r="D176" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E176" s="22" t="inlineStr">
@@ -12439,7 +13381,7 @@
       </c>
       <c r="I176" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_fees_tf_ro.txt: sidebar "Undergraduate Fees Intake / 2026/2027" ... "Payment Schedule ... Fall Semester 2026/2027" ... in-page "Fall Semester 2026/2027"</t>
+          <t>sidebar "Undergraduate Fees Intake / 2026/2027" ... "Payment Schedule ... Fall Semester 2026/2027" ... in-page "Fall Semester 2026/2027"</t>
         </is>
       </c>
     </row>
@@ -12459,7 +13401,7 @@
       </c>
       <c r="D177" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E177" s="20" t="inlineStr">
@@ -12484,7 +13426,7 @@
       </c>
       <c r="I177" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_fees_tf_ro.txt: sidebar "Medical Program Studies" ... in-page "Medical Program Fees"</t>
+          <t>sidebar "Medical Program Studies" ... in-page "Medical Program Fees"</t>
         </is>
       </c>
     </row>
@@ -12504,7 +13446,7 @@
       </c>
       <c r="D178" s="23" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E178" s="22" t="inlineStr">
@@ -12529,7 +13471,7 @@
       </c>
       <c r="I178" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_fees_tf_ro.txt: "Continuing 2024-2025" ... "Intake 2026/2027" ... "Continuing Students 2024–2025"</t>
+          <t>"Continuing 2024-2025" ... "Intake 2026/2027" ... "Continuing Students 2024–2025"</t>
         </is>
       </c>
     </row>
@@ -12549,7 +13491,7 @@
       </c>
       <c r="D179" s="21" t="inlineStr">
         <is>
-          <t>Tuition &amp; Fees</t>
+          <t>Undergraduate Fees page</t>
         </is>
       </c>
       <c r="E179" s="20" t="inlineStr">
@@ -12574,7 +13516,7 @@
       </c>
       <c r="I179" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P32.txt: "Post Graduate Fees"</t>
+          <t>"Post Graduate Fees"</t>
         </is>
       </c>
     </row>
@@ -12594,7 +13536,7 @@
       </c>
       <c r="D180" s="23" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>English Tests overview</t>
         </is>
       </c>
       <c r="E180" s="22" t="inlineStr">
@@ -12619,7 +13561,7 @@
       </c>
       <c r="I180" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P33.txt: "Candidates with PMU recognized proficiency English language test certificates can verify the admission requirements on the following links IELTS requirements and TOEFL requirements."</t>
+          <t>"Candidates with PMU recognized proficiency English language test certificates can verify the admission requirements on the following links IELTS requirements and TOEFL requirements."</t>
         </is>
       </c>
     </row>
@@ -12639,7 +13581,7 @@
       </c>
       <c r="D181" s="21" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>English Tests overview</t>
         </is>
       </c>
       <c r="E181" s="20" t="inlineStr">
@@ -12664,7 +13606,7 @@
       </c>
       <c r="I181" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P33.txt: "Read more  about the current technology used for the English placement test Aptis."</t>
+          <t>"Read more  about the current technology used for the English placement test Aptis."</t>
         </is>
       </c>
     </row>
@@ -12684,7 +13626,7 @@
       </c>
       <c r="D182" s="23" t="inlineStr">
         <is>
-          <t>Overview</t>
+          <t>English Tests overview</t>
         </is>
       </c>
       <c r="E182" s="22" t="inlineStr">
@@ -12709,7 +13651,7 @@
       </c>
       <c r="I182" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P33.txt: "PMU has used international English language proficiency tests for admissions that ensure the accuracy of the outcomes."</t>
+          <t>"PMU has used international English language proficiency tests for admissions that ensure the accuracy of the outcomes."</t>
         </is>
       </c>
     </row>
@@ -12729,7 +13671,7 @@
       </c>
       <c r="D183" s="21" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E183" s="20" t="inlineStr">
@@ -12754,7 +13696,7 @@
       </c>
       <c r="I183" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "he/she will be required to take the IELTS through the PMU Testing Center or any other authorized testing center"; P36: "Core | 83 | 19"; apply_raw_text.txt: "TOEFL iBT: Overall 83, Writing 19"</t>
+          <t>"he/she will be required to take the IELTS through the PMU Testing Center or any other authorized testing center"; TOEFL page: "Core | 83 | 19"; "TOEFL iBT: Overall 83, Writing 19"</t>
         </is>
       </c>
     </row>
@@ -12774,7 +13716,7 @@
       </c>
       <c r="D184" s="23" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E184" s="22" t="inlineStr">
@@ -12799,7 +13741,7 @@
       </c>
       <c r="I184" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "Based on candidates overall and writing scores, they will be placed on one of the following levels: ... Level / Pre Beginner / Beginner / Intermediate / Advanced"</t>
+          <t>"Based on candidates overall and writing scores, they will be placed on one of the following levels: ... Level / Pre Beginner / Beginner / Intermediate / Advanced"</t>
         </is>
       </c>
     </row>
@@ -12819,7 +13761,7 @@
       </c>
       <c r="D185" s="21" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E185" s="20" t="inlineStr">
@@ -12844,7 +13786,7 @@
       </c>
       <c r="I185" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "they will be scheduled to take Aptis test (visit Aptis webpage)" ... "The duration of the placement test is approximately 4 hours."; P05: "End of Placement Test &amp; Retake | 2026-07-05"</t>
+          <t>"they will be scheduled to take Aptis test (visit Aptis webpage)" ... "The duration of the placement test is approximately 4 hours."; Admission Calendar: "End of Placement Test &amp; Retake | 2026-07-05"</t>
         </is>
       </c>
     </row>
@@ -12864,7 +13806,7 @@
       </c>
       <c r="D186" s="23" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E186" s="22" t="inlineStr">
@@ -12889,7 +13831,7 @@
       </c>
       <c r="I186" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "Pre Beginner"; P35/P36/P26/P30: "Pre-Beginner"</t>
+          <t>"Pre Beginner"; IELTS page/TOEFL page/Preparatory Program page/Prep-to-Undergraduate page: "Pre-Beginner"</t>
         </is>
       </c>
     </row>
@@ -12909,7 +13851,7 @@
       </c>
       <c r="D187" s="21" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E187" s="20" t="inlineStr">
@@ -12934,7 +13876,7 @@
       </c>
       <c r="I187" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "Based on candidates overall and writing scores"</t>
+          <t>"Based on candidates overall and writing scores"</t>
         </is>
       </c>
     </row>
@@ -12954,7 +13896,7 @@
       </c>
       <c r="D188" s="23" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E188" s="22" t="inlineStr">
@@ -12979,7 +13921,7 @@
       </c>
       <c r="I188" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "Aptis is an English language test service provided by British Council"</t>
+          <t>"Aptis is an English language test service provided by British Council"</t>
         </is>
       </c>
     </row>
@@ -12999,7 +13941,7 @@
       </c>
       <c r="D189" s="21" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E189" s="20" t="inlineStr">
@@ -13024,7 +13966,7 @@
       </c>
       <c r="I189" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "Once the candidates meet the admission’s general requirements, they will be scheduled to take Aptis test"</t>
+          <t>"Once the candidates meet the admission’s general requirements, they will be scheduled to take Aptis test"</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13986,7 @@
       </c>
       <c r="D190" s="23" t="inlineStr">
         <is>
-          <t>Aptis</t>
+          <t>Aptis page</t>
         </is>
       </c>
       <c r="E190" s="22" t="inlineStr">
@@ -13069,7 +14011,7 @@
       </c>
       <c r="I190" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P34.txt: "Candidates are highly encouraged to visit the below links to explore the Aptis before sitting for the test."</t>
+          <t>"Candidates are highly encouraged to visit the below links to explore the Aptis before sitting for the test."</t>
         </is>
       </c>
     </row>
@@ -13089,7 +14031,7 @@
       </c>
       <c r="D191" s="21" t="inlineStr">
         <is>
-          <t>IELTS</t>
+          <t>IELTS page</t>
         </is>
       </c>
       <c r="E191" s="20" t="inlineStr">
@@ -13114,7 +14056,7 @@
       </c>
       <c r="I191" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P35.txt: "if the candidate provides a valid  IELTS  certificate (Academic version)" ... "The validation of the IELTS certificate | Two years..."; P36: "The original TOEFL iBT report has to be sent directly from ETS to PMU"</t>
+          <t>"if the candidate provides a valid  IELTS  certificate (Academic version)" ... "The validation of the IELTS certificate | Two years..."; TOEFL page: "The original TOEFL iBT report has to be sent directly from ETS to PMU"</t>
         </is>
       </c>
     </row>
@@ -13134,7 +14076,7 @@
       </c>
       <c r="D192" s="23" t="inlineStr">
         <is>
-          <t>IELTS</t>
+          <t>IELTS page</t>
         </is>
       </c>
       <c r="E192" s="22" t="inlineStr">
@@ -13159,7 +14101,7 @@
       </c>
       <c r="I192" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P35.txt: "might be admitted to different level in the Preparatory Program ... successfully meets one of the below requirements of the categories below:"</t>
+          <t>"might be admitted to different level in the Preparatory Program ... successfully meets one of the below requirements of the categories below:"</t>
         </is>
       </c>
     </row>
@@ -13179,7 +14121,7 @@
       </c>
       <c r="D193" s="21" t="inlineStr">
         <is>
-          <t>IELTS</t>
+          <t>IELTS page</t>
         </is>
       </c>
       <c r="E193" s="20" t="inlineStr">
@@ -13204,7 +14146,7 @@
       </c>
       <c r="I193" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P35.txt: "The validation of the IELTS certificate | Two years from the date of IELTS test"</t>
+          <t>"The validation of the IELTS certificate | Two years from the date of IELTS test"</t>
         </is>
       </c>
     </row>
@@ -13224,7 +14166,7 @@
       </c>
       <c r="D194" s="23" t="inlineStr">
         <is>
-          <t>TOEFL</t>
+          <t>TOEFL page</t>
         </is>
       </c>
       <c r="E194" s="22" t="inlineStr">
@@ -13249,7 +14191,7 @@
       </c>
       <c r="I194" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P36.txt: "might be admitted to different level in the Preparatory Program ... meets one of the below minimum requirements of the categories below:"</t>
+          <t>"might be admitted to different level in the Preparatory Program ... meets one of the below minimum requirements of the categories below:"</t>
         </is>
       </c>
     </row>
@@ -13269,7 +14211,7 @@
       </c>
       <c r="D195" s="21" t="inlineStr">
         <is>
-          <t>TOEFL</t>
+          <t>TOEFL page</t>
         </is>
       </c>
       <c r="E195" s="20" t="inlineStr">
@@ -13294,7 +14236,7 @@
       </c>
       <c r="I195" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P36.txt: "The validation of the TOEFL iBT report | Two years from the date of TOEFL iBT test"</t>
+          <t>"The validation of the TOEFL iBT report | Two years from the date of TOEFL iBT test"</t>
         </is>
       </c>
     </row>
@@ -13314,7 +14256,7 @@
       </c>
       <c r="D196" s="23" t="inlineStr">
         <is>
-          <t>TOEFL</t>
+          <t>TOEFL page</t>
         </is>
       </c>
       <c r="E196" s="22" t="inlineStr">
@@ -13339,7 +14281,7 @@
       </c>
       <c r="I196" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P36.txt: "the commencement date of the applied semester" (blank lines) "(online or home edition is not accepted)" / "The original TOEFL iBT report has to be sent directly from ETS to PMU"</t>
+          <t>"the commencement date of the applied semester" (blank lines) "(online or home edition is not accepted)" / "The original TOEFL iBT report has to be sent directly from ETS to PMU"</t>
         </is>
       </c>
     </row>
@@ -13359,7 +14301,7 @@
       </c>
       <c r="D197" s="21" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E197" s="20" t="inlineStr">
@@ -13379,12 +14321,12 @@
       </c>
       <c r="H197" s="21" t="inlineStr">
         <is>
-          <t>Publish one definitive list on P31, P37 and /apply and remove "etc.".</t>
+          <t>Publish one definitive list on the CS &amp; Engineering Requirements page, the SAT page and /apply and remove "etc.".</t>
         </is>
       </c>
       <c r="I197" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P37.txt: "Software Engineering, Artificial Intelligence, Mechanical Engineering, Electrical Engineering and Civil Engineering etc."; P31: list without AI and without "etc."</t>
+          <t>"Software Engineering, Artificial Intelligence, Mechanical Engineering, Electrical Engineering and Civil Engineering etc."; CS &amp; Engineering page: list without AI and without "etc."</t>
         </is>
       </c>
     </row>
@@ -13404,7 +14346,7 @@
       </c>
       <c r="D198" s="23" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E198" s="22" t="inlineStr">
@@ -13429,7 +14371,7 @@
       </c>
       <c r="I198" s="23" t="inlineStr">
         <is>
-          <t>excluded.json: {"url": "https://www.etec.gov.sa/en/service/theHumanitiesTrack/servicegoal", "t": "Tahseely", "from": "https://www.pmu.edu.sa/admission/sat-admission"}</t>
+          <t>{"url": "https://www.etec.gov.sa/en/service/theHumanitiesTrack/servicegoal", "t": "Tahseely", "from": "https://www.pmu.edu.sa/admission/sat-admission"}</t>
         </is>
       </c>
     </row>
@@ -13449,7 +14391,7 @@
       </c>
       <c r="D199" s="21" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E199" s="20" t="inlineStr">
@@ -13474,7 +14416,7 @@
       </c>
       <c r="I199" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P37.txt: "Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests." ; P35/P36: "Two years from the date of ... test"</t>
+          <t>"Students with international high school certificate might submit SAT with minimum score of 1200 instead of Qudrat and Tahseely tests." ; IELTS page/TOEFL page: "Two years from the date of ... test"</t>
         </is>
       </c>
     </row>
@@ -13494,7 +14436,7 @@
       </c>
       <c r="D200" s="23" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E200" s="22" t="inlineStr">
@@ -13519,7 +14461,7 @@
       </c>
       <c r="I200" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P37.txt: "may wave one or more of the mathematics courses"; "Introductory Algebra | Wave | Wave" ... "Pre-Calculus | N/A | Wave"</t>
+          <t>"may wave one or more of the mathematics courses"; "Introductory Algebra | Wave | Wave" ... "Pre-Calculus | N/A | Wave"</t>
         </is>
       </c>
     </row>
@@ -13539,7 +14481,7 @@
       </c>
       <c r="D201" s="21" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E201" s="20" t="inlineStr">
@@ -13559,12 +14501,12 @@
       </c>
       <c r="H201" s="21" t="inlineStr">
         <is>
-          <t>Use "SAT" consistently across P37, P31, P08 and the Admissions overview.</t>
+          <t>Use "SAT" consistently across the SAT page, the CS &amp; Engineering Requirements page, the /apply page and the Admissions overview.</t>
         </is>
       </c>
       <c r="I201" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P37.txt: "SCHOLASTIC APTITUDE TEST" / "Scholastic Aptitude Test (SAT)"; P31: "(SAT 1)"; apply_raw_text.txt: "Qudrat / SAT 1"</t>
+          <t>"SCHOLASTIC APTITUDE TEST" / "Scholastic Aptitude Test (SAT)"; CS &amp; Engineering page: "(SAT 1)"; "Qudrat / SAT 1"</t>
         </is>
       </c>
     </row>
@@ -13584,7 +14526,7 @@
       </c>
       <c r="D202" s="23" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E202" s="22" t="inlineStr">
@@ -13609,7 +14551,7 @@
       </c>
       <c r="I202" s="23" t="inlineStr">
         <is>
-          <t>rendered/pages/P37.txt: "However, some majors require specific level of certain skills to apply for these specializations."</t>
+          <t>"However, some majors require specific level of certain skills to apply for these specializations."</t>
         </is>
       </c>
     </row>
@@ -13629,7 +14571,7 @@
       </c>
       <c r="D203" s="21" t="inlineStr">
         <is>
-          <t>Scholastic Aptitude Test (SAT)</t>
+          <t>SAT page</t>
         </is>
       </c>
       <c r="E203" s="20" t="inlineStr">
@@ -13654,7 +14596,7 @@
       </c>
       <c r="I203" s="21" t="inlineStr">
         <is>
-          <t>rendered/pages/P37.txt: "Introductory Algebra | Wave | Wave / Intermediate Algebra | N/A | Wave / Pre-Calculus | N/A | Wave"; P30: "PRPM 0011 – Introductory Algebra"</t>
+          <t>"Introductory Algebra | Wave | Wave / Intermediate Algebra | N/A | Wave / Pre-Calculus | N/A | Wave"; Prep-to-Undergraduate page: "PRPM 0011 – Introductory Algebra"</t>
         </is>
       </c>
     </row>
@@ -13674,7 +14616,7 @@
       </c>
       <c r="D204" s="23" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E204" s="22" t="inlineStr">
@@ -13699,7 +14641,7 @@
       </c>
       <c r="I204" s="23" t="inlineStr">
         <is>
-          <t>browser/result2_mobile_probes.json (P04/P05 sidebar): {"t": "Contact Info", "h": ".../Admission/Admission_Contact_GDP.aspx"}; rendered/pages/P23.txt: "CONTACT INFO | Graduate Study Admission Coordinator | Email: graduateadm@pmu.edu.sa"</t>
+          <t>Sidebar "Contact Info" opens /Admission/Admission_Contact_GDP.aspx: "CONTACT INFO | Graduate Study Admission Coordinator | Email: graduateadm@pmu.edu.sa"</t>
         </is>
       </c>
     </row>
@@ -13719,7 +14661,7 @@
       </c>
       <c r="D205" s="21" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E205" s="20" t="inlineStr">
@@ -13744,7 +14686,7 @@
       </c>
       <c r="I205" s="21" t="inlineStr">
         <is>
-          <t>admission_page_dom.json (P00): 'Contact Us' -&gt; https://pmu.edu.sa/Staff_Profile/Staff_List.aspx?&amp;DEpt=4&amp;Name=Staff%20Name; excluded.json (P02): "pmustaffs/departmentstafflist/4", "t": "Contact Us"</t>
+          <t>'Contact Us' -&gt; https://pmu.edu.sa/Staff_Profile/Staff_List.aspx?&amp;DEpt=4&amp;Name=Staff%20Name; "pmustaffs/departmentstafflist/4", "t": "Contact Us"</t>
         </is>
       </c>
     </row>
@@ -13764,7 +14706,7 @@
       </c>
       <c r="D206" s="23" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E206" s="22" t="inlineStr">
@@ -13789,7 +14731,7 @@
       </c>
       <c r="I206" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_future_students_ro.txt: " Admission Calendar" (sidebar); rendered/pages/P00.txt: "Admissions Calendar"; P05.txt: "ADMISSIONS CALENDARS"</t>
+          <t>" Admission Calendar" (sidebar); "Admissions Calendar"; "ADMISSIONS CALENDARS"</t>
         </is>
       </c>
     </row>
@@ -13809,7 +14751,7 @@
       </c>
       <c r="D207" s="21" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E207" s="20" t="inlineStr">
@@ -13829,12 +14771,12 @@
       </c>
       <c r="H207" s="21" t="inlineStr">
         <is>
-          <t>Adopt one official abbreviation (the programme name 'Master of Science in Human Development (MSHD)' suggests MSHD) and correct the P11 page title.</t>
+          <t>Adopt one official abbreviation (the programme name 'Master of Science in Human Development (MSHD)' suggests MSHD) and correct the PhD Mechanical Engineering page page title.</t>
         </is>
       </c>
       <c r="I207" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_future_students_ro.txt: "Application Form for MSEHD"; P00.txt: "Admissions to the MSHD Program"; pages/admission_application_form_deme_gdp.txt: "TITLE: Application Form for MSDH ::"</t>
+          <t>"Application Form for MSEHD"; "Admissions to the MSHD Program"; "TITLE: Application Form for MSDH ::"</t>
         </is>
       </c>
     </row>
@@ -13854,7 +14796,7 @@
       </c>
       <c r="D208" s="23" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E208" s="22" t="inlineStr">
@@ -13879,7 +14821,7 @@
       </c>
       <c r="I208" s="23" t="inlineStr">
         <is>
-          <t>browser/result2_mobile_probes.json (P10, P20, P21 hrefs): "https://www.pmu.edu.sa/Admission/Tuition_Fees_RO.aspx"; crawl/admission_page_dom.json (P00 graduate menu): "Tuition &amp; Fees | .../Admission/Post_Graduate_Fees_TF_RO.aspx"</t>
+          <t>Graduate sidebar "Tuition &amp; Fees" opens /Admission/Tuition_Fees_RO.aspx instead of /Admission/Post_Graduate_Fees_TF_RO.aspx</t>
         </is>
       </c>
     </row>
@@ -13899,7 +14841,7 @@
       </c>
       <c r="D209" s="21" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E209" s="20" t="inlineStr">
@@ -13924,7 +14866,7 @@
       </c>
       <c r="I209" s="21" t="inlineStr">
         <is>
-          <t>P15.txt: "Graduate Programs &gt; MSHD Admissions"; P10 href "Admissions_Requirements_MSEHD_GDP.aspx"; P23 source: "Application Form for MSEHD"; P11 title: "Application Form for MSDH"; P22: "Master of Science in Education and Human Development"</t>
+          <t>"Graduate Programs &gt; MSHD Admissions"; Graduate Programs page href "Admissions_Requirements_MSEHD_GDP.aspx"; Graduate Contact page source: "Application Form for MSEHD"; PhD ME page title: "Application Form for MSDH"; Post Graduate Fees: "Master of Science in Education and Human Development"</t>
         </is>
       </c>
     </row>
@@ -13944,7 +14886,7 @@
       </c>
       <c r="D210" s="23" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E210" s="22" t="inlineStr">
@@ -13969,7 +14911,7 @@
       </c>
       <c r="I210" s="23" t="inlineStr">
         <is>
-          <t>P11.txt (also P12, P14, P16, P17, P18, P19): "Candidates will be personally interviewed by committee of the program administrators and faculty"</t>
+          <t>"Candidates will be personally interviewed by committee of the program administrators and faculty"</t>
         </is>
       </c>
     </row>
@@ -13989,7 +14931,7 @@
       </c>
       <c r="D211" s="21" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E211" s="20" t="inlineStr">
@@ -14014,7 +14956,7 @@
       </c>
       <c r="I211" s="21" t="inlineStr">
         <is>
-          <t>P05.txt: "Graduate Admission Calendar ... Last day to apply for graduate studies | 2026-07-16"; no deadline/date text in P10–P21</t>
+          <t>"Graduate Admission Calendar ... Last day to apply for graduate studies | 2026-07-16"; no deadline/date text in Graduate Programs page–MIBL page</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14976,7 @@
       </c>
       <c r="D212" s="23" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E212" s="22" t="inlineStr">
@@ -14059,7 +15001,7 @@
       </c>
       <c r="I212" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_application_form_mba_gdp.txt (also EMBA, PhD-BA, MSHD, MSME, MIBL forms and application_form_gr): "Pay a non-refundable application fee of SAR 950 (incl. VAT) upon submission of documents"</t>
+          <t>"Pay a non-refundable application fee of SAR 950 (incl. VAT) upon submission of documents"</t>
         </is>
       </c>
     </row>
@@ -14079,7 +15021,7 @@
       </c>
       <c r="D213" s="21" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E213" s="20" t="inlineStr">
@@ -14104,7 +15046,7 @@
       </c>
       <c r="I213" s="21" t="inlineStr">
         <is>
-          <t>crawl/admission_page_dom.json: "t": "Contact Info", "raw": "../Admission/Admission_Contact_GDP.aspx"; pages/admission_college_of_medicine_admission.txt sidebar ends "Apply Now / Contact Info"; P23 lists only "Graduate Study Admission Coordinator"</t>
+          <t>Undergraduate sidebar "Contact Info" opens /Admission/Admission_Contact_GDP.aspx, which lists only the "Graduate Study Admission Coordinator"</t>
         </is>
       </c>
     </row>
@@ -14124,7 +15066,7 @@
       </c>
       <c r="D214" s="23" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E214" s="22" t="inlineStr">
@@ -14149,7 +15091,7 @@
       </c>
       <c r="I214" s="23" t="inlineStr">
         <is>
-          <t>pages/admission_college_of_medicine_admission.txt sidebar: "Web Admission Guide"; probes: "https://www.pmu.edu.sa/PDF/Viewer.aspx?ID=203"; scope_inventory.csv: /apply "redirects to https://admissions.pmu.edu.sa/welcome"</t>
+          <t>Sidebar link "Web Admission Guide" opens https://www.pmu.edu.sa/PDF/Viewer.aspx?ID=203; /apply redirects to https://admissions.pmu.edu.sa/welcome</t>
         </is>
       </c>
     </row>
@@ -14169,7 +15111,7 @@
       </c>
       <c r="D215" s="21" t="inlineStr">
         <is>
-          <t>Shared admissions sidebar menu</t>
+          <t>Admissions sidebar menu (all pages)</t>
         </is>
       </c>
       <c r="E215" s="20" t="inlineStr">
@@ -14194,7 +15136,7 @@
       </c>
       <c r="I215" s="21" t="inlineStr">
         <is>
-          <t>pages/admission_sat-admission.txt menu: "Undergraduate Admissions / Home / New Applicant / Freshman"; breadcrumb "Home &gt;"; browser/result2_mobile_probes.json href "https://www.pmu.edu.sa/Admission/Undergraduate_Programs_Admission.aspx"</t>
+          <t>menu: "Undergraduate Admissions / Home / New Applicant / Freshman"; breadcrumb "Home &gt;"; "https://www.pmu.edu.sa/Admission/Undergraduate_Programs_Admission.aspx"</t>
         </is>
       </c>
     </row>
@@ -14231,14 +15173,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -14251,7 +15196,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Values pending these decisions should not be published as policy until confirmed in writing by the owner</t>
+          <t>Pending values should not be published as policy until the owner confirms them in writing</t>
         </is>
       </c>
     </row>
@@ -14261,6 +15206,9 @@
       <c r="C3" s="18" t="n"/>
       <c r="D3" s="18" t="n"/>
       <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="19" t="inlineStr">
@@ -14270,20 +15218,35 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Decision needed</t>
+          <t>Decision required</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
+          <t>What the published pages show</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>Recommendation (subject to owner approval)</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
           <t>Owner (proposed)</t>
         </is>
       </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>Linked refs</t>
         </is>
       </c>
-      <c r="E4" s="19" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
@@ -14297,20 +15260,35 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>Next intake and one application route per applicant type (Saudi / non-Saudi / transfer / visiting / graduate); publish requirements on a visible page</t>
+          <t>Next intake and application route by applicant type</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
+          <t>The only admission calendar covers Fall 2026 and all dates have passed; the portal shows no published events; /apply redirects instantly; the non-Saudi route shows "Closed" with no date.</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>(a) Publish the next-intake calendar now; (b) publish an interim notice "Admissions closed – next intake opens on …" until dates are approved.</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Publish (b) immediately, then (a) once dates are approved, with one route per applicant type (Saudi, non-Saudi, transfer, visiting, graduate).</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
           <t>Admissions + Web + IT</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F-04, F-22, F-23, F-48, F-71</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14324,20 +15302,35 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Fee &amp; VAT matrix: international transfer/visitor (500 excl. vs 950 incl.), Medicine (1,000 vs 1,150), Aptis (575; requested 950)</t>
+          <t>Fee and VAT matrix</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
+          <t>International transfer/visitor fee SAR 500 (excl. VAT) vs SAR 950 (incl. VAT) on other pages and on the official Other Fees page; Medicine SAR 1,000 vs SAR 1,150; Aptis SAR 575 (a change to SAR 950 was requested).</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>(a) Confirm current amounts; (b) approve new amounts with an effective intake.</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Finance confirms one table (amount, VAT basis, applicant type, effective intake); every admission page then cites that table.</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
           <t>Finance + Admissions + PREP</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F-02, F-03, F-13</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="H6" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14351,20 +15344,35 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>Minimum weighted scores (74% requested vs published minima giving 73% / 72%) and whether to publish them</t>
+          <t>Minimum weighted scores</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
+          <t>Published minima compute to 72% (non-engineering) and 73% (engineering/AI/CS); 74% was requested in the thread; the CS &amp; Engineering page refers to a minimum weighted total that is not published.</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>(a) Publish one figure per group; (b) keep the figure internal and remove the reference; (c) revise the component minima.</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>Decide (a) or (b) and record the effective intake; ensure the published component minima are consistent with the decision.</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
           <t>Admissions policy owner</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F-07, F-71</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14378,20 +15386,35 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>Criteria for international CS/Engineering applicants replacing SAT II; scope of SAT 1200 alternative; list of majors with higher requirements (incl. AI?)</t>
+          <t>Undergraduate criteria for international and specialised majors</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
+          <t>SAT II (discontinued in 2021) is still required for international CS/Engineering applicants; the SAT 1200 alternative and the list of majors with higher requirements (AI included or not) differ between pages.</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>(a) Replace SAT II with SAT I/Tahseely-equivalent criteria; (b) define the SAT 1200 scope; (c) publish one list of majors.</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Approve (a)–(c) together so that the international, SAT, CS &amp; Engineering and /apply pages state the same rule.</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
           <t>Admissions + Colleges</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F-01, F-35, F-76</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14405,20 +15428,35 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>Graduate English requirements: MIBL 6.0 vs 6.5; EMGMS (remove other university text, IELTS 7/TOEFL 79/PBT); application route for EMGMS</t>
+          <t>Graduate English requirements and EMGMS page</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
+          <t>MIBL states IELTS 6.5 on one page and 6.0 on another; the EMGMS page contains another institution's text, different English thresholds and no application route.</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>(a) Confirm MIBL threshold; (b) replace the EMGMS page with PMU-approved requirements; (c) confirm EMGMS intake status.</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>Remove the external text immediately; publish approved EMGMS requirements and route, and one MIBL threshold.</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
           <t>Graduate Studies + College of Engineering</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F-16, F-29, F-68, F-69, F-74</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -14432,20 +15470,35 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>TOEFL/IELTS equivalence table incl. the TOEFL 1–6 scale</t>
+          <t>English test equivalence</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
+          <t>Undergraduate pages state 'equivalent TOEFL iBT' without a score; IELTS 6.0 is paired with TOEFL 83 (not equivalent in ETS tables); the TOEFL 1–6 reporting scale is not addressed; the Aptis page mentions IELTS only for direct entry.</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>(a) Approve one equivalence table; (b) keep the current table and state its basis.</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Approve one table for all pages, including the TOEFL 1–6 scale.</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
           <t>Admissions + Testing Center</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F-08, F-10, F-41</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="H10" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14459,20 +15512,35 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Medicine selection formula and minimums; language requirement</t>
+          <t>Medicine selection formula</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
         <is>
+          <t>Published component minima (95 / 80 / 80) cannot reach the stated minimum total of 86; no English-language requirement is stated.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>(a) Revise the minima; (b) revise the formula wording.</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>College of Medicine confirms the formula, minima and language requirement.</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
           <t>College of Medicine + Admissions</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F-06, F-40</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14486,20 +15554,35 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Graduate catalogue: offered programmes and canonical pages (MSHD/MSEHD, Innovation &amp; Sustainability programme)</t>
+          <t>Graduate catalogue and programme names</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
+          <t>Some priced programmes have no admission page (e.g. Innovation, Sustainability and Entrepreneurship); names differ across pages (MSHD/MSEHD, PhD/Doctoral); the PhD ME page title names another programme.</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>(a) Confirm the programmes offered per intake; (b) adopt one official name per programme.</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>Publish one graduate catalogue used by admission, fee and programme pages.</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
           <t>Graduate Studies + Academic Affairs</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F-11, F-25, F-32, F-75</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="H12" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14513,20 +15596,35 @@
       </c>
       <c r="B13" s="21" t="inlineStr">
         <is>
-          <t>Admissions contact channel and privacy notice on query form / portal</t>
+          <t>Admissions contact and privacy notice</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
         <is>
+          <t>'Contact Us' leads to a Student Affairs staff list; the query form collects name, email and mobile without a visible privacy notice; the portal shows no privacy link.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>(a) Create an admissions contact page; (b) add a privacy notice after compliance review.</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>Approve both; publish an official admissions email/phone and a reviewed notice.</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
           <t>Admissions + Compliance</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F-45, F-65, F-77</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
@@ -14540,36 +15638,51 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Retire/redirect legacy pages (freshman_admission, transfer-student-admission, ielts_course, old calendars/news)</t>
+          <t>Legacy pages</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
+          <t>Older admission pages (e.g. freshman admission with old weights, transfer page with IELTS 5.0, 2019 IELTS course) remain online and reachable by search.</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>(a) Redirect to current pages; (b) unpublish; (c) archive with a notice.</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>Redirect or unpublish after Admissions confirms each page.</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
           <t>Admissions + Web</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F-05, F-09, F-15, F-17, F-33</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E14"/>
-  <conditionalFormatting sqref="E5:E14">
+  <autoFilter ref="A4:H14"/>
+  <conditionalFormatting sqref="H5:H14">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>E5="P1"</formula>
+      <formula>H5="P1"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>E5="P2"</formula>
+      <formula>H5="P2"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>E5="P3"</formula>
+      <formula>H5="P3"</formula>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
@@ -14610,7 +15723,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Amendments requested in the thread "comments on Admission pages", re-checked against the live site on 10 October 2026</t>
+          <t>Amendments requested in the thread "comments on Admission pages", re-checked against the live site on 11 October 2026</t>
         </is>
       </c>
     </row>
@@ -14627,7 +15740,7 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>Live today (10 Oct 2026)</t>
+          <t>Live status (re-checked 11 Oct 2026)</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
